--- a/docs/xlsx/jobs-2026-09-28.xlsx
+++ b/docs/xlsx/jobs-2026-09-28.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="991" uniqueCount="698">
   <si>
     <t>Title</t>
   </si>
@@ -38,13 +38,2083 @@
   </si>
   <si>
     <t>Link</t>
+  </si>
+  <si>
+    <t>Accountant</t>
+  </si>
+  <si>
+    <t>Kansas Department of Wildlife and Parks</t>
+  </si>
+  <si>
+    <t>Topeka, KS</t>
+  </si>
+  <si>
+    <t>Permanent</t>
+  </si>
+  <si>
+    <t>$23.75 per hour</t>
+  </si>
+  <si>
+    <t>admin-leadership</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-accountant-topeka-kansas/5893377513</t>
+  </si>
+  <si>
+    <t>Clean Air Advocate</t>
+  </si>
+  <si>
+    <t>Environment America</t>
+  </si>
+  <si>
+    <t>Boston, MA</t>
+  </si>
+  <si>
+    <t>The target annual compensation for someone with 2-5 years of relevant experience is $41,750-$46,000.</t>
+  </si>
+  <si>
+    <t>admin-leadership-policy-and-law</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-clean-air-advocate-boston-massachusetts/5514745033</t>
+  </si>
+  <si>
+    <t>Coordinator, Community Engagement</t>
+  </si>
+  <si>
+    <t>Napa County Resource Conservation District</t>
+  </si>
+  <si>
+    <t>Napa, CA</t>
+  </si>
+  <si>
+    <t>$71,282 - $80,226 per year</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-coordinator-community-engagement-napa-california/2648316937</t>
+  </si>
+  <si>
+    <t>Director, Federal Campaigns</t>
+  </si>
+  <si>
+    <t>Washington, DC</t>
+  </si>
+  <si>
+    <t>The target annual compensation for someone with 4-8 years of relevant experience is $43,500-$60,000.</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-director-federal-campaigns-washington-dc/2198508520</t>
+  </si>
+  <si>
+    <t>Ecological Operator Technician</t>
+  </si>
+  <si>
+    <t>Native Resource Preservation LLC</t>
+  </si>
+  <si>
+    <t>West Saint Paul or Marshall/Clarkfield, MN</t>
+  </si>
+  <si>
+    <t>$20.00/hr</t>
+  </si>
+  <si>
+    <t>restoration-forestry-botany</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-ecological-operator-technician-west-saint-paul-minnesota/4054029989</t>
+  </si>
+  <si>
+    <t>Ecological Technician</t>
+  </si>
+  <si>
+    <t>$19.00/hr</t>
+  </si>
+  <si>
+    <t>botany-restoration</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-ecological-technician-west-saint-paul-minnesota/1388394287</t>
+  </si>
+  <si>
+    <t>Educator</t>
+  </si>
+  <si>
+    <t>HAWKs Lake Norman</t>
+  </si>
+  <si>
+    <t>Cornelius, NC</t>
+  </si>
+  <si>
+    <t>$18 - $20 per hour</t>
+  </si>
+  <si>
+    <t>environmental-education-outdoor-recreation</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-educator-cornelius-north-carolina/5795931659</t>
+  </si>
+  <si>
+    <t>Environmental Inspector I/II</t>
+  </si>
+  <si>
+    <t>City of San Jose Environmental Services Department</t>
+  </si>
+  <si>
+    <t>San Jose, CA</t>
+  </si>
+  <si>
+    <t>$99,361.60 - $133,140.80 per year</t>
+  </si>
+  <si>
+    <t>hydrology</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-environmental-inspector-iii-san-jose-california/1319583998</t>
+  </si>
+  <si>
+    <t>Executive Director</t>
+  </si>
+  <si>
+    <t>LandWatch</t>
+  </si>
+  <si>
+    <t>Salinas, CA</t>
+  </si>
+  <si>
+    <t>$140,000 - $160,000 per year</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-executive-director-salinas-california/9127744304</t>
+  </si>
+  <si>
+    <t>Clean &amp; Prosperous</t>
+  </si>
+  <si>
+    <t>Seattle, WA</t>
+  </si>
+  <si>
+    <t>$185,000 - $215,000 per year</t>
+  </si>
+  <si>
+    <t>admin-leadership-policy-and-law-sustainability</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-executive-director-seattle-washington/9956210856</t>
+  </si>
+  <si>
+    <t>Federal Lands Special Project Manager</t>
+  </si>
+  <si>
+    <t>Washington State Department of Natural Resources</t>
+  </si>
+  <si>
+    <t>Olympia, WA</t>
+  </si>
+  <si>
+    <t>Temporary</t>
+  </si>
+  <si>
+    <t>$7,220 - $8,419 per month</t>
+  </si>
+  <si>
+    <t>admin-leadership-forestry</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-federal-lands-special-project-manager-olympia-washington/1856278324</t>
+  </si>
+  <si>
+    <t>Field Crew Leader</t>
+  </si>
+  <si>
+    <t>O'ahu Invasive Species Committee</t>
+  </si>
+  <si>
+    <t>Kailua, HI</t>
+  </si>
+  <si>
+    <t>$4,071 per month</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-field-crew-leader-kailua-hawaii/5958834693</t>
+  </si>
+  <si>
+    <t>Forester Specialist</t>
+  </si>
+  <si>
+    <t>Indiana Adjutant General's Office</t>
+  </si>
+  <si>
+    <t>Edinburgh, IN</t>
+  </si>
+  <si>
+    <t>$47,320 per year</t>
+  </si>
+  <si>
+    <t>forestry</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-forester-specialist-edinburgh-indiana/5238374576</t>
+  </si>
+  <si>
+    <t>Gopher Tortoise Program Lead</t>
+  </si>
+  <si>
+    <t>Lykes Bros. Inc.</t>
+  </si>
+  <si>
+    <t>Tampa, FL</t>
+  </si>
+  <si>
+    <t>Competitive base and bonus.</t>
+  </si>
+  <si>
+    <t>admin-leadership-wildlife</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-gopher-tortoise-program-lead-tampa-florida/6344687380</t>
+  </si>
+  <si>
+    <t>Government Relations &amp; Civic Engagement Manager</t>
+  </si>
+  <si>
+    <t>American Bird Conservancy</t>
+  </si>
+  <si>
+    <t>Remote, Remote</t>
+  </si>
+  <si>
+    <t>Estimated at $48/hour*; Based on experience</t>
+  </si>
+  <si>
+    <t>admin-leadership-policy-and-law-wildlife</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-government-relations--civic-engagement-manager-remote-remote/4341578088</t>
+  </si>
+  <si>
+    <t>Graduate Fellow in Environmental Education and Science Communication</t>
+  </si>
+  <si>
+    <t>University of Idaho</t>
+  </si>
+  <si>
+    <t>McCall, ID</t>
+  </si>
+  <si>
+    <t>Student</t>
+  </si>
+  <si>
+    <t>$1000 Fellowship award</t>
+  </si>
+  <si>
+    <t>environmental-education</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-graduate-fellow-in-environmental-education-and-science-communication-mccall-idaho/8548047787</t>
+  </si>
+  <si>
+    <t>Habitat Senior Assistant</t>
+  </si>
+  <si>
+    <t>Lewis and Clark Community College</t>
+  </si>
+  <si>
+    <t>East Alton, IL</t>
+  </si>
+  <si>
+    <t>$40,716 - $52,931 per year</t>
+  </si>
+  <si>
+    <t>forestry-restoration</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-habitat-senior-assistant-east-alton-illinois/7076806935</t>
+  </si>
+  <si>
+    <t>Hunting and Angling Recruitment, Retention &amp; Reactivation Specialist</t>
+  </si>
+  <si>
+    <t>Council to Advance Hunting and the Shooting Sports/WY Game &amp; Fish Dept.</t>
+  </si>
+  <si>
+    <t>Cheyenne, WY</t>
+  </si>
+  <si>
+    <t>$52,000 per year</t>
+  </si>
+  <si>
+    <t>admin-leadership-outdoor-recreation</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-hunting-and-angling-recruitment-retention--reactivation-specialist-cheyenne-wyoming/8595893066</t>
+  </si>
+  <si>
+    <t>Natural Resource Specialist</t>
+  </si>
+  <si>
+    <t>Sacramento Area Sewer District</t>
+  </si>
+  <si>
+    <t>Sacramento, CA</t>
+  </si>
+  <si>
+    <t>$86,611.20 - $105,289.60 per year</t>
+  </si>
+  <si>
+    <t>general-stewardship-wildlife</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-natural-resource-specialist-sacramento-california/8858103210</t>
+  </si>
+  <si>
+    <t>Operations and Finance Manager, Remote</t>
+  </si>
+  <si>
+    <t>Working Circle</t>
+  </si>
+  <si>
+    <t>$65,000 - $75,000 per year</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-operations-and-finance-manager-remote-remote-remote/9731335830</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-operations-and-finance-manager-remote-remote-remote/5109660854</t>
+  </si>
+  <si>
+    <t>Operations Manager</t>
+  </si>
+  <si>
+    <t>Environmental Protection in the Caribbean</t>
+  </si>
+  <si>
+    <t>Green Cove Springs, FL</t>
+  </si>
+  <si>
+    <t>$20 - $25 per hour</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-operations-manager-green-cove-springs-florida/4588418091</t>
+  </si>
+  <si>
+    <t>Park Attendant</t>
+  </si>
+  <si>
+    <t>City of Albuquerque Open Space/Tryfacta</t>
+  </si>
+  <si>
+    <t>Albuquerque, NM</t>
+  </si>
+  <si>
+    <t>$14.71 per hour</t>
+  </si>
+  <si>
+    <t>general-stewardship-outdoor-recreation</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-park-attendant-albuquerque-new-mexico/3189374522</t>
+  </si>
+  <si>
+    <t>Private Lands Biologist</t>
+  </si>
+  <si>
+    <t>University of Georgia - REMOTE</t>
+  </si>
+  <si>
+    <t>Buena Vista, GA</t>
+  </si>
+  <si>
+    <t>$48,000 - $53,060 per year</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-private-lands-biologist-buena-vista-georgia/7904100858</t>
+  </si>
+  <si>
+    <t>Regional Program Manager</t>
+  </si>
+  <si>
+    <t>Montana Conservation Corps</t>
+  </si>
+  <si>
+    <t>Helena, MT</t>
+  </si>
+  <si>
+    <t>$55,120 per year</t>
+  </si>
+  <si>
+    <t>admin-leadership-general-stewardship</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-regional-program-manager-helena-montana/9299663823</t>
+  </si>
+  <si>
+    <t>Restoration, Invasive Species, and Forestry Technician</t>
+  </si>
+  <si>
+    <t>Redstart</t>
+  </si>
+  <si>
+    <t>Corinth, VT</t>
+  </si>
+  <si>
+    <t>$16-18/hour DOE</t>
+  </si>
+  <si>
+    <t>botany-forestry-restoration</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-restoration-invasive-species-and-forestry-technician-corinth-vermont/1713322448</t>
+  </si>
+  <si>
+    <t>River Star Coordinator</t>
+  </si>
+  <si>
+    <t>The Elizabeth River Project</t>
+  </si>
+  <si>
+    <t>Norfolk, VA</t>
+  </si>
+  <si>
+    <t>$23 per hour</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-river-star-coordinator-norfolk-virginia/7598690375</t>
+  </si>
+  <si>
+    <t>Senior Game Warden</t>
+  </si>
+  <si>
+    <t>Wyoming Game &amp; Fish</t>
+  </si>
+  <si>
+    <t>$6,612.67 - $7,347.60 per month</t>
+  </si>
+  <si>
+    <t>outdoor-recreation-wildlife</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-senior-game-warden-cheyenne-wyoming/3290822727</t>
+  </si>
+  <si>
+    <t>State Park Manager Supervisor I</t>
+  </si>
+  <si>
+    <t>Independence, KS</t>
+  </si>
+  <si>
+    <t>$33.10 - $33.93 per hour</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-state-park-manager-supervisor-i-independence-kansas/5727550562</t>
+  </si>
+  <si>
+    <t>Summer Research Fellow</t>
+  </si>
+  <si>
+    <t>Edmund Niles Huyck Preserve, Inc.</t>
+  </si>
+  <si>
+    <t>Rensselaerville, NY</t>
+  </si>
+  <si>
+    <t>$10,000</t>
+  </si>
+  <si>
+    <t>ecology-land-trust-environmental-education</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-summer-research-fellow-rensselaerville-new-york/3385511501</t>
+  </si>
+  <si>
+    <t>USDA-ARS Perennial Ryegrass Abiotic Stress Genetics Postdoctoral Fellowship</t>
+  </si>
+  <si>
+    <t>USDA-ARS-PWA-2026-0377</t>
+  </si>
+  <si>
+    <t>Corvallis, OR</t>
+  </si>
+  <si>
+    <t>Faculty / Postdoc</t>
+  </si>
+  <si>
+    <t>Stipend $6,928.92 Monthly</t>
+  </si>
+  <si>
+    <t>botany-ecology</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-usda-ars-perennial-ryegrass-abiotic-stress-genetics-postdoctoral-fellowship-corvallis-oregon/8805725987</t>
+  </si>
+  <si>
+    <t>Vice President of Conservation</t>
+  </si>
+  <si>
+    <t>Heritage Conservancy</t>
+  </si>
+  <si>
+    <t>Doylestown, PA</t>
+  </si>
+  <si>
+    <t>$120,000 - $140,000 per year</t>
+  </si>
+  <si>
+    <t>admin-leadership-general-stewardship-land-trust</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-vice-president-of-conservation-doylestown-pennsylvania/2851595241</t>
+  </si>
+  <si>
+    <t>Visitor Services Information Assistant</t>
+  </si>
+  <si>
+    <t>U.S. Forest Service- White Mountain National Forest</t>
+  </si>
+  <si>
+    <t>Campton &amp; Gorham, NH</t>
+  </si>
+  <si>
+    <t>$19.52 per hour</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-visitor-services-information-assistant-campton--gorham-new-hampshire/9425216626</t>
+  </si>
+  <si>
+    <t>Wildlife Biologist - Nuisance Wildlife</t>
+  </si>
+  <si>
+    <t>Wildernex LLC Wildlife Control</t>
+  </si>
+  <si>
+    <t>San Antonio, TX</t>
+  </si>
+  <si>
+    <t>$45,000 - $85,000 per year</t>
+  </si>
+  <si>
+    <t>wildlife</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-wildlife-biologist---nuisance-wildlife-san-antonio-texas/1827047792</t>
+  </si>
+  <si>
+    <t>Wildlife Conflict Mitigation Biologist</t>
+  </si>
+  <si>
+    <t>Florida Fish and Wildlife Conservation Commission</t>
+  </si>
+  <si>
+    <t>Panama City, FL</t>
+  </si>
+  <si>
+    <t>$23.44 per hour</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-wildlife-conflict-mitigation-biologist-panama-city-florida/4179285578</t>
+  </si>
+  <si>
+    <t>Wildlife Veterinarian</t>
+  </si>
+  <si>
+    <t>Rainforest Awareness Rescue Education Center - RAREC</t>
+  </si>
+  <si>
+    <t>Iquitos, Lima, Peru, Latin America</t>
+  </si>
+  <si>
+    <t>US$ 500 per month + bonuses</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-wildlife-veterinarian-iquitos-latin-america/7205926291</t>
+  </si>
+  <si>
+    <t>Zero Waste Advocate</t>
+  </si>
+  <si>
+    <t>PIRG</t>
+  </si>
+  <si>
+    <t>Denver, CO</t>
+  </si>
+  <si>
+    <t>The starting target annual compensation range for someone with 2-5 years of relevant experience is $41,750-$46,000 in the first year</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-zero-waste-advocate-denver-colorado/8275591678</t>
+  </si>
+  <si>
+    <t>Account Executive, Earned Media</t>
+  </si>
+  <si>
+    <t>WeAreRally, LLC</t>
+  </si>
+  <si>
+    <t>Los Angeles, California</t>
+  </si>
+  <si>
+    <t>Full Time</t>
+  </si>
+  <si>
+    <t>USD 32.00 - 34.00/hour</t>
+  </si>
+  <si>
+    <t>Climate Change, Education, Housing Homelessness</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/consultant-job/47eade9c89304c00b5195fc57ab87a18-account-executive-earned-media-wearerally-llc-los-angeles</t>
+  </si>
+  <si>
+    <t>Accounting Associate - Finance</t>
+  </si>
+  <si>
+    <t>Community Economic Development Assistance Corp. (CEDAC)</t>
+  </si>
+  <si>
+    <t>Boston, Massachusetts</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Community Development, Economic Development, Housing Homelessness</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/8b88e4b0a24b40aeafce0caf5bc349ab-accounting-associate-finance-community-economic-development-assistance-corp-cedac-boston</t>
+  </si>
+  <si>
+    <t>Advocate Supervisor</t>
+  </si>
+  <si>
+    <t>Family Law CASA of King County</t>
+  </si>
+  <si>
+    <t>Tukwila, Washington</t>
+  </si>
+  <si>
+    <t>USD 74000.00 - 76000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Family, Legal Assistance</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/a5677a8ac20c4a7890c2377fb6ccf450-advocate-supervisor-family-law-casa-of-king-county-tukwila</t>
+  </si>
+  <si>
+    <t>Affordable Housing Manager</t>
+  </si>
+  <si>
+    <t>Community Grants, Planning &amp; Housing, LLC</t>
+  </si>
+  <si>
+    <t>Cranbury, NJ</t>
+  </si>
+  <si>
+    <t>USD 68000.00 - 75000.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Economic Development, Urban Areas</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/consultant-job/82251a41c7164f68aa3e429ccdcfa8b7-affordable-housing-manager-community-grants-planning-housing-llc-cranbury</t>
+  </si>
+  <si>
+    <t>Analista de Relacionamento com Doadores</t>
+  </si>
+  <si>
+    <t>Instituto Semear</t>
+  </si>
+  <si>
+    <t>Remote (BR)</t>
+  </si>
+  <si>
+    <t>Contract</t>
+  </si>
+  <si>
+    <t>Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/34f65013c6b140a5b4d2bb530ee11f48-analista-de-relacionamento-com-doadores-instituto-semear-sao-paulo</t>
+  </si>
+  <si>
+    <t>Assistant Director of Development, Outreach, and Faith Community Engagement</t>
+  </si>
+  <si>
+    <t>TSNE</t>
+  </si>
+  <si>
+    <t>USD 84000.00 - 87000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/0f0ce784084a4eccb905bb5163f44bd2-assistant-director-of-development-outreach-and-faith-community-engagement-tsne-boston</t>
+  </si>
+  <si>
+    <t>Associate or Senior Associate, Strategic Communications</t>
+  </si>
+  <si>
+    <t>Be Clear</t>
+  </si>
+  <si>
+    <t>Remote</t>
+  </si>
+  <si>
+    <t>USD 60000.00 - 95000.00/year</t>
+  </si>
+  <si>
+    <t>Economic Development, Education, Human Rights Civil Liberties</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/consultant-job/37fe68cfd72d4c04a97c62b061bfe528-associate-or-senior-associate-strategic-communications-be-clear-edgewater</t>
+  </si>
+  <si>
+    <t>Attorney - Immigration Law</t>
+  </si>
+  <si>
+    <t>Building Service 32BJ Benefit Funds</t>
+  </si>
+  <si>
+    <t>New York, New York</t>
+  </si>
+  <si>
+    <t>USD 90854.87 - 140000.00/year</t>
+  </si>
+  <si>
+    <t>Immigrants Or Refugees, Civic Engagement</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/24670d7ab54948e7aba0fbe1bc2de85b-attorney-immigration-law-building-service-32bj-benefit-funds-new-york</t>
+  </si>
+  <si>
+    <t>Attorney - Matrimonial Law</t>
+  </si>
+  <si>
+    <t>Family</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/b8e309e703944c748d284cbb3c56e826-attorney-matrimonial-law-building-service-32bj-benefit-funds-new-york</t>
+  </si>
+  <si>
+    <t>California Organizing Manager</t>
+  </si>
+  <si>
+    <t>Mothers Against Media Addiction (MAMA)</t>
+  </si>
+  <si>
+    <t>Remote (California)</t>
+  </si>
+  <si>
+    <t>Full Time, Temporary</t>
+  </si>
+  <si>
+    <t>USD 80000.00 - 90000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Consumer Protection, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/23227b8488824ebd91e5c846e717963d-california-organizing-manager-mothers-against-media-addiction-mama-new-york</t>
+  </si>
+  <si>
+    <t>Captadores/as de Fondos en vía pública para Ingeniería Sin Fronteras Argentina -CABA - Turno Mañana</t>
+  </si>
+  <si>
+    <t>Ingeniería Sin Fronteras Argentina</t>
+  </si>
+  <si>
+    <t>Buenos Aires, Ciudad Autónoma de Buenos Aires, AR</t>
+  </si>
+  <si>
+    <t>Children Youth, Community Development, Science Technology</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/0746d9506c5848d989e226b75766236a-captadoresas-de-fondos-en-via-publica-para-ingenieria-sin-fronteras-argentina-caba-turno-manana-ingenieria-sin-fronteras-argentina-buenos-aires</t>
+  </si>
+  <si>
+    <t>Case Manager / Aftercare Associate</t>
+  </si>
+  <si>
+    <t>ACE (Association of Community Employment Programs for the Homeless, Inc.)</t>
+  </si>
+  <si>
+    <t>Queens County, New York</t>
+  </si>
+  <si>
+    <t>USD 64000.00 - 67000.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Housing Homelessness, Job Workplace</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/c64536091596494aaae6e5f060de472a-case-manager-aftercare-associate-ace-association-of-community-employment-programs-for-the-homeless-inc-queens-county</t>
+  </si>
+  <si>
+    <t>Chief Development Officer</t>
+  </si>
+  <si>
+    <t>Harlem Grown</t>
+  </si>
+  <si>
+    <t>USD 130000.00 - 165000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Civic Engagement, Community Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/db427b7ac0304aa8911e3396940c1953-chief-development-officer-harlem-grown-new-york</t>
+  </si>
+  <si>
+    <t>City Cohort Lead - Detroit, MI</t>
+  </si>
+  <si>
+    <t>Civic Nation</t>
+  </si>
+  <si>
+    <t>Remote (Michigan)</t>
+  </si>
+  <si>
+    <t>Part Time, Temporary</t>
+  </si>
+  <si>
+    <t>USD 115.00 - 115.00/hour</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Education, Women</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/de1e2a549d874f1eab2468dce77650ae-city-cohort-lead-detroit-mi-civic-nation-washington</t>
+  </si>
+  <si>
+    <t>City Cohort Lead - Memphis, TN</t>
+  </si>
+  <si>
+    <t>Remote (Tennessee)</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/17a3ec29ca00408ab74fa0d32152500d-city-cohort-lead-memphis-tn-civic-nation-washington</t>
+  </si>
+  <si>
+    <t>City Cohort Lead - San Antonio, TX</t>
+  </si>
+  <si>
+    <t>Remote (Texas)</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/0eb109112bc44bf0ac220f2d10bb3892-city-cohort-lead-san-antonio-tx-civic-nation-washington</t>
+  </si>
+  <si>
+    <t>Classroom Facilitator</t>
+  </si>
+  <si>
+    <t>Project Success</t>
+  </si>
+  <si>
+    <t>Mankato, Minnesota</t>
+  </si>
+  <si>
+    <t>USD 50000.00 - 55000.00/year</t>
+  </si>
+  <si>
+    <t>Arts Music, Children Youth, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/5b80bd870871445e88db3e7f0758cd08-classroom-facilitator-project-success-mankato</t>
+  </si>
+  <si>
+    <t>Clean Transportation Team Position (multi-levels)</t>
+  </si>
+  <si>
+    <t>NESCAUM</t>
+  </si>
+  <si>
+    <t>USD 70000.00 - 118000.00/year</t>
+  </si>
+  <si>
+    <t>Energy, Environment, Policy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/d15444434e2843ca9b6afa79b0e59730-clean-transportation-team-position-multi-levels-nescaum-boston</t>
+  </si>
+  <si>
+    <t>Communications and Marketing Manager</t>
+  </si>
+  <si>
+    <t>National Academy of Elder Law Attorneys</t>
+  </si>
+  <si>
+    <t>Vienna, VA</t>
+  </si>
+  <si>
+    <t>USD 65000.00 - 80000.00/year</t>
+  </si>
+  <si>
+    <t>Legal Assistance, Seniors Retirement, Consumer Protection</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/4c1ee867c3764d1991d50178d010c312-communications-and-marketing-manager-national-academy-of-elder-law-attorneys-vienna</t>
+  </si>
+  <si>
+    <t>Communications Manager</t>
+  </si>
+  <si>
+    <t>Evitable</t>
+  </si>
+  <si>
+    <t>San Francisco, California</t>
+  </si>
+  <si>
+    <t>USD 85000.00 - 130000.00/year</t>
+  </si>
+  <si>
+    <t>Science Technology, Transparency Oversight, Consumer Protection</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/277c1a5f6b9747e19e1c7327f83a1c54-communications-manager-evitable-san-francisco</t>
+  </si>
+  <si>
+    <t>Communications Manager at the First Parish in Lincoln</t>
+  </si>
+  <si>
+    <t>First Parish in Lincoln</t>
+  </si>
+  <si>
+    <t>Lincoln, MA</t>
+  </si>
+  <si>
+    <t>Part Time</t>
+  </si>
+  <si>
+    <t>USD 32000.00 - 35000.00/year</t>
+  </si>
+  <si>
+    <t>Education, Family, Religion Spirituality</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/65f2d9c6392e498694b7928413df9e44-communications-manager-at-the-first-parish-in-lincoln-first-parish-in-lincoln-lincoln</t>
+  </si>
+  <si>
+    <t>Community Health Worker</t>
+  </si>
+  <si>
+    <t>Lighthouse Foundation of Chicagoland</t>
+  </si>
+  <si>
+    <t>Chicago, Illinois</t>
+  </si>
+  <si>
+    <t>USD 30.00 - 30.00/hour</t>
+  </si>
+  <si>
+    <t>Arts Music, Community Development, Job Workplace</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/1e089ebf7d4545a39d7c635c69fcf4ad-community-health-worker-lighthouse-foundation-of-chicagoland-chicago</t>
+  </si>
+  <si>
+    <t>Conference Operations Coordinator</t>
+  </si>
+  <si>
+    <t>WSCPA</t>
+  </si>
+  <si>
+    <t>Bellevue, Washington</t>
+  </si>
+  <si>
+    <t>USD 27.00 - 30.00/hour</t>
+  </si>
+  <si>
+    <t>Education, Financial Literacy Personal Finance, Community Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/458f80d58edf4b92983e23a9ab852c88-conference-operations-coordinator-wscpa-bellevue</t>
+  </si>
+  <si>
+    <t>Congressional Leadership Academy Manager</t>
+  </si>
+  <si>
+    <t>National Foster Youth Institute</t>
+  </si>
+  <si>
+    <t>USD 70000.00 - 70000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Family, Poverty</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/f22a0db191294b658980f107cfaf4cdb-congressional-leadership-academy-manager-national-foster-youth-institute-washington</t>
+  </si>
+  <si>
+    <t>Conservation Program Mananger</t>
+  </si>
+  <si>
+    <t>Rocky Mountain Youth Corps (Taos, New Mexico)</t>
+  </si>
+  <si>
+    <t>Taos, New Mexico</t>
+  </si>
+  <si>
+    <t>USD 47840.00 - 54080.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Environment, Job Workplace</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/567cc635b3c74eaa8b542dc4bfee0eb0-conservation-program-mananger-rocky-mountain-youth-corps-taos-new-mexico-taos</t>
+  </si>
+  <si>
+    <t>Coordinator, Community Services</t>
+  </si>
+  <si>
+    <t>Federation for Children with Special Needs</t>
+  </si>
+  <si>
+    <t>USD 48500.00 - 58500.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Family</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/de8be26d21c64c3590b9891f196a5c1a-coordinator-community-services-federation-for-children-with-special-needs-boston</t>
+  </si>
+  <si>
+    <t>Coordinator, Food Recovery Program</t>
+  </si>
+  <si>
+    <t>Spoonfuls</t>
+  </si>
+  <si>
+    <t>Newton, Massachusetts</t>
+  </si>
+  <si>
+    <t>USD 25.00 - 25.00/hour</t>
+  </si>
+  <si>
+    <t>Environment, Hunger Food Security, Poverty</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/582727bd220446ebbc3b97c9a005e0ca-coordinator-food-recovery-program-spoonfuls-newton</t>
+  </si>
+  <si>
+    <t>Curriculum and Materials Development Specialist</t>
+  </si>
+  <si>
+    <t>CAI</t>
+  </si>
+  <si>
+    <t>Education, Health Medicine, Mental Health</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/6cac696a129a424db945082f8dd6edd3-curriculum-and-materials-development-specialist-cai-new-york</t>
+  </si>
+  <si>
+    <t>Data Analyst II</t>
+  </si>
+  <si>
+    <t>Education Analytics</t>
+  </si>
+  <si>
+    <t>Madison, Wisconsin</t>
+  </si>
+  <si>
+    <t>USD 72000.00 - 84000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/bb26e390ef6e4b4f99e29474b1301c96-data-analyst-ii-education-analytics-madison</t>
+  </si>
+  <si>
+    <t>Data Analyst II-Business Analyst Focus</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/a6c86418aec54052a317bd035a808b80-data-analyst-ii-business-analyst-focus-education-analytics-madison</t>
+  </si>
+  <si>
+    <t>Data Analyst, Fundraising</t>
+  </si>
+  <si>
+    <t>UJA-Federation of New York</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/4b0913be3719464fac36d89414dab35e-data-analyst-fundraising-uja-federation-of-new-york-new-york</t>
+  </si>
+  <si>
+    <t>Database and Development Lead</t>
+  </si>
+  <si>
+    <t>ALL STARS PROJECT INC.</t>
+  </si>
+  <si>
+    <t>USD 55000.00 - 60000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/a863742ea9284a0b877fdeece9771038-database-and-development-lead-all-stars-project-inc-new-york</t>
+  </si>
+  <si>
+    <t>Development and Communications Manager</t>
+  </si>
+  <si>
+    <t>Philly Community Wireless</t>
+  </si>
+  <si>
+    <t>Philadelphia, Pennsylvania</t>
+  </si>
+  <si>
+    <t>USD 52000.00 - 52000.00/year</t>
+  </si>
+  <si>
+    <t>Communications Access, Community Development, Economic Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/6651e8e5f8314abfa745efdd0e54a234-development-and-communications-manager-philly-community-wireless-philadelphia</t>
+  </si>
+  <si>
+    <t>Development Associate</t>
+  </si>
+  <si>
+    <t>Civic Joy Fund</t>
+  </si>
+  <si>
+    <t>USD 30.00 - 35.00/hour</t>
+  </si>
+  <si>
+    <t>Arts Music, Civic Engagement, Community Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/de9a92e18200406bb266b120ba46e7aa-development-associate-civic-joy-fund-san-francisco</t>
+  </si>
+  <si>
+    <t>Home for a Home</t>
+  </si>
+  <si>
+    <t>USD 35.00 - 45.00/hour</t>
+  </si>
+  <si>
+    <t>Community Development, Economic Development, Family</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/43c487de6b40457fb7435c7cc8e3bcbb-development-associate-home-for-a-home-palm-springs</t>
+  </si>
+  <si>
+    <t>Development Coordinator/Manager</t>
+  </si>
+  <si>
+    <t>USD 55000.00 - 73000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/4eda206684404810a7c31b853a923fbd-development-coordinatormanager-harlem-grown-new-york</t>
+  </si>
+  <si>
+    <t>Development Director</t>
+  </si>
+  <si>
+    <t>The Family Hope Foundation</t>
+  </si>
+  <si>
+    <t>USD 35000.00 - 45000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Disability, Family</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/205bb03e16274c2ea386a3395286d126-development-director-the-family-hope-foundation-grand-rapids</t>
+  </si>
+  <si>
+    <t>Development Manager</t>
+  </si>
+  <si>
+    <t>Global Learning Exchange Initiative</t>
+  </si>
+  <si>
+    <t>Antigua Guatemala, Sacatepéquez Department, GT</t>
+  </si>
+  <si>
+    <t>USD 1200.00 - 1500.00/month</t>
+  </si>
+  <si>
+    <t>Children Youth, Community Development, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/f1feef0ce5954329a0387cf7c94451be-development-manager-global-learning-exchange-initiative-antigua-guatemala</t>
+  </si>
+  <si>
+    <t>Development Officer</t>
+  </si>
+  <si>
+    <t>Connecticut Community Foundation</t>
+  </si>
+  <si>
+    <t>Waterbury, CT</t>
+  </si>
+  <si>
+    <t>USD 78000.00 - 92000.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Financial Literacy Personal Finance, Volunteering</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/a4d320f1e57c450789beefa6cf4bffd6-development-officer-connecticut-community-foundation-waterbury</t>
+  </si>
+  <si>
+    <t>Development Operations Associate</t>
+  </si>
+  <si>
+    <t>Land Together</t>
+  </si>
+  <si>
+    <t>USD 58000.00 - 68000.00/year</t>
+  </si>
+  <si>
+    <t>Crime Safety, Environment, Prison Reform</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/b4a6498f6611421b8835a28889310b49-development-operations-associate-land-together-sacramento</t>
+  </si>
+  <si>
+    <t>Director of Admissions and Marketing</t>
+  </si>
+  <si>
+    <t>May Center for Learning</t>
+  </si>
+  <si>
+    <t>Santa Fe, New Mexico</t>
+  </si>
+  <si>
+    <t>USD 76000.00 - 80000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/acbbe76090e443ec8613e2fe29dab202-director-of-admissions-and-marketing-may-center-for-learning-santa-fe</t>
+  </si>
+  <si>
+    <t>Director of Community Organizing</t>
+  </si>
+  <si>
+    <t>USD 140000.00 - 175000.00/year</t>
+  </si>
+  <si>
+    <t>Science Technology, Consumer Protection, Human Rights Civil Liberties</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ec09f46f2b834084a5b78dd75bd45f71-director-of-community-organizing-evitable-san-francisco</t>
+  </si>
+  <si>
+    <t>Director of Development</t>
+  </si>
+  <si>
+    <t>Literations</t>
+  </si>
+  <si>
+    <t>USD 120000.00 - 140000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Education, Seniors Retirement</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/88458c1a8e7a4739b376ac5ab7f0c433-director-of-development-literations-boston</t>
+  </si>
+  <si>
+    <t>Zeiterion Theatre</t>
+  </si>
+  <si>
+    <t>New Bedford, MA</t>
+  </si>
+  <si>
+    <t>USD 70000.00 - 98000.00/year</t>
+  </si>
+  <si>
+    <t>Arts Music, Sports Recreation</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/a98074db332e4f9c8fdf3e36da48aa89-director-of-development-zeiterion-theatre-new-bedford</t>
+  </si>
+  <si>
+    <t>USD 130000.00 - 140000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/7f9e4a7ef09142f0900ebc56ef964e8e-director-of-development-mothers-against-media-addiction-mama-new-york</t>
+  </si>
+  <si>
+    <t>Director of Finance</t>
+  </si>
+  <si>
+    <t>DreamYard Project</t>
+  </si>
+  <si>
+    <t>Bronx County, New York</t>
+  </si>
+  <si>
+    <t>USD 125000.00 - 140000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/200ffe111ff74aab89e8d3452bae3d7c-director-of-finance-dreamyard-project-bronx-county</t>
+  </si>
+  <si>
+    <t>Director of Industry Relations</t>
+  </si>
+  <si>
+    <t>U.S. Wheat Associates</t>
+  </si>
+  <si>
+    <t>Portland, Oregon</t>
+  </si>
+  <si>
+    <t>Agriculture, Community Development, Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/1a4c7450b7af4f91bd58ed39fb6fcbda-director-of-industry-relations-us-wheat-associates-portland</t>
+  </si>
+  <si>
+    <t>Director of Mediation</t>
+  </si>
+  <si>
+    <t>Office of the Massachusetts Attorney General</t>
+  </si>
+  <si>
+    <t>USD 96000.00 - 106000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/government-job/cb504f66a4f4477f8092f564ed9fe895-director-of-mediation-office-of-the-massachusetts-attorney-general-boston</t>
+  </si>
+  <si>
+    <t>Director of Programs</t>
+  </si>
+  <si>
+    <t>Weeksville Heritage Center</t>
+  </si>
+  <si>
+    <t>Brooklyn, New York</t>
+  </si>
+  <si>
+    <t>USD 100000.00 - 120000.00/year</t>
+  </si>
+  <si>
+    <t>Arts Music, Education, Family</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/73af2bd4af14468aa4cc423ea690b0bb-director-of-programs-weeksville-heritage-center-brooklyn</t>
+  </si>
+  <si>
+    <t>Director of Programs &amp; Impact</t>
+  </si>
+  <si>
+    <t>USD 85000.00 - 85000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/d6a04b90261b41d5a52f351dfccd9c97-director-of-programs-impact-national-foster-youth-institute-los-angeles</t>
+  </si>
+  <si>
+    <t>Director, Legal Policy (or Senior Director, commensurate with experience)</t>
+  </si>
+  <si>
+    <t>Human Rights Campaign</t>
+  </si>
+  <si>
+    <t>Washington, District of Columbia</t>
+  </si>
+  <si>
+    <t>USD 159000.00 - 199000.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Human Rights Civil Liberties, Lgbtq</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ea66a8ab3135478d86a68a8c80458489-director-legal-policy-or-senior-director-commensurate-with-experience-human-rights-campaign-washington</t>
+  </si>
+  <si>
+    <t>Director, Multicultural Ministries - Catholic Diocese of Arlington</t>
+  </si>
+  <si>
+    <t>Catholic Diocese of Arlington</t>
+  </si>
+  <si>
+    <t>Annandale, Virginia</t>
+  </si>
+  <si>
+    <t>USD 78000.00 - 90000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/31981b0428194671ad3e745bb185f24b-director-multicultural-ministries-catholic-diocese-of-arlington-catholic-diocese-of-arlington-annandale</t>
+  </si>
+  <si>
+    <t>Education Manager, JA Innovation Center @ Lawrence High School</t>
+  </si>
+  <si>
+    <t>Junior Achievement of Greater Boston</t>
+  </si>
+  <si>
+    <t>Lawrence, Massachusetts</t>
+  </si>
+  <si>
+    <t>USD 60000.00 - 70000.00/year</t>
+  </si>
+  <si>
+    <t>Education, Entrepreneurship</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/a57df8a5235649268a6cc201492f060b-education-manager-ja-innovation-center-lawrence-high-school-junior-achievement-of-greater-boston-lawrence</t>
+  </si>
+  <si>
+    <t>Executive Assistant and Operations Manager</t>
+  </si>
+  <si>
+    <t>National Cancer Registrars Association</t>
+  </si>
+  <si>
+    <t>Alexandria, Virginia</t>
+  </si>
+  <si>
+    <t>Health Medicine</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/9dc8db3ac46e4344b6b8730cdb90f005-executive-assistant-and-operations-manager-national-cancer-registrars-association-alexandria</t>
+  </si>
+  <si>
+    <t>Institute for Humane Education</t>
+  </si>
+  <si>
+    <t>USD 85000.00 - 100000.00/year</t>
+  </si>
+  <si>
+    <t>Education, Environment, Human Rights Civil Liberties</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/54c60a0f616a4bff98151c57a3220d9c-executive-director-institute-for-humane-education-surry</t>
+  </si>
+  <si>
+    <t>Breaking Free</t>
+  </si>
+  <si>
+    <t>Remote (Minnesota)</t>
+  </si>
+  <si>
+    <t>USD 95000.00 - 125000.00/year</t>
+  </si>
+  <si>
+    <t>Housing Homelessness, Human Rights Civil Liberties, Legal Assistance</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/fb0e4580e2054121a61038cc74ffed8a-executive-director-breaking-free-saint-paul</t>
+  </si>
+  <si>
+    <t>Executive Director Saco Main Street</t>
+  </si>
+  <si>
+    <t>Saco Main Street</t>
+  </si>
+  <si>
+    <t>Saco, Maine</t>
+  </si>
+  <si>
+    <t>USD 49920.00 - 59904.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/c8506140b4d44ea8bd0b6d983ea0236d-executive-director-saco-main-street-saco-main-street-saco</t>
+  </si>
+  <si>
+    <t>Financial Counselor</t>
+  </si>
+  <si>
+    <t>New York Legal Assistance Group (NYLAG)</t>
+  </si>
+  <si>
+    <t>USD 73718.00 - 77743.00/year</t>
+  </si>
+  <si>
+    <t>Legal Assistance</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/27fbe6f22dbe4561912296690d426fdb-financial-counselor-new-york-legal-assistance-group-nylag-new-york</t>
+  </si>
+  <si>
+    <t>Fractional Program Director</t>
+  </si>
+  <si>
+    <t>Fencing in the Park Inc.</t>
+  </si>
+  <si>
+    <t>Kings County, New York</t>
+  </si>
+  <si>
+    <t>USD 50000.00 - 58000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/dc6e62cf52dd40a19d09053ace2c0364-fractional-program-director-fencing-in-the-park-inc-kings-county</t>
+  </si>
+  <si>
+    <t>Grant Manager, Trusts and Foundations</t>
+  </si>
+  <si>
+    <t>MSI US</t>
+  </si>
+  <si>
+    <t>Family, Health Medicine, Reproductive Health Rights</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/c38b9f35614f487d939e966a47a5844f-grant-manager-trusts-and-foundations-msi-us-washington</t>
+  </si>
+  <si>
+    <t>Housing Specialist</t>
+  </si>
+  <si>
+    <t>Urban Pathways</t>
+  </si>
+  <si>
+    <t>USD 49863.51 - 67315.74/year</t>
+  </si>
+  <si>
+    <t>Housing Homelessness</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ecbe5e400427451bae21fa4b0d6b764b-housing-specialist-urban-pathways-new-york</t>
+  </si>
+  <si>
+    <t>HR Manager</t>
+  </si>
+  <si>
+    <t>National Black Theatre</t>
+  </si>
+  <si>
+    <t>USD 75000.00 - 80000.00/year</t>
+  </si>
+  <si>
+    <t>Arts Music, Entrepreneurship, Race Ethnicity</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/071e9d4187d34325b6d67fc4082a9682-hr-manager-national-black-theatre-new-york</t>
+  </si>
+  <si>
+    <t>IMMIGRATION LAW ATTORNEY CWJC (Springfield)</t>
+  </si>
+  <si>
+    <t>Community Legal Aid &amp; Affiliate</t>
+  </si>
+  <si>
+    <t>Springfield, Massachusetts</t>
+  </si>
+  <si>
+    <t>USD 73000.00 - 109000.00/year</t>
+  </si>
+  <si>
+    <t>Legal Assistance, Poverty</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/3733809c50bc44a6862035fa29b060d7-immigration-law-attorney-cwjc-springfield-community-legal-aid-affiliate-springfield</t>
+  </si>
+  <si>
+    <t>Iowa Canvasser</t>
+  </si>
+  <si>
+    <t>Food &amp; Water Watch</t>
+  </si>
+  <si>
+    <t>Des Moines, Iowa</t>
+  </si>
+  <si>
+    <t>Agriculture, Consumer Protection, Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/5aee486673a94bfca521ad840e78b36d-iowa-canvasser-food-water-watch-des-moines</t>
+  </si>
+  <si>
+    <t>IT Manager</t>
+  </si>
+  <si>
+    <t>USD 85000.00 - 90000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/bc664caa5b5746519d0a6d9654bef1ac-it-manager-all-stars-project-inc-new-york</t>
+  </si>
+  <si>
+    <t>Licensed Mental Health Clinician</t>
+  </si>
+  <si>
+    <t>Center for Living and Learning</t>
+  </si>
+  <si>
+    <t>Van Nuys, California</t>
+  </si>
+  <si>
+    <t>USD 86000.00 - 100000.00/year</t>
+  </si>
+  <si>
+    <t>Housing Homelessness, Mental Health</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/825157ea75404313a91289bf5b997310-licensed-mental-health-clinician-center-for-living-and-learning-van-nuys</t>
+  </si>
+  <si>
+    <t>Manager of Communications</t>
+  </si>
+  <si>
+    <t>USD 60000.00 - 60000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/44ac044dc507443c96ec0d2f581bfd3b-manager-of-communications-lighthouse-foundation-of-chicagoland-chicago</t>
+  </si>
+  <si>
+    <t>Manager of Communications and Marketing</t>
+  </si>
+  <si>
+    <t>Washington State Dental Association</t>
+  </si>
+  <si>
+    <t>Seattle, Washington</t>
+  </si>
+  <si>
+    <t>USD 75000.00 - 90000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/d65e6c73dcac4816acfdd874c81af7db-manager-of-communications-and-marketing-washington-state-dental-association-seattle</t>
+  </si>
+  <si>
+    <t>Manager of Violence Prevention Programs</t>
+  </si>
+  <si>
+    <t>Worcester Youth Center, Inc.</t>
+  </si>
+  <si>
+    <t>Worcester, Massachusetts</t>
+  </si>
+  <si>
+    <t>USD 68000.00 - 72000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Civic Engagement, Mental Health</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/5678c0766c9547669d8f90e7bd9c0e64-manager-of-violence-prevention-programs-worcester-youth-center-inc-worcester</t>
+  </si>
+  <si>
+    <t>Manager, New Cities, What Works Cities</t>
+  </si>
+  <si>
+    <t>Results for America</t>
+  </si>
+  <si>
+    <t>USD 84023.00 - 95693.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Philanthropy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/40e579a7313046afa0acb7b0436406dc-manager-new-cities-what-works-cities-results-for-america-washington</t>
+  </si>
+  <si>
+    <t>Managing Director, 530A Initiatives</t>
+  </si>
+  <si>
+    <t>NYC Kids RISE</t>
+  </si>
+  <si>
+    <t>Long Island City, New York</t>
+  </si>
+  <si>
+    <t>USD 147800.00 - 182100.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Community Development, Economic Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/0b4f7951e59a43d4b0fe9f568d84f0d7-managing-director-530a-initiatives-nyc-kids-rise-long-island-city</t>
+  </si>
+  <si>
+    <t>Member Engagement Coordinator</t>
+  </si>
+  <si>
+    <t>American Society of Clinical Oncology</t>
+  </si>
+  <si>
+    <t>USD 29.79 - 39.18/year</t>
+  </si>
+  <si>
+    <t>Education, Health Medicine, Research Social Science</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/7301460ffbf44aa7964ddf3aa2eb4654-member-engagement-coordinator-american-society-of-clinical-oncology-alexandria</t>
+  </si>
+  <si>
+    <t>Membership Recruitment Specialist</t>
+  </si>
+  <si>
+    <t>Girl Scout Council of the Nation's Capital</t>
+  </si>
+  <si>
+    <t>Martinsburg, West Virginia</t>
+  </si>
+  <si>
+    <t>USD 52000.00 - 55000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/037644a4583e4e56a096ed5577f3eb9d-membership-recruitment-specialist-girl-scout-council-of-the-nations-capital-martinsburg</t>
+  </si>
+  <si>
+    <t>Membership Services Coordinator</t>
+  </si>
+  <si>
+    <t>Vienna, Virginia</t>
+  </si>
+  <si>
+    <t>USD 50000.00 - 65000.00/year</t>
+  </si>
+  <si>
+    <t>Health Medicine, Legal Assistance, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/12098677e9094c059d936f64ddec8ee1-membership-services-coordinator-national-academy-of-elder-law-attorneys-vienna</t>
+  </si>
+  <si>
+    <t>PAC Coordinator</t>
+  </si>
+  <si>
+    <t>National Rural Letter Carriers Association</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/f2a13f9b0a644830ab7b010aeab5b386-pac-coordinator-national-rural-letter-carriers-association-alexandria</t>
+  </si>
+  <si>
+    <t>Paralegal - Opportunity Under Law</t>
+  </si>
+  <si>
+    <t>Public Counsel</t>
+  </si>
+  <si>
+    <t>Los Angeles, CA</t>
+  </si>
+  <si>
+    <t>USD 60903.12 - 66520.08/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/5b8dfc85bb2e4d729655594a348b2fd6-paralegal-opportunity-under-law-public-counsel-los-angeles</t>
+  </si>
+  <si>
+    <t>Paralegal or Legal Advocate Immigrants Rights</t>
+  </si>
+  <si>
+    <t>Centro Legal de la Raza</t>
+  </si>
+  <si>
+    <t>Oakland, California</t>
+  </si>
+  <si>
+    <t>USD 31.39 - 34.56/hour</t>
+  </si>
+  <si>
+    <t>Immigrants Or Refugees</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/9f5d1659fced4f918847110ccaa4e674-paralegal-or-legal-advocate-immigrants-rights-centro-legal-de-la-raza-oakland</t>
+  </si>
+  <si>
+    <t>Part-time Administrative Assistant</t>
+  </si>
+  <si>
+    <t>Pennsylvania State University - Evidence-to-Impact Collaborative</t>
+  </si>
+  <si>
+    <t>Family, Health Medicine, Research Social Science</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/7848a452845b4b8d8f47d14b343775c2-part-time-administrative-assistant-pennsylvania-state-university-evidence-to-impact-collaborative-state-college</t>
+  </si>
+  <si>
+    <t>Policy Analyst or Senior Policy Analyst - State Programming</t>
+  </si>
+  <si>
+    <t>National Association of Medicaid Directors</t>
+  </si>
+  <si>
+    <t>USD 88000.00 - 120000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/91f920f31f7e4bf2aefec2f65d5abb5f-policy-analyst-or-senior-policy-analyst-state-programming-national-association-of-medicaid-directors-washington</t>
+  </si>
+  <si>
+    <t>Practice Facilitator</t>
+  </si>
+  <si>
+    <t>USD 80000.00 - 95000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/46baf7b3312b4538b5bac1885c7f7933-practice-facilitator-cai-new-york</t>
+  </si>
+  <si>
+    <t>Program Assistant</t>
+  </si>
+  <si>
+    <t>West End House</t>
+  </si>
+  <si>
+    <t>USD 18.00 - 23.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/b5078212a1d04dd793c0771707ca7b44-program-assistant-west-end-house-boston</t>
+  </si>
+  <si>
+    <t>Program Associate, AmeriCorps Workforce Development</t>
+  </si>
+  <si>
+    <t>National Council on Aging</t>
+  </si>
+  <si>
+    <t>Wheeling, West Virginia</t>
+  </si>
+  <si>
+    <t>USD 44000.00 - 50000.00/year</t>
+  </si>
+  <si>
+    <t>Seniors Retirement, Economic Development, Job Workplace</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/a5f58945bb7e4e87910acf8a3af33f92-program-associate-americorps-workforce-development-national-council-on-aging-wheeling</t>
+  </si>
+  <si>
+    <t>Program Coordinator</t>
+  </si>
+  <si>
+    <t>Partnership for After School Education (PASE)</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/2619400d326a4229b68b36a60ef142d9-program-coordinator-partnership-for-after-school-education-pase-new-york</t>
+  </si>
+  <si>
+    <t>Program Instructor</t>
+  </si>
+  <si>
+    <t>Close Up Foundation</t>
+  </si>
+  <si>
+    <t>USD 41592.00 - 41592.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Civic Engagement, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/db34ccdd7c034a5b83b47a9df0569099-program-instructor-close-up-foundation-washington</t>
+  </si>
+  <si>
+    <t>Program Manager</t>
+  </si>
+  <si>
+    <t>USD 65000.00 - 70000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/0b74c12271c8404ea2621e53a5686649-program-manager-weeksville-heritage-center-brooklyn</t>
+  </si>
+  <si>
+    <t>Program Manager II</t>
+  </si>
+  <si>
+    <t>City of Berkeley</t>
+  </si>
+  <si>
+    <t>Berkeley, California</t>
+  </si>
+  <si>
+    <t>USD 152532.43 - 184582.11/year</t>
+  </si>
+  <si>
+    <t>Community Development, Housing Homelessness</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/government-job/dfce5477222346fdb3efa785037b84a2-program-manager-ii-city-of-berkeley-berkeley</t>
+  </si>
+  <si>
+    <t>Projects Specialist</t>
+  </si>
+  <si>
+    <t>Pennsylvania CDFI Network</t>
+  </si>
+  <si>
+    <t>Philadelphia, Pa</t>
+  </si>
+  <si>
+    <t>USD 60000.00/year</t>
+  </si>
+  <si>
+    <t>Economic Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/19bb4b3fdc9145e8978caf71f3ef85d6-projects-specialist-pennsylvania-cdfi-network-philadelphia</t>
+  </si>
+  <si>
+    <t>Resident Ranger &amp; Land Steward</t>
+  </si>
+  <si>
+    <t>Hale Education</t>
+  </si>
+  <si>
+    <t>Westwood, MA</t>
+  </si>
+  <si>
+    <t>USD 17.00 - 19.50/hour</t>
+  </si>
+  <si>
+    <t>Children Youth, Education, Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/dba265bbddec4e589a51e0a9dbb60889-resident-ranger-land-steward-hale-education-westwood</t>
+  </si>
+  <si>
+    <t>Senior Associate, Broadband Initiative</t>
+  </si>
+  <si>
+    <t>Pew Charitable Trusts</t>
+  </si>
+  <si>
+    <t>USD 87200.00 - 97500.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/923ab8043aac414583eeaf0a316450f3-senior-associate-broadband-initiative-pew-charitable-trusts-washington</t>
+  </si>
+  <si>
+    <t>Senior Campaign Director, 530A Initiatives</t>
+  </si>
+  <si>
+    <t>USD 123200.00 - 150900.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/0bc4ce00a98d40098e7ed4cffc307154-senior-campaign-director-530a-initiatives-nyc-kids-rise-long-island-city</t>
+  </si>
+  <si>
+    <t>Senior Coordinator, Resource Development</t>
+  </si>
+  <si>
+    <t>Good360</t>
+  </si>
+  <si>
+    <t>Community Development, Disaster Relief, Economic Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/227492a5f5df41dba072a409ed745055-senior-coordinator-resource-development-good360-alexandria</t>
+  </si>
+  <si>
+    <t>Senior International Student Advisor</t>
+  </si>
+  <si>
+    <t>School of VISUAL ARTS</t>
+  </si>
+  <si>
+    <t>USD 75000.00 - 75000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/fdda36be99164adabbe644a64ec7d9bf-senior-international-student-advisor-school-of-visual-arts-new-york</t>
+  </si>
+  <si>
+    <t>Senior Marketing Manager</t>
+  </si>
+  <si>
+    <t>Woolly Mammoth Theatre Company</t>
+  </si>
+  <si>
+    <t>Arts Music, Civic Engagement, Lgbtq</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/01c5be781d734b778c3bd08c4909a412-senior-marketing-manager-woolly-mammoth-theatre-company-washington</t>
+  </si>
+  <si>
+    <t>Senior Organizer - Suffolk County Regional Office</t>
+  </si>
+  <si>
+    <t>New York Civil Liberties Union Foundation</t>
+  </si>
+  <si>
+    <t>Centereach, New York</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/1d71c541659e451190f06321e601cbd8-senior-organizer-suffolk-county-regional-office-new-york-civil-liberties-union-foundation-centereach</t>
+  </si>
+  <si>
+    <t>Senior Program Director</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/923f3539bf1c4ee1b2726260f4de179e-senior-program-director-partnership-for-after-school-education-pase-new-york</t>
+  </si>
+  <si>
+    <t>Senior Specialist, Building Science &amp; Analysis</t>
+  </si>
+  <si>
+    <t>Institute for Market Transformation</t>
+  </si>
+  <si>
+    <t>USD 100000.00 - 115000.00/year</t>
+  </si>
+  <si>
+    <t>Economic Development, Energy, Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/c33245db486a44f8b0f402e1b5fb52d0-senior-specialist-building-science-analysis-institute-for-market-transformation-washington</t>
+  </si>
+  <si>
+    <t>Staff Attorney - Housing &amp; Habitability</t>
+  </si>
+  <si>
+    <t>Legal Clinic for the Disabled</t>
+  </si>
+  <si>
+    <t>USD 67500.00/year</t>
+  </si>
+  <si>
+    <t>Disability, Health Medicine, Housing Homelessness</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/c5b6877100034774983d59150afa5c6c-staff-attorney-housing-habitability-legal-clinic-for-the-disabled-philadelphia</t>
+  </si>
+  <si>
+    <t>Supervisor of Volunteer Advocates</t>
+  </si>
+  <si>
+    <t>Fairfax Court Appointed Special Advocates (CASA)</t>
+  </si>
+  <si>
+    <t>Fairfax, Virginia</t>
+  </si>
+  <si>
+    <t>USD 60000.00 - 63000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Crime Safety, Family</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/97b2e944244948a9ba87f83dd45ae7ae-supervisor-of-volunteer-advocates-fairfax-court-appointed-special-advocates-casa-fairfax</t>
+  </si>
+  <si>
+    <t>Teach English in Honduras (housing, benefits + stipend provided)</t>
+  </si>
+  <si>
+    <t>One Thousand Schools</t>
+  </si>
+  <si>
+    <t>El Progreso, Yoro Department, HN</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/96c0bc219eee4f64b69b2e12d9b23d60-teach-english-in-honduras-housing-benefits-stipend-provided-one-thousand-schools-el-progreso</t>
+  </si>
+  <si>
+    <t>Youth Services Director</t>
+  </si>
+  <si>
+    <t>Armstrong McGuire &amp; Associates</t>
+  </si>
+  <si>
+    <t>Conover, North Carolina</t>
+  </si>
+  <si>
+    <t>USD 50000.00 - 60000.00/year</t>
+  </si>
+  <si>
+    <t>Arts Music, Education, Health Medicine</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/consultant-job/6ae8cb573514499bb42db318a057ae60-youth-services-director-armstrong-mcguire-associates-conover</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -54,6 +2124,10 @@
     </font>
     <font>
       <b/>
+    </font>
+    <font>
+      <u/>
+      <color rgb="FF1155CC"/>
     </font>
   </fonts>
   <fills count="2">
@@ -76,9 +2150,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -418,7 +2493,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H38"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -457,8 +2532,898 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" t="s">
+        <v>24</v>
+      </c>
+      <c r="F4" t="s">
+        <v>13</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>26</v>
+      </c>
+      <c r="B5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" t="s">
+        <v>27</v>
+      </c>
+      <c r="D5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" t="s">
+        <v>28</v>
+      </c>
+      <c r="F5" t="s">
+        <v>19</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>30</v>
+      </c>
+      <c r="B6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C6" t="s">
+        <v>32</v>
+      </c>
+      <c r="D6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E6" t="s">
+        <v>33</v>
+      </c>
+      <c r="F6" t="s">
+        <v>34</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>36</v>
+      </c>
+      <c r="B7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C7" t="s">
+        <v>32</v>
+      </c>
+      <c r="D7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E7" t="s">
+        <v>37</v>
+      </c>
+      <c r="F7" t="s">
+        <v>38</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>40</v>
+      </c>
+      <c r="B8" t="s">
+        <v>41</v>
+      </c>
+      <c r="C8" t="s">
+        <v>42</v>
+      </c>
+      <c r="D8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E8" t="s">
+        <v>43</v>
+      </c>
+      <c r="F8" t="s">
+        <v>44</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>46</v>
+      </c>
+      <c r="B9" t="s">
+        <v>47</v>
+      </c>
+      <c r="C9" t="s">
+        <v>48</v>
+      </c>
+      <c r="D9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E9" t="s">
+        <v>49</v>
+      </c>
+      <c r="F9" t="s">
+        <v>50</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>52</v>
+      </c>
+      <c r="B10" t="s">
+        <v>53</v>
+      </c>
+      <c r="C10" t="s">
+        <v>54</v>
+      </c>
+      <c r="D10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E10" t="s">
+        <v>55</v>
+      </c>
+      <c r="F10" t="s">
+        <v>19</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>52</v>
+      </c>
+      <c r="B11" t="s">
+        <v>57</v>
+      </c>
+      <c r="C11" t="s">
+        <v>58</v>
+      </c>
+      <c r="D11" t="s">
+        <v>11</v>
+      </c>
+      <c r="E11" t="s">
+        <v>59</v>
+      </c>
+      <c r="F11" t="s">
+        <v>60</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>62</v>
+      </c>
+      <c r="B12" t="s">
+        <v>63</v>
+      </c>
+      <c r="C12" t="s">
+        <v>64</v>
+      </c>
+      <c r="D12" t="s">
+        <v>65</v>
+      </c>
+      <c r="E12" t="s">
+        <v>66</v>
+      </c>
+      <c r="F12" t="s">
+        <v>67</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>69</v>
+      </c>
+      <c r="B13" t="s">
+        <v>70</v>
+      </c>
+      <c r="C13" t="s">
+        <v>71</v>
+      </c>
+      <c r="D13" t="s">
+        <v>11</v>
+      </c>
+      <c r="E13" t="s">
+        <v>72</v>
+      </c>
+      <c r="F13" t="s">
+        <v>38</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>74</v>
+      </c>
+      <c r="B14" t="s">
+        <v>75</v>
+      </c>
+      <c r="C14" t="s">
+        <v>76</v>
+      </c>
+      <c r="D14" t="s">
+        <v>11</v>
+      </c>
+      <c r="E14" t="s">
+        <v>77</v>
+      </c>
+      <c r="F14" t="s">
+        <v>78</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>80</v>
+      </c>
+      <c r="B15" t="s">
+        <v>81</v>
+      </c>
+      <c r="C15" t="s">
+        <v>82</v>
+      </c>
+      <c r="D15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E15" t="s">
+        <v>83</v>
+      </c>
+      <c r="F15" t="s">
+        <v>84</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>86</v>
+      </c>
+      <c r="B16" t="s">
+        <v>87</v>
+      </c>
+      <c r="C16" t="s">
+        <v>88</v>
+      </c>
+      <c r="D16" t="s">
+        <v>11</v>
+      </c>
+      <c r="E16" t="s">
+        <v>89</v>
+      </c>
+      <c r="F16" t="s">
+        <v>90</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>92</v>
+      </c>
+      <c r="B17" t="s">
+        <v>93</v>
+      </c>
+      <c r="C17" t="s">
+        <v>94</v>
+      </c>
+      <c r="D17" t="s">
+        <v>95</v>
+      </c>
+      <c r="E17" t="s">
+        <v>96</v>
+      </c>
+      <c r="F17" t="s">
+        <v>97</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>99</v>
+      </c>
+      <c r="B18" t="s">
+        <v>100</v>
+      </c>
+      <c r="C18" t="s">
+        <v>101</v>
+      </c>
+      <c r="D18" t="s">
+        <v>11</v>
+      </c>
+      <c r="E18" t="s">
+        <v>102</v>
+      </c>
+      <c r="F18" t="s">
+        <v>103</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>105</v>
+      </c>
+      <c r="B19" t="s">
+        <v>106</v>
+      </c>
+      <c r="C19" t="s">
+        <v>107</v>
+      </c>
+      <c r="D19" t="s">
+        <v>11</v>
+      </c>
+      <c r="E19" t="s">
+        <v>108</v>
+      </c>
+      <c r="F19" t="s">
+        <v>109</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>111</v>
+      </c>
+      <c r="B20" t="s">
+        <v>112</v>
+      </c>
+      <c r="C20" t="s">
+        <v>113</v>
+      </c>
+      <c r="D20" t="s">
+        <v>11</v>
+      </c>
+      <c r="E20" t="s">
+        <v>114</v>
+      </c>
+      <c r="F20" t="s">
+        <v>115</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>117</v>
+      </c>
+      <c r="B21" t="s">
+        <v>118</v>
+      </c>
+      <c r="C21" t="s">
+        <v>88</v>
+      </c>
+      <c r="D21" t="s">
+        <v>11</v>
+      </c>
+      <c r="E21" t="s">
+        <v>119</v>
+      </c>
+      <c r="F21" t="s">
+        <v>13</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>117</v>
+      </c>
+      <c r="B22" t="s">
+        <v>118</v>
+      </c>
+      <c r="C22" t="s">
+        <v>88</v>
+      </c>
+      <c r="D22" t="s">
+        <v>11</v>
+      </c>
+      <c r="E22" t="s">
+        <v>119</v>
+      </c>
+      <c r="F22" t="s">
+        <v>13</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>122</v>
+      </c>
+      <c r="B23" t="s">
+        <v>123</v>
+      </c>
+      <c r="C23" t="s">
+        <v>124</v>
+      </c>
+      <c r="D23" t="s">
+        <v>11</v>
+      </c>
+      <c r="E23" t="s">
+        <v>125</v>
+      </c>
+      <c r="F23" t="s">
+        <v>13</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>127</v>
+      </c>
+      <c r="B24" t="s">
+        <v>128</v>
+      </c>
+      <c r="C24" t="s">
+        <v>129</v>
+      </c>
+      <c r="D24" t="s">
+        <v>11</v>
+      </c>
+      <c r="E24" t="s">
+        <v>130</v>
+      </c>
+      <c r="F24" t="s">
+        <v>131</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>133</v>
+      </c>
+      <c r="B25" t="s">
+        <v>134</v>
+      </c>
+      <c r="C25" t="s">
+        <v>135</v>
+      </c>
+      <c r="D25" t="s">
+        <v>11</v>
+      </c>
+      <c r="E25" t="s">
+        <v>136</v>
+      </c>
+      <c r="F25" t="s">
+        <v>115</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>138</v>
+      </c>
+      <c r="B26" t="s">
+        <v>139</v>
+      </c>
+      <c r="C26" t="s">
+        <v>140</v>
+      </c>
+      <c r="D26" t="s">
+        <v>11</v>
+      </c>
+      <c r="E26" t="s">
+        <v>141</v>
+      </c>
+      <c r="F26" t="s">
+        <v>142</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>144</v>
+      </c>
+      <c r="B27" t="s">
+        <v>145</v>
+      </c>
+      <c r="C27" t="s">
+        <v>146</v>
+      </c>
+      <c r="D27" t="s">
+        <v>11</v>
+      </c>
+      <c r="E27" t="s">
+        <v>147</v>
+      </c>
+      <c r="F27" t="s">
+        <v>148</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>150</v>
+      </c>
+      <c r="B28" t="s">
+        <v>151</v>
+      </c>
+      <c r="C28" t="s">
+        <v>152</v>
+      </c>
+      <c r="D28" t="s">
+        <v>11</v>
+      </c>
+      <c r="E28" t="s">
+        <v>153</v>
+      </c>
+      <c r="F28" t="s">
+        <v>13</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>155</v>
+      </c>
+      <c r="B29" t="s">
+        <v>156</v>
+      </c>
+      <c r="C29" t="s">
+        <v>107</v>
+      </c>
+      <c r="D29" t="s">
+        <v>11</v>
+      </c>
+      <c r="E29" t="s">
+        <v>157</v>
+      </c>
+      <c r="F29" t="s">
+        <v>158</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>160</v>
+      </c>
+      <c r="B30" t="s">
+        <v>9</v>
+      </c>
+      <c r="C30" t="s">
+        <v>161</v>
+      </c>
+      <c r="D30" t="s">
+        <v>11</v>
+      </c>
+      <c r="E30" t="s">
+        <v>162</v>
+      </c>
+      <c r="F30" t="s">
+        <v>109</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>164</v>
+      </c>
+      <c r="B31" t="s">
+        <v>165</v>
+      </c>
+      <c r="C31" t="s">
+        <v>166</v>
+      </c>
+      <c r="D31" t="s">
+        <v>65</v>
+      </c>
+      <c r="E31" t="s">
+        <v>167</v>
+      </c>
+      <c r="F31" t="s">
+        <v>168</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>170</v>
+      </c>
+      <c r="B32" t="s">
+        <v>171</v>
+      </c>
+      <c r="C32" t="s">
+        <v>172</v>
+      </c>
+      <c r="D32" t="s">
+        <v>173</v>
+      </c>
+      <c r="E32" t="s">
+        <v>174</v>
+      </c>
+      <c r="F32" t="s">
+        <v>175</v>
+      </c>
+      <c r="H32" s="2" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>177</v>
+      </c>
+      <c r="B33" t="s">
+        <v>178</v>
+      </c>
+      <c r="C33" t="s">
+        <v>179</v>
+      </c>
+      <c r="D33" t="s">
+        <v>11</v>
+      </c>
+      <c r="E33" t="s">
+        <v>180</v>
+      </c>
+      <c r="F33" t="s">
+        <v>181</v>
+      </c>
+      <c r="H33" s="2" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>183</v>
+      </c>
+      <c r="B34" t="s">
+        <v>184</v>
+      </c>
+      <c r="C34" t="s">
+        <v>185</v>
+      </c>
+      <c r="D34" t="s">
+        <v>65</v>
+      </c>
+      <c r="E34" t="s">
+        <v>186</v>
+      </c>
+      <c r="F34" t="s">
+        <v>44</v>
+      </c>
+      <c r="H34" s="2" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>188</v>
+      </c>
+      <c r="B35" t="s">
+        <v>189</v>
+      </c>
+      <c r="C35" t="s">
+        <v>190</v>
+      </c>
+      <c r="D35" t="s">
+        <v>11</v>
+      </c>
+      <c r="E35" t="s">
+        <v>191</v>
+      </c>
+      <c r="F35" t="s">
+        <v>192</v>
+      </c>
+      <c r="H35" s="2" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>194</v>
+      </c>
+      <c r="B36" t="s">
+        <v>195</v>
+      </c>
+      <c r="C36" t="s">
+        <v>196</v>
+      </c>
+      <c r="D36" t="s">
+        <v>11</v>
+      </c>
+      <c r="E36" t="s">
+        <v>197</v>
+      </c>
+      <c r="F36" t="s">
+        <v>192</v>
+      </c>
+      <c r="H36" s="2" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>199</v>
+      </c>
+      <c r="B37" t="s">
+        <v>200</v>
+      </c>
+      <c r="C37" t="s">
+        <v>201</v>
+      </c>
+      <c r="D37" t="s">
+        <v>65</v>
+      </c>
+      <c r="E37" t="s">
+        <v>202</v>
+      </c>
+      <c r="F37" t="s">
+        <v>192</v>
+      </c>
+      <c r="H37" s="2" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>204</v>
+      </c>
+      <c r="B38" t="s">
+        <v>205</v>
+      </c>
+      <c r="C38" t="s">
+        <v>206</v>
+      </c>
+      <c r="D38" t="s">
+        <v>11</v>
+      </c>
+      <c r="E38" t="s">
+        <v>207</v>
+      </c>
+      <c r="F38" t="s">
+        <v>60</v>
+      </c>
+      <c r="H38" s="2" t="s">
+        <v>208</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
+  <hyperlinks>
+    <hyperlink ref="H2" r:id="rId1"/>
+    <hyperlink ref="H3" r:id="rId2"/>
+    <hyperlink ref="H4" r:id="rId3"/>
+    <hyperlink ref="H5" r:id="rId4"/>
+    <hyperlink ref="H6" r:id="rId5"/>
+    <hyperlink ref="H7" r:id="rId6"/>
+    <hyperlink ref="H8" r:id="rId7"/>
+    <hyperlink ref="H9" r:id="rId8"/>
+    <hyperlink ref="H10" r:id="rId9"/>
+    <hyperlink ref="H11" r:id="rId10"/>
+    <hyperlink ref="H12" r:id="rId11"/>
+    <hyperlink ref="H13" r:id="rId12"/>
+    <hyperlink ref="H14" r:id="rId13"/>
+    <hyperlink ref="H15" r:id="rId14"/>
+    <hyperlink ref="H16" r:id="rId15"/>
+    <hyperlink ref="H17" r:id="rId16"/>
+    <hyperlink ref="H18" r:id="rId17"/>
+    <hyperlink ref="H19" r:id="rId18"/>
+    <hyperlink ref="H20" r:id="rId19"/>
+    <hyperlink ref="H21" r:id="rId20"/>
+    <hyperlink ref="H22" r:id="rId21"/>
+    <hyperlink ref="H23" r:id="rId22"/>
+    <hyperlink ref="H24" r:id="rId23"/>
+    <hyperlink ref="H25" r:id="rId24"/>
+    <hyperlink ref="H26" r:id="rId25"/>
+    <hyperlink ref="H27" r:id="rId26"/>
+    <hyperlink ref="H28" r:id="rId27"/>
+    <hyperlink ref="H29" r:id="rId28"/>
+    <hyperlink ref="H30" r:id="rId29"/>
+    <hyperlink ref="H31" r:id="rId30"/>
+    <hyperlink ref="H32" r:id="rId31"/>
+    <hyperlink ref="H33" r:id="rId32"/>
+    <hyperlink ref="H34" r:id="rId33"/>
+    <hyperlink ref="H35" r:id="rId34"/>
+    <hyperlink ref="H36" r:id="rId35"/>
+    <hyperlink ref="H37" r:id="rId36"/>
+    <hyperlink ref="H38" r:id="rId37"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
@@ -514,7 +3479,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H101"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -553,8 +3518,2410 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>209</v>
+      </c>
+      <c r="B2" t="s">
+        <v>210</v>
+      </c>
+      <c r="C2" t="s">
+        <v>211</v>
+      </c>
+      <c r="D2" t="s">
+        <v>212</v>
+      </c>
+      <c r="E2" t="s">
+        <v>213</v>
+      </c>
+      <c r="F2" t="s">
+        <v>214</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>216</v>
+      </c>
+      <c r="B3" t="s">
+        <v>217</v>
+      </c>
+      <c r="C3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D3" t="s">
+        <v>212</v>
+      </c>
+      <c r="E3" t="s">
+        <v>219</v>
+      </c>
+      <c r="F3" t="s">
+        <v>220</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>222</v>
+      </c>
+      <c r="B4" t="s">
+        <v>223</v>
+      </c>
+      <c r="C4" t="s">
+        <v>224</v>
+      </c>
+      <c r="D4" t="s">
+        <v>212</v>
+      </c>
+      <c r="E4" t="s">
+        <v>225</v>
+      </c>
+      <c r="F4" t="s">
+        <v>226</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>228</v>
+      </c>
+      <c r="B5" t="s">
+        <v>229</v>
+      </c>
+      <c r="C5" t="s">
+        <v>230</v>
+      </c>
+      <c r="D5" t="s">
+        <v>212</v>
+      </c>
+      <c r="E5" t="s">
+        <v>231</v>
+      </c>
+      <c r="F5" t="s">
+        <v>232</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>234</v>
+      </c>
+      <c r="B6" t="s">
+        <v>235</v>
+      </c>
+      <c r="C6" t="s">
+        <v>236</v>
+      </c>
+      <c r="D6" t="s">
+        <v>237</v>
+      </c>
+      <c r="E6" t="s">
+        <v>219</v>
+      </c>
+      <c r="F6" t="s">
+        <v>238</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>240</v>
+      </c>
+      <c r="B7" t="s">
+        <v>241</v>
+      </c>
+      <c r="C7" t="s">
+        <v>218</v>
+      </c>
+      <c r="D7" t="s">
+        <v>212</v>
+      </c>
+      <c r="E7" t="s">
+        <v>242</v>
+      </c>
+      <c r="F7" t="s">
+        <v>219</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>244</v>
+      </c>
+      <c r="B8" t="s">
+        <v>245</v>
+      </c>
+      <c r="C8" t="s">
+        <v>246</v>
+      </c>
+      <c r="D8" t="s">
+        <v>212</v>
+      </c>
+      <c r="E8" t="s">
+        <v>247</v>
+      </c>
+      <c r="F8" t="s">
+        <v>248</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>250</v>
+      </c>
+      <c r="B9" t="s">
+        <v>251</v>
+      </c>
+      <c r="C9" t="s">
+        <v>252</v>
+      </c>
+      <c r="D9" t="s">
+        <v>212</v>
+      </c>
+      <c r="E9" t="s">
+        <v>253</v>
+      </c>
+      <c r="F9" t="s">
+        <v>254</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>256</v>
+      </c>
+      <c r="B10" t="s">
+        <v>251</v>
+      </c>
+      <c r="C10" t="s">
+        <v>252</v>
+      </c>
+      <c r="D10" t="s">
+        <v>212</v>
+      </c>
+      <c r="E10" t="s">
+        <v>253</v>
+      </c>
+      <c r="F10" t="s">
+        <v>257</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>259</v>
+      </c>
+      <c r="B11" t="s">
+        <v>260</v>
+      </c>
+      <c r="C11" t="s">
+        <v>261</v>
+      </c>
+      <c r="D11" t="s">
+        <v>262</v>
+      </c>
+      <c r="E11" t="s">
+        <v>263</v>
+      </c>
+      <c r="F11" t="s">
+        <v>264</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>266</v>
+      </c>
+      <c r="B12" t="s">
+        <v>267</v>
+      </c>
+      <c r="C12" t="s">
+        <v>268</v>
+      </c>
+      <c r="D12" t="s">
+        <v>237</v>
+      </c>
+      <c r="E12" t="s">
+        <v>219</v>
+      </c>
+      <c r="F12" t="s">
+        <v>269</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>271</v>
+      </c>
+      <c r="B13" t="s">
+        <v>272</v>
+      </c>
+      <c r="C13" t="s">
+        <v>273</v>
+      </c>
+      <c r="D13" t="s">
+        <v>212</v>
+      </c>
+      <c r="E13" t="s">
+        <v>274</v>
+      </c>
+      <c r="F13" t="s">
+        <v>275</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>277</v>
+      </c>
+      <c r="B14" t="s">
+        <v>278</v>
+      </c>
+      <c r="C14" t="s">
+        <v>252</v>
+      </c>
+      <c r="D14" t="s">
+        <v>212</v>
+      </c>
+      <c r="E14" t="s">
+        <v>279</v>
+      </c>
+      <c r="F14" t="s">
+        <v>280</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>282</v>
+      </c>
+      <c r="B15" t="s">
+        <v>283</v>
+      </c>
+      <c r="C15" t="s">
+        <v>284</v>
+      </c>
+      <c r="D15" t="s">
+        <v>285</v>
+      </c>
+      <c r="E15" t="s">
+        <v>286</v>
+      </c>
+      <c r="F15" t="s">
+        <v>287</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>289</v>
+      </c>
+      <c r="B16" t="s">
+        <v>283</v>
+      </c>
+      <c r="C16" t="s">
+        <v>290</v>
+      </c>
+      <c r="D16" t="s">
+        <v>285</v>
+      </c>
+      <c r="E16" t="s">
+        <v>286</v>
+      </c>
+      <c r="F16" t="s">
+        <v>287</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>292</v>
+      </c>
+      <c r="B17" t="s">
+        <v>283</v>
+      </c>
+      <c r="C17" t="s">
+        <v>293</v>
+      </c>
+      <c r="D17" t="s">
+        <v>262</v>
+      </c>
+      <c r="E17" t="s">
+        <v>286</v>
+      </c>
+      <c r="F17" t="s">
+        <v>287</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>295</v>
+      </c>
+      <c r="B18" t="s">
+        <v>296</v>
+      </c>
+      <c r="C18" t="s">
+        <v>297</v>
+      </c>
+      <c r="D18" t="s">
+        <v>212</v>
+      </c>
+      <c r="E18" t="s">
+        <v>298</v>
+      </c>
+      <c r="F18" t="s">
+        <v>299</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>301</v>
+      </c>
+      <c r="B19" t="s">
+        <v>302</v>
+      </c>
+      <c r="C19" t="s">
+        <v>17</v>
+      </c>
+      <c r="D19" t="s">
+        <v>212</v>
+      </c>
+      <c r="E19" t="s">
+        <v>303</v>
+      </c>
+      <c r="F19" t="s">
+        <v>304</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>306</v>
+      </c>
+      <c r="B20" t="s">
+        <v>307</v>
+      </c>
+      <c r="C20" t="s">
+        <v>308</v>
+      </c>
+      <c r="D20" t="s">
+        <v>212</v>
+      </c>
+      <c r="E20" t="s">
+        <v>309</v>
+      </c>
+      <c r="F20" t="s">
+        <v>310</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>312</v>
+      </c>
+      <c r="B21" t="s">
+        <v>313</v>
+      </c>
+      <c r="C21" t="s">
+        <v>314</v>
+      </c>
+      <c r="D21" t="s">
+        <v>212</v>
+      </c>
+      <c r="E21" t="s">
+        <v>315</v>
+      </c>
+      <c r="F21" t="s">
+        <v>316</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>318</v>
+      </c>
+      <c r="B22" t="s">
+        <v>319</v>
+      </c>
+      <c r="C22" t="s">
+        <v>320</v>
+      </c>
+      <c r="D22" t="s">
+        <v>321</v>
+      </c>
+      <c r="E22" t="s">
+        <v>322</v>
+      </c>
+      <c r="F22" t="s">
+        <v>323</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>325</v>
+      </c>
+      <c r="B23" t="s">
+        <v>326</v>
+      </c>
+      <c r="C23" t="s">
+        <v>327</v>
+      </c>
+      <c r="D23" t="s">
+        <v>321</v>
+      </c>
+      <c r="E23" t="s">
+        <v>328</v>
+      </c>
+      <c r="F23" t="s">
+        <v>329</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>331</v>
+      </c>
+      <c r="B24" t="s">
+        <v>332</v>
+      </c>
+      <c r="C24" t="s">
+        <v>333</v>
+      </c>
+      <c r="D24" t="s">
+        <v>212</v>
+      </c>
+      <c r="E24" t="s">
+        <v>334</v>
+      </c>
+      <c r="F24" t="s">
+        <v>335</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>337</v>
+      </c>
+      <c r="B25" t="s">
+        <v>338</v>
+      </c>
+      <c r="C25" t="s">
+        <v>246</v>
+      </c>
+      <c r="D25" t="s">
+        <v>212</v>
+      </c>
+      <c r="E25" t="s">
+        <v>339</v>
+      </c>
+      <c r="F25" t="s">
+        <v>340</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>342</v>
+      </c>
+      <c r="B26" t="s">
+        <v>343</v>
+      </c>
+      <c r="C26" t="s">
+        <v>344</v>
+      </c>
+      <c r="D26" t="s">
+        <v>212</v>
+      </c>
+      <c r="E26" t="s">
+        <v>345</v>
+      </c>
+      <c r="F26" t="s">
+        <v>346</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>348</v>
+      </c>
+      <c r="B27" t="s">
+        <v>349</v>
+      </c>
+      <c r="C27" t="s">
+        <v>218</v>
+      </c>
+      <c r="D27" t="s">
+        <v>212</v>
+      </c>
+      <c r="E27" t="s">
+        <v>350</v>
+      </c>
+      <c r="F27" t="s">
+        <v>351</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>353</v>
+      </c>
+      <c r="B28" t="s">
+        <v>354</v>
+      </c>
+      <c r="C28" t="s">
+        <v>355</v>
+      </c>
+      <c r="D28" t="s">
+        <v>212</v>
+      </c>
+      <c r="E28" t="s">
+        <v>356</v>
+      </c>
+      <c r="F28" t="s">
+        <v>357</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>359</v>
+      </c>
+      <c r="B29" t="s">
+        <v>360</v>
+      </c>
+      <c r="C29" t="s">
+        <v>252</v>
+      </c>
+      <c r="D29" t="s">
+        <v>212</v>
+      </c>
+      <c r="E29" t="s">
+        <v>263</v>
+      </c>
+      <c r="F29" t="s">
+        <v>361</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>363</v>
+      </c>
+      <c r="B30" t="s">
+        <v>364</v>
+      </c>
+      <c r="C30" t="s">
+        <v>365</v>
+      </c>
+      <c r="D30" t="s">
+        <v>212</v>
+      </c>
+      <c r="E30" t="s">
+        <v>366</v>
+      </c>
+      <c r="F30" t="s">
+        <v>219</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>368</v>
+      </c>
+      <c r="B31" t="s">
+        <v>364</v>
+      </c>
+      <c r="C31" t="s">
+        <v>365</v>
+      </c>
+      <c r="D31" t="s">
+        <v>212</v>
+      </c>
+      <c r="E31" t="s">
+        <v>366</v>
+      </c>
+      <c r="F31" t="s">
+        <v>219</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>370</v>
+      </c>
+      <c r="B32" t="s">
+        <v>371</v>
+      </c>
+      <c r="C32" t="s">
+        <v>252</v>
+      </c>
+      <c r="D32" t="s">
+        <v>212</v>
+      </c>
+      <c r="E32" t="s">
+        <v>263</v>
+      </c>
+      <c r="F32" t="s">
+        <v>219</v>
+      </c>
+      <c r="H32" s="2" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>373</v>
+      </c>
+      <c r="B33" t="s">
+        <v>374</v>
+      </c>
+      <c r="C33" t="s">
+        <v>252</v>
+      </c>
+      <c r="D33" t="s">
+        <v>212</v>
+      </c>
+      <c r="E33" t="s">
+        <v>375</v>
+      </c>
+      <c r="F33" t="s">
+        <v>219</v>
+      </c>
+      <c r="H33" s="2" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>377</v>
+      </c>
+      <c r="B34" t="s">
+        <v>378</v>
+      </c>
+      <c r="C34" t="s">
+        <v>379</v>
+      </c>
+      <c r="D34" t="s">
+        <v>212</v>
+      </c>
+      <c r="E34" t="s">
+        <v>380</v>
+      </c>
+      <c r="F34" t="s">
+        <v>381</v>
+      </c>
+      <c r="H34" s="2" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>383</v>
+      </c>
+      <c r="B35" t="s">
+        <v>384</v>
+      </c>
+      <c r="C35" t="s">
+        <v>314</v>
+      </c>
+      <c r="D35" t="s">
+        <v>321</v>
+      </c>
+      <c r="E35" t="s">
+        <v>385</v>
+      </c>
+      <c r="F35" t="s">
+        <v>386</v>
+      </c>
+      <c r="H35" s="2" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>383</v>
+      </c>
+      <c r="B36" t="s">
+        <v>388</v>
+      </c>
+      <c r="C36" t="s">
+        <v>246</v>
+      </c>
+      <c r="D36" t="s">
+        <v>237</v>
+      </c>
+      <c r="E36" t="s">
+        <v>389</v>
+      </c>
+      <c r="F36" t="s">
+        <v>390</v>
+      </c>
+      <c r="H36" s="2" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>392</v>
+      </c>
+      <c r="B37" t="s">
+        <v>278</v>
+      </c>
+      <c r="C37" t="s">
+        <v>252</v>
+      </c>
+      <c r="D37" t="s">
+        <v>212</v>
+      </c>
+      <c r="E37" t="s">
+        <v>393</v>
+      </c>
+      <c r="F37" t="s">
+        <v>280</v>
+      </c>
+      <c r="H37" s="2" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>395</v>
+      </c>
+      <c r="B38" t="s">
+        <v>396</v>
+      </c>
+      <c r="C38" t="s">
+        <v>284</v>
+      </c>
+      <c r="D38" t="s">
+        <v>321</v>
+      </c>
+      <c r="E38" t="s">
+        <v>397</v>
+      </c>
+      <c r="F38" t="s">
+        <v>398</v>
+      </c>
+      <c r="H38" s="2" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>400</v>
+      </c>
+      <c r="B39" t="s">
+        <v>401</v>
+      </c>
+      <c r="C39" t="s">
+        <v>402</v>
+      </c>
+      <c r="D39" t="s">
+        <v>212</v>
+      </c>
+      <c r="E39" t="s">
+        <v>403</v>
+      </c>
+      <c r="F39" t="s">
+        <v>404</v>
+      </c>
+      <c r="H39" s="2" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>406</v>
+      </c>
+      <c r="B40" t="s">
+        <v>407</v>
+      </c>
+      <c r="C40" t="s">
+        <v>408</v>
+      </c>
+      <c r="D40" t="s">
+        <v>212</v>
+      </c>
+      <c r="E40" t="s">
+        <v>409</v>
+      </c>
+      <c r="F40" t="s">
+        <v>410</v>
+      </c>
+      <c r="H40" s="2" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>412</v>
+      </c>
+      <c r="B41" t="s">
+        <v>413</v>
+      </c>
+      <c r="C41" t="s">
+        <v>261</v>
+      </c>
+      <c r="D41" t="s">
+        <v>212</v>
+      </c>
+      <c r="E41" t="s">
+        <v>414</v>
+      </c>
+      <c r="F41" t="s">
+        <v>415</v>
+      </c>
+      <c r="H41" s="2" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>417</v>
+      </c>
+      <c r="B42" t="s">
+        <v>418</v>
+      </c>
+      <c r="C42" t="s">
+        <v>419</v>
+      </c>
+      <c r="D42" t="s">
+        <v>212</v>
+      </c>
+      <c r="E42" t="s">
+        <v>420</v>
+      </c>
+      <c r="F42" t="s">
+        <v>421</v>
+      </c>
+      <c r="H42" s="2" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>423</v>
+      </c>
+      <c r="B43" t="s">
+        <v>313</v>
+      </c>
+      <c r="C43" t="s">
+        <v>314</v>
+      </c>
+      <c r="D43" t="s">
+        <v>212</v>
+      </c>
+      <c r="E43" t="s">
+        <v>424</v>
+      </c>
+      <c r="F43" t="s">
+        <v>425</v>
+      </c>
+      <c r="H43" s="2" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>427</v>
+      </c>
+      <c r="B44" t="s">
+        <v>428</v>
+      </c>
+      <c r="C44" t="s">
+        <v>218</v>
+      </c>
+      <c r="D44" t="s">
+        <v>212</v>
+      </c>
+      <c r="E44" t="s">
+        <v>429</v>
+      </c>
+      <c r="F44" t="s">
+        <v>430</v>
+      </c>
+      <c r="H44" s="2" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>427</v>
+      </c>
+      <c r="B45" t="s">
+        <v>432</v>
+      </c>
+      <c r="C45" t="s">
+        <v>433</v>
+      </c>
+      <c r="D45" t="s">
+        <v>212</v>
+      </c>
+      <c r="E45" t="s">
+        <v>434</v>
+      </c>
+      <c r="F45" t="s">
+        <v>435</v>
+      </c>
+      <c r="H45" s="2" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>427</v>
+      </c>
+      <c r="B46" t="s">
+        <v>260</v>
+      </c>
+      <c r="C46" t="s">
+        <v>246</v>
+      </c>
+      <c r="D46" t="s">
+        <v>212</v>
+      </c>
+      <c r="E46" t="s">
+        <v>437</v>
+      </c>
+      <c r="F46" t="s">
+        <v>264</v>
+      </c>
+      <c r="H46" s="2" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>439</v>
+      </c>
+      <c r="B47" t="s">
+        <v>440</v>
+      </c>
+      <c r="C47" t="s">
+        <v>441</v>
+      </c>
+      <c r="D47" t="s">
+        <v>212</v>
+      </c>
+      <c r="E47" t="s">
+        <v>442</v>
+      </c>
+      <c r="F47" t="s">
+        <v>280</v>
+      </c>
+      <c r="H47" s="2" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>444</v>
+      </c>
+      <c r="B48" t="s">
+        <v>445</v>
+      </c>
+      <c r="C48" t="s">
+        <v>446</v>
+      </c>
+      <c r="D48" t="s">
+        <v>212</v>
+      </c>
+      <c r="E48" t="s">
+        <v>219</v>
+      </c>
+      <c r="F48" t="s">
+        <v>447</v>
+      </c>
+      <c r="H48" s="2" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>449</v>
+      </c>
+      <c r="B49" t="s">
+        <v>450</v>
+      </c>
+      <c r="C49" t="s">
+        <v>218</v>
+      </c>
+      <c r="D49" t="s">
+        <v>212</v>
+      </c>
+      <c r="E49" t="s">
+        <v>451</v>
+      </c>
+      <c r="F49" t="s">
+        <v>219</v>
+      </c>
+      <c r="H49" s="2" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>453</v>
+      </c>
+      <c r="B50" t="s">
+        <v>454</v>
+      </c>
+      <c r="C50" t="s">
+        <v>455</v>
+      </c>
+      <c r="D50" t="s">
+        <v>212</v>
+      </c>
+      <c r="E50" t="s">
+        <v>456</v>
+      </c>
+      <c r="F50" t="s">
+        <v>457</v>
+      </c>
+      <c r="H50" s="2" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>459</v>
+      </c>
+      <c r="B51" t="s">
+        <v>338</v>
+      </c>
+      <c r="C51" t="s">
+        <v>246</v>
+      </c>
+      <c r="D51" t="s">
+        <v>212</v>
+      </c>
+      <c r="E51" t="s">
+        <v>460</v>
+      </c>
+      <c r="F51" t="s">
+        <v>340</v>
+      </c>
+      <c r="H51" s="2" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>462</v>
+      </c>
+      <c r="B52" t="s">
+        <v>463</v>
+      </c>
+      <c r="C52" t="s">
+        <v>464</v>
+      </c>
+      <c r="D52" t="s">
+        <v>212</v>
+      </c>
+      <c r="E52" t="s">
+        <v>465</v>
+      </c>
+      <c r="F52" t="s">
+        <v>466</v>
+      </c>
+      <c r="H52" s="2" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>468</v>
+      </c>
+      <c r="B53" t="s">
+        <v>469</v>
+      </c>
+      <c r="C53" t="s">
+        <v>470</v>
+      </c>
+      <c r="D53" t="s">
+        <v>212</v>
+      </c>
+      <c r="E53" t="s">
+        <v>471</v>
+      </c>
+      <c r="F53" t="s">
+        <v>219</v>
+      </c>
+      <c r="H53" s="2" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>473</v>
+      </c>
+      <c r="B54" t="s">
+        <v>474</v>
+      </c>
+      <c r="C54" t="s">
+        <v>475</v>
+      </c>
+      <c r="D54" t="s">
+        <v>212</v>
+      </c>
+      <c r="E54" t="s">
+        <v>476</v>
+      </c>
+      <c r="F54" t="s">
+        <v>477</v>
+      </c>
+      <c r="H54" s="2" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>479</v>
+      </c>
+      <c r="B55" t="s">
+        <v>480</v>
+      </c>
+      <c r="C55" t="s">
+        <v>481</v>
+      </c>
+      <c r="D55" t="s">
+        <v>212</v>
+      </c>
+      <c r="E55" t="s">
+        <v>309</v>
+      </c>
+      <c r="F55" t="s">
+        <v>482</v>
+      </c>
+      <c r="H55" s="2" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>52</v>
+      </c>
+      <c r="B56" t="s">
+        <v>484</v>
+      </c>
+      <c r="C56" t="s">
+        <v>246</v>
+      </c>
+      <c r="D56" t="s">
+        <v>212</v>
+      </c>
+      <c r="E56" t="s">
+        <v>485</v>
+      </c>
+      <c r="F56" t="s">
+        <v>486</v>
+      </c>
+      <c r="H56" s="2" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>52</v>
+      </c>
+      <c r="B57" t="s">
+        <v>488</v>
+      </c>
+      <c r="C57" t="s">
+        <v>489</v>
+      </c>
+      <c r="D57" t="s">
+        <v>212</v>
+      </c>
+      <c r="E57" t="s">
+        <v>490</v>
+      </c>
+      <c r="F57" t="s">
+        <v>491</v>
+      </c>
+      <c r="H57" s="2" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>493</v>
+      </c>
+      <c r="B58" t="s">
+        <v>494</v>
+      </c>
+      <c r="C58" t="s">
+        <v>495</v>
+      </c>
+      <c r="D58" t="s">
+        <v>321</v>
+      </c>
+      <c r="E58" t="s">
+        <v>496</v>
+      </c>
+      <c r="F58" t="s">
+        <v>386</v>
+      </c>
+      <c r="H58" s="2" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>498</v>
+      </c>
+      <c r="B59" t="s">
+        <v>499</v>
+      </c>
+      <c r="C59" t="s">
+        <v>252</v>
+      </c>
+      <c r="D59" t="s">
+        <v>212</v>
+      </c>
+      <c r="E59" t="s">
+        <v>500</v>
+      </c>
+      <c r="F59" t="s">
+        <v>501</v>
+      </c>
+      <c r="H59" s="2" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>503</v>
+      </c>
+      <c r="B60" t="s">
+        <v>504</v>
+      </c>
+      <c r="C60" t="s">
+        <v>505</v>
+      </c>
+      <c r="D60" t="s">
+        <v>321</v>
+      </c>
+      <c r="E60" t="s">
+        <v>506</v>
+      </c>
+      <c r="F60" t="s">
+        <v>404</v>
+      </c>
+      <c r="H60" s="2" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>508</v>
+      </c>
+      <c r="B61" t="s">
+        <v>509</v>
+      </c>
+      <c r="C61" t="s">
+        <v>464</v>
+      </c>
+      <c r="D61" t="s">
+        <v>212</v>
+      </c>
+      <c r="E61" t="s">
+        <v>485</v>
+      </c>
+      <c r="F61" t="s">
+        <v>510</v>
+      </c>
+      <c r="H61" s="2" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>512</v>
+      </c>
+      <c r="B62" t="s">
+        <v>513</v>
+      </c>
+      <c r="C62" t="s">
+        <v>252</v>
+      </c>
+      <c r="D62" t="s">
+        <v>212</v>
+      </c>
+      <c r="E62" t="s">
+        <v>514</v>
+      </c>
+      <c r="F62" t="s">
+        <v>515</v>
+      </c>
+      <c r="H62" s="2" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>517</v>
+      </c>
+      <c r="B63" t="s">
+        <v>518</v>
+      </c>
+      <c r="C63" t="s">
+        <v>252</v>
+      </c>
+      <c r="D63" t="s">
+        <v>212</v>
+      </c>
+      <c r="E63" t="s">
+        <v>519</v>
+      </c>
+      <c r="F63" t="s">
+        <v>520</v>
+      </c>
+      <c r="H63" s="2" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>522</v>
+      </c>
+      <c r="B64" t="s">
+        <v>523</v>
+      </c>
+      <c r="C64" t="s">
+        <v>524</v>
+      </c>
+      <c r="D64" t="s">
+        <v>212</v>
+      </c>
+      <c r="E64" t="s">
+        <v>525</v>
+      </c>
+      <c r="F64" t="s">
+        <v>526</v>
+      </c>
+      <c r="H64" s="2" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>528</v>
+      </c>
+      <c r="B65" t="s">
+        <v>529</v>
+      </c>
+      <c r="C65" t="s">
+        <v>530</v>
+      </c>
+      <c r="D65" t="s">
+        <v>285</v>
+      </c>
+      <c r="E65" t="s">
+        <v>356</v>
+      </c>
+      <c r="F65" t="s">
+        <v>531</v>
+      </c>
+      <c r="H65" s="2" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>533</v>
+      </c>
+      <c r="B66" t="s">
+        <v>374</v>
+      </c>
+      <c r="C66" t="s">
+        <v>252</v>
+      </c>
+      <c r="D66" t="s">
+        <v>212</v>
+      </c>
+      <c r="E66" t="s">
+        <v>534</v>
+      </c>
+      <c r="F66" t="s">
+        <v>219</v>
+      </c>
+      <c r="H66" s="2" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>536</v>
+      </c>
+      <c r="B67" t="s">
+        <v>537</v>
+      </c>
+      <c r="C67" t="s">
+        <v>538</v>
+      </c>
+      <c r="D67" t="s">
+        <v>212</v>
+      </c>
+      <c r="E67" t="s">
+        <v>539</v>
+      </c>
+      <c r="F67" t="s">
+        <v>540</v>
+      </c>
+      <c r="H67" s="2" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>542</v>
+      </c>
+      <c r="B68" t="s">
+        <v>326</v>
+      </c>
+      <c r="C68" t="s">
+        <v>327</v>
+      </c>
+      <c r="D68" t="s">
+        <v>212</v>
+      </c>
+      <c r="E68" t="s">
+        <v>543</v>
+      </c>
+      <c r="F68" t="s">
+        <v>329</v>
+      </c>
+      <c r="H68" s="2" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>545</v>
+      </c>
+      <c r="B69" t="s">
+        <v>546</v>
+      </c>
+      <c r="C69" t="s">
+        <v>547</v>
+      </c>
+      <c r="D69" t="s">
+        <v>212</v>
+      </c>
+      <c r="E69" t="s">
+        <v>548</v>
+      </c>
+      <c r="F69" t="s">
+        <v>482</v>
+      </c>
+      <c r="H69" s="2" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>550</v>
+      </c>
+      <c r="B70" t="s">
+        <v>551</v>
+      </c>
+      <c r="C70" t="s">
+        <v>552</v>
+      </c>
+      <c r="D70" t="s">
+        <v>212</v>
+      </c>
+      <c r="E70" t="s">
+        <v>553</v>
+      </c>
+      <c r="F70" t="s">
+        <v>554</v>
+      </c>
+      <c r="H70" s="2" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>556</v>
+      </c>
+      <c r="B71" t="s">
+        <v>557</v>
+      </c>
+      <c r="C71" t="s">
+        <v>246</v>
+      </c>
+      <c r="D71" t="s">
+        <v>212</v>
+      </c>
+      <c r="E71" t="s">
+        <v>558</v>
+      </c>
+      <c r="F71" t="s">
+        <v>559</v>
+      </c>
+      <c r="H71" s="2" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>561</v>
+      </c>
+      <c r="B72" t="s">
+        <v>562</v>
+      </c>
+      <c r="C72" t="s">
+        <v>563</v>
+      </c>
+      <c r="D72" t="s">
+        <v>212</v>
+      </c>
+      <c r="E72" t="s">
+        <v>564</v>
+      </c>
+      <c r="F72" t="s">
+        <v>565</v>
+      </c>
+      <c r="H72" s="2" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>567</v>
+      </c>
+      <c r="B73" t="s">
+        <v>568</v>
+      </c>
+      <c r="C73" t="s">
+        <v>481</v>
+      </c>
+      <c r="D73" t="s">
+        <v>212</v>
+      </c>
+      <c r="E73" t="s">
+        <v>569</v>
+      </c>
+      <c r="F73" t="s">
+        <v>570</v>
+      </c>
+      <c r="H73" s="2" t="s">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>572</v>
+      </c>
+      <c r="B74" t="s">
+        <v>573</v>
+      </c>
+      <c r="C74" t="s">
+        <v>574</v>
+      </c>
+      <c r="D74" t="s">
+        <v>212</v>
+      </c>
+      <c r="E74" t="s">
+        <v>575</v>
+      </c>
+      <c r="F74" t="s">
+        <v>576</v>
+      </c>
+      <c r="H74" s="2" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>578</v>
+      </c>
+      <c r="B75" t="s">
+        <v>307</v>
+      </c>
+      <c r="C75" t="s">
+        <v>579</v>
+      </c>
+      <c r="D75" t="s">
+        <v>212</v>
+      </c>
+      <c r="E75" t="s">
+        <v>580</v>
+      </c>
+      <c r="F75" t="s">
+        <v>581</v>
+      </c>
+      <c r="H75" s="2" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>583</v>
+      </c>
+      <c r="B76" t="s">
+        <v>584</v>
+      </c>
+      <c r="C76" t="s">
+        <v>481</v>
+      </c>
+      <c r="D76" t="s">
+        <v>212</v>
+      </c>
+      <c r="E76" t="s">
+        <v>219</v>
+      </c>
+      <c r="F76" t="s">
+        <v>219</v>
+      </c>
+      <c r="H76" s="2" t="s">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>586</v>
+      </c>
+      <c r="B77" t="s">
+        <v>587</v>
+      </c>
+      <c r="C77" t="s">
+        <v>588</v>
+      </c>
+      <c r="D77" t="s">
+        <v>212</v>
+      </c>
+      <c r="E77" t="s">
+        <v>589</v>
+      </c>
+      <c r="F77" t="s">
+        <v>501</v>
+      </c>
+      <c r="H77" s="2" t="s">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>591</v>
+      </c>
+      <c r="B78" t="s">
+        <v>592</v>
+      </c>
+      <c r="C78" t="s">
+        <v>593</v>
+      </c>
+      <c r="D78" t="s">
+        <v>212</v>
+      </c>
+      <c r="E78" t="s">
+        <v>594</v>
+      </c>
+      <c r="F78" t="s">
+        <v>595</v>
+      </c>
+      <c r="H78" s="2" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>597</v>
+      </c>
+      <c r="B79" t="s">
+        <v>598</v>
+      </c>
+      <c r="C79" t="s">
+        <v>246</v>
+      </c>
+      <c r="D79" t="s">
+        <v>285</v>
+      </c>
+      <c r="E79" t="s">
+        <v>219</v>
+      </c>
+      <c r="F79" t="s">
+        <v>599</v>
+      </c>
+      <c r="H79" s="2" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>601</v>
+      </c>
+      <c r="B80" t="s">
+        <v>602</v>
+      </c>
+      <c r="C80" t="s">
+        <v>464</v>
+      </c>
+      <c r="D80" t="s">
+        <v>212</v>
+      </c>
+      <c r="E80" t="s">
+        <v>603</v>
+      </c>
+      <c r="F80" t="s">
+        <v>482</v>
+      </c>
+      <c r="H80" s="2" t="s">
+        <v>604</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>605</v>
+      </c>
+      <c r="B81" t="s">
+        <v>360</v>
+      </c>
+      <c r="C81" t="s">
+        <v>252</v>
+      </c>
+      <c r="D81" t="s">
+        <v>212</v>
+      </c>
+      <c r="E81" t="s">
+        <v>606</v>
+      </c>
+      <c r="F81" t="s">
+        <v>361</v>
+      </c>
+      <c r="H81" s="2" t="s">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>608</v>
+      </c>
+      <c r="B82" t="s">
+        <v>609</v>
+      </c>
+      <c r="C82" t="s">
+        <v>218</v>
+      </c>
+      <c r="D82" t="s">
+        <v>237</v>
+      </c>
+      <c r="E82" t="s">
+        <v>610</v>
+      </c>
+      <c r="F82" t="s">
+        <v>299</v>
+      </c>
+      <c r="H82" s="2" t="s">
+        <v>611</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>612</v>
+      </c>
+      <c r="B83" t="s">
+        <v>613</v>
+      </c>
+      <c r="C83" t="s">
+        <v>614</v>
+      </c>
+      <c r="D83" t="s">
+        <v>262</v>
+      </c>
+      <c r="E83" t="s">
+        <v>615</v>
+      </c>
+      <c r="F83" t="s">
+        <v>616</v>
+      </c>
+      <c r="H83" s="2" t="s">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>618</v>
+      </c>
+      <c r="B84" t="s">
+        <v>619</v>
+      </c>
+      <c r="C84" t="s">
+        <v>252</v>
+      </c>
+      <c r="D84" t="s">
+        <v>212</v>
+      </c>
+      <c r="E84" t="s">
+        <v>375</v>
+      </c>
+      <c r="F84" t="s">
+        <v>421</v>
+      </c>
+      <c r="H84" s="2" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>621</v>
+      </c>
+      <c r="B85" t="s">
+        <v>622</v>
+      </c>
+      <c r="C85" t="s">
+        <v>464</v>
+      </c>
+      <c r="D85" t="s">
+        <v>262</v>
+      </c>
+      <c r="E85" t="s">
+        <v>623</v>
+      </c>
+      <c r="F85" t="s">
+        <v>624</v>
+      </c>
+      <c r="H85" s="2" t="s">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>626</v>
+      </c>
+      <c r="B86" t="s">
+        <v>454</v>
+      </c>
+      <c r="C86" t="s">
+        <v>455</v>
+      </c>
+      <c r="D86" t="s">
+        <v>212</v>
+      </c>
+      <c r="E86" t="s">
+        <v>627</v>
+      </c>
+      <c r="F86" t="s">
+        <v>457</v>
+      </c>
+      <c r="H86" s="2" t="s">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>629</v>
+      </c>
+      <c r="B87" t="s">
+        <v>630</v>
+      </c>
+      <c r="C87" t="s">
+        <v>631</v>
+      </c>
+      <c r="D87" t="s">
+        <v>212</v>
+      </c>
+      <c r="E87" t="s">
+        <v>632</v>
+      </c>
+      <c r="F87" t="s">
+        <v>633</v>
+      </c>
+      <c r="H87" s="2" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>635</v>
+      </c>
+      <c r="B88" t="s">
+        <v>636</v>
+      </c>
+      <c r="C88" t="s">
+        <v>637</v>
+      </c>
+      <c r="D88" t="s">
+        <v>212</v>
+      </c>
+      <c r="E88" t="s">
+        <v>638</v>
+      </c>
+      <c r="F88" t="s">
+        <v>639</v>
+      </c>
+      <c r="H88" s="2" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>641</v>
+      </c>
+      <c r="B89" t="s">
+        <v>642</v>
+      </c>
+      <c r="C89" t="s">
+        <v>643</v>
+      </c>
+      <c r="D89" t="s">
+        <v>212</v>
+      </c>
+      <c r="E89" t="s">
+        <v>644</v>
+      </c>
+      <c r="F89" t="s">
+        <v>645</v>
+      </c>
+      <c r="H89" s="2" t="s">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>647</v>
+      </c>
+      <c r="B90" t="s">
+        <v>648</v>
+      </c>
+      <c r="C90" t="s">
+        <v>464</v>
+      </c>
+      <c r="D90" t="s">
+        <v>212</v>
+      </c>
+      <c r="E90" t="s">
+        <v>649</v>
+      </c>
+      <c r="F90" t="s">
+        <v>219</v>
+      </c>
+      <c r="H90" s="2" t="s">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>651</v>
+      </c>
+      <c r="B91" t="s">
+        <v>562</v>
+      </c>
+      <c r="C91" t="s">
+        <v>563</v>
+      </c>
+      <c r="D91" t="s">
+        <v>212</v>
+      </c>
+      <c r="E91" t="s">
+        <v>652</v>
+      </c>
+      <c r="F91" t="s">
+        <v>565</v>
+      </c>
+      <c r="H91" s="2" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>654</v>
+      </c>
+      <c r="B92" t="s">
+        <v>655</v>
+      </c>
+      <c r="C92" t="s">
+        <v>481</v>
+      </c>
+      <c r="D92" t="s">
+        <v>212</v>
+      </c>
+      <c r="E92" t="s">
+        <v>375</v>
+      </c>
+      <c r="F92" t="s">
+        <v>656</v>
+      </c>
+      <c r="H92" s="2" t="s">
+        <v>657</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>658</v>
+      </c>
+      <c r="B93" t="s">
+        <v>659</v>
+      </c>
+      <c r="C93" t="s">
+        <v>252</v>
+      </c>
+      <c r="D93" t="s">
+        <v>212</v>
+      </c>
+      <c r="E93" t="s">
+        <v>660</v>
+      </c>
+      <c r="F93" t="s">
+        <v>238</v>
+      </c>
+      <c r="H93" s="2" t="s">
+        <v>661</v>
+      </c>
+    </row>
+    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>662</v>
+      </c>
+      <c r="B94" t="s">
+        <v>663</v>
+      </c>
+      <c r="C94" t="s">
+        <v>464</v>
+      </c>
+      <c r="D94" t="s">
+        <v>212</v>
+      </c>
+      <c r="E94" t="s">
+        <v>519</v>
+      </c>
+      <c r="F94" t="s">
+        <v>664</v>
+      </c>
+      <c r="H94" s="2" t="s">
+        <v>665</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>666</v>
+      </c>
+      <c r="B95" t="s">
+        <v>667</v>
+      </c>
+      <c r="C95" t="s">
+        <v>668</v>
+      </c>
+      <c r="D95" t="s">
+        <v>212</v>
+      </c>
+      <c r="E95" t="s">
+        <v>627</v>
+      </c>
+      <c r="F95" t="s">
+        <v>219</v>
+      </c>
+      <c r="H95" s="2" t="s">
+        <v>669</v>
+      </c>
+    </row>
+    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>670</v>
+      </c>
+      <c r="B96" t="s">
+        <v>619</v>
+      </c>
+      <c r="C96" t="s">
+        <v>252</v>
+      </c>
+      <c r="D96" t="s">
+        <v>212</v>
+      </c>
+      <c r="E96" t="s">
+        <v>519</v>
+      </c>
+      <c r="F96" t="s">
+        <v>421</v>
+      </c>
+      <c r="H96" s="2" t="s">
+        <v>671</v>
+      </c>
+    </row>
+    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>672</v>
+      </c>
+      <c r="B97" t="s">
+        <v>673</v>
+      </c>
+      <c r="C97" t="s">
+        <v>246</v>
+      </c>
+      <c r="D97" t="s">
+        <v>212</v>
+      </c>
+      <c r="E97" t="s">
+        <v>674</v>
+      </c>
+      <c r="F97" t="s">
+        <v>675</v>
+      </c>
+      <c r="H97" s="2" t="s">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="98" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>677</v>
+      </c>
+      <c r="B98" t="s">
+        <v>678</v>
+      </c>
+      <c r="C98" t="s">
+        <v>379</v>
+      </c>
+      <c r="D98" t="s">
+        <v>212</v>
+      </c>
+      <c r="E98" t="s">
+        <v>679</v>
+      </c>
+      <c r="F98" t="s">
+        <v>680</v>
+      </c>
+      <c r="H98" s="2" t="s">
+        <v>681</v>
+      </c>
+    </row>
+    <row r="99" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>682</v>
+      </c>
+      <c r="B99" t="s">
+        <v>683</v>
+      </c>
+      <c r="C99" t="s">
+        <v>684</v>
+      </c>
+      <c r="D99" t="s">
+        <v>212</v>
+      </c>
+      <c r="E99" t="s">
+        <v>685</v>
+      </c>
+      <c r="F99" t="s">
+        <v>686</v>
+      </c>
+      <c r="H99" s="2" t="s">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="100" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>688</v>
+      </c>
+      <c r="B100" t="s">
+        <v>689</v>
+      </c>
+      <c r="C100" t="s">
+        <v>690</v>
+      </c>
+      <c r="D100" t="s">
+        <v>212</v>
+      </c>
+      <c r="E100" t="s">
+        <v>219</v>
+      </c>
+      <c r="F100" t="s">
+        <v>565</v>
+      </c>
+      <c r="H100" s="2" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="101" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>692</v>
+      </c>
+      <c r="B101" t="s">
+        <v>693</v>
+      </c>
+      <c r="C101" t="s">
+        <v>694</v>
+      </c>
+      <c r="D101" t="s">
+        <v>212</v>
+      </c>
+      <c r="E101" t="s">
+        <v>695</v>
+      </c>
+      <c r="F101" t="s">
+        <v>696</v>
+      </c>
+      <c r="H101" s="2" t="s">
+        <v>697</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
+  <hyperlinks>
+    <hyperlink ref="H2" r:id="rId1"/>
+    <hyperlink ref="H3" r:id="rId2"/>
+    <hyperlink ref="H4" r:id="rId3"/>
+    <hyperlink ref="H5" r:id="rId4"/>
+    <hyperlink ref="H6" r:id="rId5"/>
+    <hyperlink ref="H7" r:id="rId6"/>
+    <hyperlink ref="H8" r:id="rId7"/>
+    <hyperlink ref="H9" r:id="rId8"/>
+    <hyperlink ref="H10" r:id="rId9"/>
+    <hyperlink ref="H11" r:id="rId10"/>
+    <hyperlink ref="H12" r:id="rId11"/>
+    <hyperlink ref="H13" r:id="rId12"/>
+    <hyperlink ref="H14" r:id="rId13"/>
+    <hyperlink ref="H15" r:id="rId14"/>
+    <hyperlink ref="H16" r:id="rId15"/>
+    <hyperlink ref="H17" r:id="rId16"/>
+    <hyperlink ref="H18" r:id="rId17"/>
+    <hyperlink ref="H19" r:id="rId18"/>
+    <hyperlink ref="H20" r:id="rId19"/>
+    <hyperlink ref="H21" r:id="rId20"/>
+    <hyperlink ref="H22" r:id="rId21"/>
+    <hyperlink ref="H23" r:id="rId22"/>
+    <hyperlink ref="H24" r:id="rId23"/>
+    <hyperlink ref="H25" r:id="rId24"/>
+    <hyperlink ref="H26" r:id="rId25"/>
+    <hyperlink ref="H27" r:id="rId26"/>
+    <hyperlink ref="H28" r:id="rId27"/>
+    <hyperlink ref="H29" r:id="rId28"/>
+    <hyperlink ref="H30" r:id="rId29"/>
+    <hyperlink ref="H31" r:id="rId30"/>
+    <hyperlink ref="H32" r:id="rId31"/>
+    <hyperlink ref="H33" r:id="rId32"/>
+    <hyperlink ref="H34" r:id="rId33"/>
+    <hyperlink ref="H35" r:id="rId34"/>
+    <hyperlink ref="H36" r:id="rId35"/>
+    <hyperlink ref="H37" r:id="rId36"/>
+    <hyperlink ref="H38" r:id="rId37"/>
+    <hyperlink ref="H39" r:id="rId38"/>
+    <hyperlink ref="H40" r:id="rId39"/>
+    <hyperlink ref="H41" r:id="rId40"/>
+    <hyperlink ref="H42" r:id="rId41"/>
+    <hyperlink ref="H43" r:id="rId42"/>
+    <hyperlink ref="H44" r:id="rId43"/>
+    <hyperlink ref="H45" r:id="rId44"/>
+    <hyperlink ref="H46" r:id="rId45"/>
+    <hyperlink ref="H47" r:id="rId46"/>
+    <hyperlink ref="H48" r:id="rId47"/>
+    <hyperlink ref="H49" r:id="rId48"/>
+    <hyperlink ref="H50" r:id="rId49"/>
+    <hyperlink ref="H51" r:id="rId50"/>
+    <hyperlink ref="H52" r:id="rId51"/>
+    <hyperlink ref="H53" r:id="rId52"/>
+    <hyperlink ref="H54" r:id="rId53"/>
+    <hyperlink ref="H55" r:id="rId54"/>
+    <hyperlink ref="H56" r:id="rId55"/>
+    <hyperlink ref="H57" r:id="rId56"/>
+    <hyperlink ref="H58" r:id="rId57"/>
+    <hyperlink ref="H59" r:id="rId58"/>
+    <hyperlink ref="H60" r:id="rId59"/>
+    <hyperlink ref="H61" r:id="rId60"/>
+    <hyperlink ref="H62" r:id="rId61"/>
+    <hyperlink ref="H63" r:id="rId62"/>
+    <hyperlink ref="H64" r:id="rId63"/>
+    <hyperlink ref="H65" r:id="rId64"/>
+    <hyperlink ref="H66" r:id="rId65"/>
+    <hyperlink ref="H67" r:id="rId66"/>
+    <hyperlink ref="H68" r:id="rId67"/>
+    <hyperlink ref="H69" r:id="rId68"/>
+    <hyperlink ref="H70" r:id="rId69"/>
+    <hyperlink ref="H71" r:id="rId70"/>
+    <hyperlink ref="H72" r:id="rId71"/>
+    <hyperlink ref="H73" r:id="rId72"/>
+    <hyperlink ref="H74" r:id="rId73"/>
+    <hyperlink ref="H75" r:id="rId74"/>
+    <hyperlink ref="H76" r:id="rId75"/>
+    <hyperlink ref="H77" r:id="rId76"/>
+    <hyperlink ref="H78" r:id="rId77"/>
+    <hyperlink ref="H79" r:id="rId78"/>
+    <hyperlink ref="H80" r:id="rId79"/>
+    <hyperlink ref="H81" r:id="rId80"/>
+    <hyperlink ref="H82" r:id="rId81"/>
+    <hyperlink ref="H83" r:id="rId82"/>
+    <hyperlink ref="H84" r:id="rId83"/>
+    <hyperlink ref="H85" r:id="rId84"/>
+    <hyperlink ref="H86" r:id="rId85"/>
+    <hyperlink ref="H87" r:id="rId86"/>
+    <hyperlink ref="H88" r:id="rId87"/>
+    <hyperlink ref="H89" r:id="rId88"/>
+    <hyperlink ref="H90" r:id="rId89"/>
+    <hyperlink ref="H91" r:id="rId90"/>
+    <hyperlink ref="H92" r:id="rId91"/>
+    <hyperlink ref="H93" r:id="rId92"/>
+    <hyperlink ref="H94" r:id="rId93"/>
+    <hyperlink ref="H95" r:id="rId94"/>
+    <hyperlink ref="H96" r:id="rId95"/>
+    <hyperlink ref="H97" r:id="rId96"/>
+    <hyperlink ref="H98" r:id="rId97"/>
+    <hyperlink ref="H99" r:id="rId98"/>
+    <hyperlink ref="H100" r:id="rId99"/>
+    <hyperlink ref="H101" r:id="rId100"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>

--- a/docs/xlsx/jobs-2026-09-28.xlsx
+++ b/docs/xlsx/jobs-2026-09-28.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="991" uniqueCount="698">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1187" uniqueCount="832">
   <si>
     <t>Title</t>
   </si>
@@ -664,6 +664,24 @@
     <t>https://www.idealist.org/en/consultant-job/47eade9c89304c00b5195fc57ab87a18-account-executive-earned-media-wearerally-llc-los-angeles</t>
   </si>
   <si>
+    <t>Accounting Associate</t>
+  </si>
+  <si>
+    <t>Teach Plus</t>
+  </si>
+  <si>
+    <t>Remote</t>
+  </si>
+  <si>
+    <t>USD 68000.00 - 68000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Community Development, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/1d4b8f56a8504cfebf523f47296a8161-accounting-associate-teach-plus-boston</t>
+  </si>
+  <si>
     <t>Accounting Associate - Finance</t>
   </si>
   <si>
@@ -682,6 +700,24 @@
     <t>https://www.idealist.org/en/nonprofit-job/8b88e4b0a24b40aeafce0caf5bc349ab-accounting-associate-finance-community-economic-development-assistance-corp-cedac-boston</t>
   </si>
   <si>
+    <t>Administrative Assistant to the CEO</t>
+  </si>
+  <si>
+    <t>Ocean Exploration Trust</t>
+  </si>
+  <si>
+    <t>Old Lyme, Connecticut</t>
+  </si>
+  <si>
+    <t>USD 60000.00 - 60000.00/year</t>
+  </si>
+  <si>
+    <t>Education, Research Social Science, Science Technology</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/20ee0cafbe834719aacbde199ca8e29f-administrative-assistant-to-the-ceo-ocean-exploration-trust-old-lyme</t>
+  </si>
+  <si>
     <t>Advocate Supervisor</t>
   </si>
   <si>
@@ -718,6 +754,27 @@
     <t>https://www.idealist.org/en/consultant-job/82251a41c7164f68aa3e429ccdcfa8b7-affordable-housing-manager-community-grants-planning-housing-llc-cranbury</t>
   </si>
   <si>
+    <t>Algebra I &amp; II Instructors- After School - Liberty LEADS</t>
+  </si>
+  <si>
+    <t>Liberty LEADS in New York City</t>
+  </si>
+  <si>
+    <t>New York, NY</t>
+  </si>
+  <si>
+    <t>Part Time</t>
+  </si>
+  <si>
+    <t>USD 35.00 - 45.00/hour</t>
+  </si>
+  <si>
+    <t>Children Youth, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/6af40f8e857747f2a35d4c69f3fd57c1-algebra-i-ii-instructors-after-school-liberty-leads-liberty-leads-in-new-york-city-new-york</t>
+  </si>
+  <si>
     <t>Analista de Relacionamento com Doadores</t>
   </si>
   <si>
@@ -754,9 +811,6 @@
     <t>Be Clear</t>
   </si>
   <si>
-    <t>Remote</t>
-  </si>
-  <si>
     <t>USD 60000.00 - 95000.00/year</t>
   </si>
   <si>
@@ -901,6 +955,24 @@
     <t>https://www.idealist.org/en/nonprofit-job/0eb109112bc44bf0ac220f2d10bb3892-city-cohort-lead-san-antonio-tx-civic-nation-washington</t>
   </si>
   <si>
+    <t>Class B Driver</t>
+  </si>
+  <si>
+    <t>Boston Area Gleaners</t>
+  </si>
+  <si>
+    <t>Acton, Massachusetts</t>
+  </si>
+  <si>
+    <t>USD 26.00 - 30.00/hour</t>
+  </si>
+  <si>
+    <t>Agriculture, Environment, Hunger Food Security</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/72e3d7a190b640ac98561a5564cce5cd-class-b-driver-boston-area-gleaners-acton</t>
+  </si>
+  <si>
     <t>Classroom Facilitator</t>
   </si>
   <si>
@@ -979,9 +1051,6 @@
     <t>Lincoln, MA</t>
   </si>
   <si>
-    <t>Part Time</t>
-  </si>
-  <si>
     <t>USD 32000.00 - 35000.00/year</t>
   </si>
   <si>
@@ -1183,9 +1252,6 @@
     <t>Home for a Home</t>
   </si>
   <si>
-    <t>USD 35.00 - 45.00/hour</t>
-  </si>
-  <si>
     <t>Community Development, Economic Development, Family</t>
   </si>
   <si>
@@ -1228,9 +1294,6 @@
     <t>USD 1200.00 - 1500.00/month</t>
   </si>
   <si>
-    <t>Children Youth, Community Development, Education</t>
-  </si>
-  <si>
     <t>https://www.idealist.org/en/nonprofit-job/f1feef0ce5954329a0387cf7c94451be-development-manager-global-learning-exchange-initiative-antigua-guatemala</t>
   </si>
   <si>
@@ -1267,6 +1330,24 @@
     <t>https://www.idealist.org/en/nonprofit-job/b4a6498f6611421b8835a28889310b49-development-operations-associate-land-together-sacramento</t>
   </si>
   <si>
+    <t>Digital Fundraising Coordinator, Special Projects</t>
+  </si>
+  <si>
+    <t>OPB</t>
+  </si>
+  <si>
+    <t>Portland, OR</t>
+  </si>
+  <si>
+    <t>USD 28.17 - 29.30/hour</t>
+  </si>
+  <si>
+    <t>Media</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/7e5ab4a011fe4d2687710e3da991132e-digital-fundraising-coordinator-special-projects-opb-portland</t>
+  </si>
+  <si>
     <t>Director of Admissions and Marketing</t>
   </si>
   <si>
@@ -1279,9 +1360,6 @@
     <t>USD 76000.00 - 80000.00/year</t>
   </si>
   <si>
-    <t>Children Youth, Education</t>
-  </si>
-  <si>
     <t>https://www.idealist.org/en/nonprofit-job/acbbe76090e443ec8613e2fe29dab202-director-of-admissions-and-marketing-may-center-for-learning-santa-fe</t>
   </si>
   <si>
@@ -1402,6 +1480,21 @@
     <t>https://www.idealist.org/en/nonprofit-job/d6a04b90261b41d5a52f351dfccd9c97-director-of-programs-impact-national-foster-youth-institute-los-angeles</t>
   </si>
   <si>
+    <t>Director, Gift Planning</t>
+  </si>
+  <si>
+    <t>Ocean Conservancy</t>
+  </si>
+  <si>
+    <t>USD 140000.00 - 145000.00/year</t>
+  </si>
+  <si>
+    <t>Climate Change, Environment, Philanthropy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/3c1598af426b4ae9afe75959a17c270c-director-gift-planning-ocean-conservancy-washington</t>
+  </si>
+  <si>
     <t>Director, Legal Policy (or Senior Director, commensurate with experience)</t>
   </si>
   <si>
@@ -1435,6 +1528,39 @@
     <t>https://www.idealist.org/en/job/31981b0428194671ad3e745bb185f24b-director-multicultural-ministries-catholic-diocese-of-arlington-catholic-diocese-of-arlington-annandale</t>
   </si>
   <si>
+    <t>Director/Manager of Foundation Relations</t>
+  </si>
+  <si>
+    <t>Lawrence Berkeley National Laboratory</t>
+  </si>
+  <si>
+    <t>Berkeley, California</t>
+  </si>
+  <si>
+    <t>USD 120000.00 - 180000.00/year</t>
+  </si>
+  <si>
+    <t>Research Social Science</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/government-job/85deb03dae3048b5a45a7a70638fd1c3-directormanager-of-foundation-relations-lawrence-berkeley-national-laboratory-berkeley</t>
+  </si>
+  <si>
+    <t>Education Legal Assistant</t>
+  </si>
+  <si>
+    <t>Alliance for Children's Rights</t>
+  </si>
+  <si>
+    <t>USD 53000.00 - 62000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Legal Assistance, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/e4085e8456ab472ca98692c7955bfb07-education-legal-assistant-alliance-for-childrens-rights-los-angeles</t>
+  </si>
+  <si>
     <t>Education Manager, JA Innovation Center @ Lawrence High School</t>
   </si>
   <si>
@@ -1453,6 +1579,18 @@
     <t>https://www.idealist.org/en/nonprofit-job/a57df8a5235649268a6cc201492f060b-education-manager-ja-innovation-center-lawrence-high-school-junior-achievement-of-greater-boston-lawrence</t>
   </si>
   <si>
+    <t>Education Staff Attorney</t>
+  </si>
+  <si>
+    <t>USD 79000.00 - 92000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Education, Family</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/273a3f6d1d3c4a1eba2d6ab82eaa7c9a-education-staff-attorney-alliance-for-childrens-rights-los-angeles</t>
+  </si>
+  <si>
     <t>Executive Assistant and Operations Manager</t>
   </si>
   <si>
@@ -1510,6 +1648,24 @@
     <t>https://www.idealist.org/en/nonprofit-job/c8506140b4d44ea8bd0b6d983ea0236d-executive-director-saco-main-street-saco-main-street-saco</t>
   </si>
   <si>
+    <t>Executive Office Assistant</t>
+  </si>
+  <si>
+    <t>The Chuck Lorre Family Foundation</t>
+  </si>
+  <si>
+    <t>Burbank, California</t>
+  </si>
+  <si>
+    <t>USD 68000.00 - 73000.00/year</t>
+  </si>
+  <si>
+    <t>Arts Music, Education, Health Medicine</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/334952ca96ce44ada8eab15be320cde0-executive-office-assistant-the-chuck-lorre-family-foundation-burbank</t>
+  </si>
+  <si>
     <t>Financial Counselor</t>
   </si>
   <si>
@@ -1582,6 +1738,30 @@
     <t>https://www.idealist.org/en/nonprofit-job/071e9d4187d34325b6d67fc4082a9682-hr-manager-national-black-theatre-new-york</t>
   </si>
   <si>
+    <t>Community Energy Project</t>
+  </si>
+  <si>
+    <t>USD 75000.00 - 90000.00/year</t>
+  </si>
+  <si>
+    <t>Climate Change, Community Development, Housing Homelessness</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/640b7754e3ba4b3282b9417a2665af50-hr-manager-community-energy-project-portland</t>
+  </si>
+  <si>
+    <t>https://transportation.org/about/careers-at-aashto/?jobId=fb06d981-c776-0bef-7832-236defeee9bd</t>
+  </si>
+  <si>
+    <t>American Association of State Highway &amp; Transportation Officials</t>
+  </si>
+  <si>
+    <t>Transportation</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/290ad997b39f490b9703f2ced4e9a43a-httpstransportationorgaboutcareers-at-aashtojobidfb06d981-c776-0bef-7832-236defeee9bd-american-association-of-state-highway-transportation-officials-washington</t>
+  </si>
+  <si>
     <t>IMMIGRATION LAW ATTORNEY CWJC (Springfield)</t>
   </si>
   <si>
@@ -1600,6 +1780,21 @@
     <t>https://www.idealist.org/en/nonprofit-job/3733809c50bc44a6862035fa29b060d7-immigration-law-attorney-cwjc-springfield-community-legal-aid-affiliate-springfield</t>
   </si>
   <si>
+    <t>Individual Giving Coordinator</t>
+  </si>
+  <si>
+    <t>DESC</t>
+  </si>
+  <si>
+    <t>USD 89133.36 - 100846.56/year</t>
+  </si>
+  <si>
+    <t>Health Medicine, Housing Homelessness, Mental Health</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/b442053eae0d4c72aab577492c0ab57d-individual-giving-coordinator-desc-seattle</t>
+  </si>
+  <si>
     <t>Iowa Canvasser</t>
   </si>
   <si>
@@ -1645,9 +1840,6 @@
     <t>Manager of Communications</t>
   </si>
   <si>
-    <t>USD 60000.00 - 60000.00/year</t>
-  </si>
-  <si>
     <t>https://www.idealist.org/en/nonprofit-job/44ac044dc507443c96ec0d2f581bfd3b-manager-of-communications-lighthouse-foundation-of-chicagoland-chicago</t>
   </si>
   <si>
@@ -1660,9 +1852,6 @@
     <t>Seattle, Washington</t>
   </si>
   <si>
-    <t>USD 75000.00 - 90000.00/year</t>
-  </si>
-  <si>
     <t>https://www.idealist.org/en/nonprofit-job/d65e6c73dcac4816acfdd874c81af7db-manager-of-communications-and-marketing-washington-state-dental-association-seattle</t>
   </si>
   <si>
@@ -1684,6 +1873,21 @@
     <t>https://www.idealist.org/en/nonprofit-job/5678c0766c9547669d8f90e7bd9c0e64-manager-of-violence-prevention-programs-worcester-youth-center-inc-worcester</t>
   </si>
   <si>
+    <t>Manager Of Youth Programs</t>
+  </si>
+  <si>
+    <t>Live Out Loud (New York based)</t>
+  </si>
+  <si>
+    <t>USD 65000.00 - 70000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Education, Lgbtq</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/832d02ffde394c91bcbfec9ddc1ec463-manager-of-youth-programs-live-out-loud-new-york-based-new-york</t>
+  </si>
+  <si>
     <t>Manager, New Cities, What Works Cities</t>
   </si>
   <si>
@@ -1819,6 +2023,24 @@
     <t>https://www.idealist.org/en/nonprofit-job/7848a452845b4b8d8f47d14b343775c2-part-time-administrative-assistant-pennsylvania-state-university-evidence-to-impact-collaborative-state-college</t>
   </si>
   <si>
+    <t>Philanthropy Manager</t>
+  </si>
+  <si>
+    <t>Sharpen Recovery</t>
+  </si>
+  <si>
+    <t>Houston, Texas</t>
+  </si>
+  <si>
+    <t>USD 45000.00 - 55000.00/year</t>
+  </si>
+  <si>
+    <t>Substance Abuse Addiction</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/d9b25b0a74ff4bba9c9a3b02f1ca0972-philanthropy-manager-sharpen-recovery-houston</t>
+  </si>
+  <si>
     <t>Policy Analyst or Senior Policy Analyst - State Programming</t>
   </si>
   <si>
@@ -1870,6 +2092,21 @@
     <t>https://www.idealist.org/en/nonprofit-job/a5f58945bb7e4e87910acf8a3af33f92-program-associate-americorps-workforce-development-national-council-on-aging-wheeling</t>
   </si>
   <si>
+    <t>PROGRAM ASSOCIATE, GOVERNORS ISLAND ARTS</t>
+  </si>
+  <si>
+    <t>Trust for Governors Island</t>
+  </si>
+  <si>
+    <t>USD 70000.00 - 75000.00/year</t>
+  </si>
+  <si>
+    <t>Arts Music, Community Development, Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/fb3fca5ca3154c33aefaf99c7ab3bdb1-program-associate-governors-island-arts-trust-for-governors-island-new-york</t>
+  </si>
+  <si>
     <t>Program Coordinator</t>
   </si>
   <si>
@@ -1879,6 +2116,21 @@
     <t>https://www.idealist.org/en/nonprofit-job/2619400d326a4229b68b36a60ef142d9-program-coordinator-partnership-for-after-school-education-pase-new-york</t>
   </si>
   <si>
+    <t>Appalachian Promise Alliance</t>
+  </si>
+  <si>
+    <t>BRISTOL, Tennessee</t>
+  </si>
+  <si>
+    <t>USD 13000.00 - 13000.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Economic Development, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/5c00d844f7a742bea480f10d3d5ba209-program-coordinator-appalachian-promise-alliance-bristol</t>
+  </si>
+  <si>
     <t>Program Instructor</t>
   </si>
   <si>
@@ -1897,9 +2149,6 @@
     <t>Program Manager</t>
   </si>
   <si>
-    <t>USD 65000.00 - 70000.00/year</t>
-  </si>
-  <si>
     <t>https://www.idealist.org/en/nonprofit-job/0b74c12271c8404ea2621e53a5686649-program-manager-weeksville-heritage-center-brooklyn</t>
   </si>
   <si>
@@ -1909,9 +2158,6 @@
     <t>City of Berkeley</t>
   </si>
   <si>
-    <t>Berkeley, California</t>
-  </si>
-  <si>
     <t>USD 152532.43 - 184582.11/year</t>
   </si>
   <si>
@@ -1921,6 +2167,18 @@
     <t>https://www.idealist.org/en/government-job/dfce5477222346fdb3efa785037b84a2-program-manager-ii-city-of-berkeley-berkeley</t>
   </si>
   <si>
+    <t>Project Manager</t>
+  </si>
+  <si>
+    <t>USD 10920.00 - 10920.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Education, Children Youth</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/29d74c8fc0d346c69cb780420dba5ace-project-manager-appalachian-promise-alliance-bristol</t>
+  </si>
+  <si>
     <t>Projects Specialist</t>
   </si>
   <si>
@@ -1939,6 +2197,21 @@
     <t>https://www.idealist.org/en/nonprofit-job/19bb4b3fdc9145e8978caf71f3ef85d6-projects-specialist-pennsylvania-cdfi-network-philadelphia</t>
   </si>
   <si>
+    <t>Research Analyst</t>
+  </si>
+  <si>
+    <t>Action Research</t>
+  </si>
+  <si>
+    <t>USD 61000.00 - 75000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Policy, Research Social Science</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/consultant-job/e84220caff94433da5d2df952480c8f9-research-analyst-action-research-kings-county</t>
+  </si>
+  <si>
     <t>Resident Ranger &amp; Land Steward</t>
   </si>
   <si>
@@ -1957,6 +2230,18 @@
     <t>https://www.idealist.org/en/nonprofit-job/dba265bbddec4e589a51e0a9dbb60889-resident-ranger-land-steward-hale-education-westwood</t>
   </si>
   <si>
+    <t>Senior Associate Director, Prospect Management and Portfolio Strategy</t>
+  </si>
+  <si>
+    <t>Columbia University, Office of Alumni Relations and Development</t>
+  </si>
+  <si>
+    <t>USD 90000.00 - 100000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/bad9baa3bcf94f81b479b7c9f124acd3-senior-associate-director-prospect-management-and-portfolio-strategy-columbia-university-office-of-alumni-relations-and-development-new-york</t>
+  </si>
+  <si>
     <t>Senior Associate, Broadband Initiative</t>
   </si>
   <si>
@@ -1978,6 +2263,30 @@
     <t>https://www.idealist.org/en/nonprofit-job/0bc4ce00a98d40098e7ed4cffc307154-senior-campaign-director-530a-initiatives-nyc-kids-rise-long-island-city</t>
   </si>
   <si>
+    <t>Senior Communications Manager, Ending Ocean Plastics</t>
+  </si>
+  <si>
+    <t>Climate Change, Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/ec587886f28342f3929531324260ba18-senior-communications-manager-ending-ocean-plastics-ocean-conservancy-washington</t>
+  </si>
+  <si>
+    <t>Senior Coordinator, Operations &amp; Events</t>
+  </si>
+  <si>
+    <t>Women In Film Los Angeles</t>
+  </si>
+  <si>
+    <t>USD 27.00 - 31.00/hour</t>
+  </si>
+  <si>
+    <t>Arts Music, Media, Women</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/64e3b6c3f38940d3a18dc9ed36eed312-senior-coordinator-operations-events-women-in-film-los-angeles-los-angeles</t>
+  </si>
+  <si>
     <t>Senior Coordinator, Resource Development</t>
   </si>
   <si>
@@ -1990,6 +2299,21 @@
     <t>https://www.idealist.org/en/nonprofit-job/227492a5f5df41dba072a409ed745055-senior-coordinator-resource-development-good360-alexandria</t>
   </si>
   <si>
+    <t>Senior Finance Manager</t>
+  </si>
+  <si>
+    <t>Pacific Institute for Studies in Development, Environment, and Security</t>
+  </si>
+  <si>
+    <t>USD 78400.00 - 138000.00/year</t>
+  </si>
+  <si>
+    <t>Agriculture, Climate Change, Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/f48808552576421cb673029b010e1885-senior-finance-manager-pacific-institute-for-studies-in-development-environment-and-security-oakland</t>
+  </si>
+  <si>
     <t>Senior International Student Advisor</t>
   </si>
   <si>
@@ -2002,6 +2326,21 @@
     <t>https://www.idealist.org/en/nonprofit-job/fdda36be99164adabbe644a64ec7d9bf-senior-international-student-advisor-school-of-visual-arts-new-york</t>
   </si>
   <si>
+    <t>Senior Manager of Campaigns and Events</t>
+  </si>
+  <si>
+    <t>The Acceleration Project</t>
+  </si>
+  <si>
+    <t>Remote (New York)</t>
+  </si>
+  <si>
+    <t>USD 70000.00 - 80000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/2def05a652cb43709c384b960c178a68-senior-manager-of-campaigns-and-events-the-acceleration-project-scarsdale</t>
+  </si>
+  <si>
     <t>Senior Marketing Manager</t>
   </si>
   <si>
@@ -2047,6 +2386,21 @@
     <t>https://www.idealist.org/en/nonprofit-job/c33245db486a44f8b0f402e1b5fb52d0-senior-specialist-building-science-analysis-institute-for-market-transformation-washington</t>
   </si>
   <si>
+    <t>Staff Attorney</t>
+  </si>
+  <si>
+    <t>Illinois Prison Project</t>
+  </si>
+  <si>
+    <t>USD 100059.00 - 130080.00/year</t>
+  </si>
+  <si>
+    <t>Legal Assistance, Prison Reform, Race Ethnicity</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/7abc0dc0b69b4f4384cca9b98b131389-staff-attorney-illinois-prison-project-chicago</t>
+  </si>
+  <si>
     <t>Staff Attorney - Housing &amp; Habitability</t>
   </si>
   <si>
@@ -2062,6 +2416,42 @@
     <t>https://www.idealist.org/en/nonprofit-job/c5b6877100034774983d59150afa5c6c-staff-attorney-housing-habitability-legal-clinic-for-the-disabled-philadelphia</t>
   </si>
   <si>
+    <t>Staff Attorney or Senior/Supervising Staff Attorney</t>
+  </si>
+  <si>
+    <t>Rutgers Immigrant Rights Clinic</t>
+  </si>
+  <si>
+    <t>Newark, NJ</t>
+  </si>
+  <si>
+    <t>USD 85000.00/year</t>
+  </si>
+  <si>
+    <t>Immigrants Or Refugees, Legal Assistance, Human Rights Civil Liberties</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/03bc029bad114750b3992473ccbde7cf-staff-attorney-or-seniorsupervising-staff-attorney-rutgers-immigrant-rights-clinic-newark</t>
+  </si>
+  <si>
+    <t>Strategic Coordinator Part Time</t>
+  </si>
+  <si>
+    <t>Secular Humanist Jewish Circle</t>
+  </si>
+  <si>
+    <t>Tucson, Arizona</t>
+  </si>
+  <si>
+    <t>USD 30.00/hour</t>
+  </si>
+  <si>
+    <t>Community Development, Religion Spirituality</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/209c0ce8f4f8480884e81f897439cc4e-strategic-coordinator-part-time-secular-humanist-jewish-circle-tucson</t>
+  </si>
+  <si>
     <t>Supervisor of Volunteer Advocates</t>
   </si>
   <si>
@@ -2092,6 +2482,21 @@
     <t>https://www.idealist.org/en/nonprofit-job/96c0bc219eee4f64b69b2e12d9b23d60-teach-english-in-honduras-housing-benefits-stipend-provided-one-thousand-schools-el-progreso</t>
   </si>
   <si>
+    <t>Vice President for External Communications and Engagement</t>
+  </si>
+  <si>
+    <t>The College Foundation of the University of Virginia</t>
+  </si>
+  <si>
+    <t>Charlottesville, Virginia</t>
+  </si>
+  <si>
+    <t>USD 185000.00 - 220000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/0d774797b76a4e2494c3f7ae584471ee-vice-president-for-external-communications-and-engagement-the-college-foundation-of-the-university-of-virginia-charlottesville</t>
+  </si>
+  <si>
     <t>Youth Services Director</t>
   </si>
   <si>
@@ -2102,9 +2507,6 @@
   </si>
   <si>
     <t>USD 50000.00 - 60000.00/year</t>
-  </si>
-  <si>
-    <t>Arts Music, Education, Health Medicine</t>
   </si>
   <si>
     <t>https://www.idealist.org/en/consultant-job/6ae8cb573514499bb42db318a057ae60-youth-services-director-armstrong-mcguire-associates-conover</t>
@@ -3479,7 +3881,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H101"/>
+  <dimension ref="A1:H129"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -3621,10 +4023,10 @@
         <v>236</v>
       </c>
       <c r="D6" t="s">
+        <v>212</v>
+      </c>
+      <c r="E6" t="s">
         <v>237</v>
-      </c>
-      <c r="E6" t="s">
-        <v>219</v>
       </c>
       <c r="F6" t="s">
         <v>238</v>
@@ -3641,151 +4043,151 @@
         <v>241</v>
       </c>
       <c r="C7" t="s">
-        <v>218</v>
+        <v>242</v>
       </c>
       <c r="D7" t="s">
         <v>212</v>
       </c>
       <c r="E7" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="F7" t="s">
-        <v>219</v>
+        <v>244</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="B8" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="C8" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="D8" t="s">
-        <v>212</v>
+        <v>249</v>
       </c>
       <c r="E8" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="F8" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="B9" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="C9" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="D9" t="s">
-        <v>212</v>
+        <v>256</v>
       </c>
       <c r="E9" t="s">
-        <v>253</v>
+        <v>225</v>
       </c>
       <c r="F9" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="B10" t="s">
-        <v>251</v>
+        <v>260</v>
       </c>
       <c r="C10" t="s">
-        <v>252</v>
+        <v>224</v>
       </c>
       <c r="D10" t="s">
         <v>212</v>
       </c>
       <c r="E10" t="s">
-        <v>253</v>
+        <v>261</v>
       </c>
       <c r="F10" t="s">
-        <v>257</v>
+        <v>225</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="B11" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="C11" t="s">
-        <v>261</v>
+        <v>218</v>
       </c>
       <c r="D11" t="s">
-        <v>262</v>
+        <v>212</v>
       </c>
       <c r="E11" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="F11" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="B12" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="C12" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="D12" t="s">
-        <v>237</v>
+        <v>212</v>
       </c>
       <c r="E12" t="s">
-        <v>219</v>
+        <v>271</v>
       </c>
       <c r="F12" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
+        <v>274</v>
+      </c>
+      <c r="B13" t="s">
+        <v>269</v>
+      </c>
+      <c r="C13" t="s">
+        <v>270</v>
+      </c>
+      <c r="D13" t="s">
+        <v>212</v>
+      </c>
+      <c r="E13" t="s">
         <v>271</v>
-      </c>
-      <c r="B13" t="s">
-        <v>272</v>
-      </c>
-      <c r="C13" t="s">
-        <v>273</v>
-      </c>
-      <c r="D13" t="s">
-        <v>212</v>
-      </c>
-      <c r="E13" t="s">
-        <v>274</v>
       </c>
       <c r="F13" t="s">
         <v>275</v>
@@ -3802,36 +4204,36 @@
         <v>278</v>
       </c>
       <c r="C14" t="s">
-        <v>252</v>
+        <v>279</v>
       </c>
       <c r="D14" t="s">
-        <v>212</v>
+        <v>280</v>
       </c>
       <c r="E14" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="F14" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="B15" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="C15" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="D15" t="s">
-        <v>285</v>
+        <v>256</v>
       </c>
       <c r="E15" t="s">
-        <v>286</v>
+        <v>225</v>
       </c>
       <c r="F15" t="s">
         <v>287</v>
@@ -3845,151 +4247,151 @@
         <v>289</v>
       </c>
       <c r="B16" t="s">
-        <v>283</v>
+        <v>290</v>
       </c>
       <c r="C16" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="D16" t="s">
-        <v>285</v>
+        <v>212</v>
       </c>
       <c r="E16" t="s">
-        <v>286</v>
+        <v>292</v>
       </c>
       <c r="F16" t="s">
-        <v>287</v>
+        <v>293</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="B17" t="s">
-        <v>283</v>
+        <v>296</v>
       </c>
       <c r="C17" t="s">
-        <v>293</v>
+        <v>270</v>
       </c>
       <c r="D17" t="s">
-        <v>262</v>
+        <v>212</v>
       </c>
       <c r="E17" t="s">
-        <v>286</v>
+        <v>297</v>
       </c>
       <c r="F17" t="s">
-        <v>287</v>
+        <v>298</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>295</v>
+        <v>300</v>
       </c>
       <c r="B18" t="s">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="C18" t="s">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c r="D18" t="s">
-        <v>212</v>
+        <v>303</v>
       </c>
       <c r="E18" t="s">
-        <v>298</v>
+        <v>304</v>
       </c>
       <c r="F18" t="s">
-        <v>299</v>
+        <v>305</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
+        <v>307</v>
+      </c>
+      <c r="B19" t="s">
         <v>301</v>
       </c>
-      <c r="B19" t="s">
-        <v>302</v>
-      </c>
       <c r="C19" t="s">
-        <v>17</v>
+        <v>308</v>
       </c>
       <c r="D19" t="s">
-        <v>212</v>
+        <v>303</v>
       </c>
       <c r="E19" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="F19" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="B20" t="s">
-        <v>307</v>
+        <v>301</v>
       </c>
       <c r="C20" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="D20" t="s">
-        <v>212</v>
+        <v>280</v>
       </c>
       <c r="E20" t="s">
-        <v>309</v>
+        <v>304</v>
       </c>
       <c r="F20" t="s">
-        <v>310</v>
+        <v>305</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B21" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C21" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="D21" t="s">
         <v>212</v>
       </c>
       <c r="E21" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="F21" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B22" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C22" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="D22" t="s">
-        <v>321</v>
+        <v>212</v>
       </c>
       <c r="E22" t="s">
         <v>322</v>
@@ -4009,53 +4411,53 @@
         <v>326</v>
       </c>
       <c r="C23" t="s">
+        <v>17</v>
+      </c>
+      <c r="D23" t="s">
+        <v>212</v>
+      </c>
+      <c r="E23" t="s">
         <v>327</v>
       </c>
-      <c r="D23" t="s">
-        <v>321</v>
-      </c>
-      <c r="E23" t="s">
+      <c r="F23" t="s">
         <v>328</v>
       </c>
-      <c r="F23" t="s">
+      <c r="H23" s="2" t="s">
         <v>329</v>
-      </c>
-      <c r="H23" s="2" t="s">
-        <v>330</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
+        <v>330</v>
+      </c>
+      <c r="B24" t="s">
         <v>331</v>
       </c>
-      <c r="B24" t="s">
+      <c r="C24" t="s">
         <v>332</v>
       </c>
-      <c r="C24" t="s">
+      <c r="D24" t="s">
+        <v>212</v>
+      </c>
+      <c r="E24" t="s">
         <v>333</v>
       </c>
-      <c r="D24" t="s">
-        <v>212</v>
-      </c>
-      <c r="E24" t="s">
+      <c r="F24" t="s">
         <v>334</v>
       </c>
-      <c r="F24" t="s">
+      <c r="H24" s="2" t="s">
         <v>335</v>
-      </c>
-      <c r="H24" s="2" t="s">
-        <v>336</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
+        <v>336</v>
+      </c>
+      <c r="B25" t="s">
         <v>337</v>
       </c>
-      <c r="B25" t="s">
+      <c r="C25" t="s">
         <v>338</v>
-      </c>
-      <c r="C25" t="s">
-        <v>246</v>
       </c>
       <c r="D25" t="s">
         <v>212</v>
@@ -4081,7 +4483,7 @@
         <v>344</v>
       </c>
       <c r="D26" t="s">
-        <v>212</v>
+        <v>249</v>
       </c>
       <c r="E26" t="s">
         <v>345</v>
@@ -4101,295 +4503,295 @@
         <v>349</v>
       </c>
       <c r="C27" t="s">
-        <v>218</v>
+        <v>350</v>
       </c>
       <c r="D27" t="s">
-        <v>212</v>
+        <v>249</v>
       </c>
       <c r="E27" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="F27" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B28" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C28" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="D28" t="s">
         <v>212</v>
       </c>
       <c r="E28" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="F28" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B29" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C29" t="s">
-        <v>252</v>
+        <v>218</v>
       </c>
       <c r="D29" t="s">
         <v>212</v>
       </c>
       <c r="E29" t="s">
-        <v>263</v>
+        <v>362</v>
       </c>
       <c r="F29" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="B30" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="C30" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="D30" t="s">
         <v>212</v>
       </c>
       <c r="E30" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="F30" t="s">
-        <v>219</v>
+        <v>369</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="B31" t="s">
-        <v>364</v>
+        <v>372</v>
       </c>
       <c r="C31" t="s">
-        <v>365</v>
+        <v>224</v>
       </c>
       <c r="D31" t="s">
         <v>212</v>
       </c>
       <c r="E31" t="s">
-        <v>366</v>
+        <v>373</v>
       </c>
       <c r="F31" t="s">
-        <v>219</v>
+        <v>374</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>369</v>
+        <v>375</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>370</v>
+        <v>376</v>
       </c>
       <c r="B32" t="s">
-        <v>371</v>
+        <v>377</v>
       </c>
       <c r="C32" t="s">
-        <v>252</v>
+        <v>378</v>
       </c>
       <c r="D32" t="s">
         <v>212</v>
       </c>
       <c r="E32" t="s">
-        <v>263</v>
+        <v>379</v>
       </c>
       <c r="F32" t="s">
-        <v>219</v>
+        <v>380</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>372</v>
+        <v>381</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>373</v>
+        <v>382</v>
       </c>
       <c r="B33" t="s">
-        <v>374</v>
+        <v>383</v>
       </c>
       <c r="C33" t="s">
-        <v>252</v>
+        <v>270</v>
       </c>
       <c r="D33" t="s">
         <v>212</v>
       </c>
       <c r="E33" t="s">
-        <v>375</v>
+        <v>281</v>
       </c>
       <c r="F33" t="s">
-        <v>219</v>
+        <v>384</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>376</v>
+        <v>385</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>377</v>
+        <v>386</v>
       </c>
       <c r="B34" t="s">
-        <v>378</v>
+        <v>387</v>
       </c>
       <c r="C34" t="s">
-        <v>379</v>
+        <v>388</v>
       </c>
       <c r="D34" t="s">
         <v>212</v>
       </c>
       <c r="E34" t="s">
-        <v>380</v>
+        <v>389</v>
       </c>
       <c r="F34" t="s">
-        <v>381</v>
+        <v>225</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>382</v>
+        <v>390</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>383</v>
+        <v>391</v>
       </c>
       <c r="B35" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="C35" t="s">
-        <v>314</v>
+        <v>388</v>
       </c>
       <c r="D35" t="s">
-        <v>321</v>
+        <v>212</v>
       </c>
       <c r="E35" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="F35" t="s">
-        <v>386</v>
+        <v>225</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>387</v>
+        <v>392</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>383</v>
+        <v>393</v>
       </c>
       <c r="B36" t="s">
-        <v>388</v>
+        <v>394</v>
       </c>
       <c r="C36" t="s">
-        <v>246</v>
+        <v>270</v>
       </c>
       <c r="D36" t="s">
-        <v>237</v>
+        <v>212</v>
       </c>
       <c r="E36" t="s">
-        <v>389</v>
+        <v>281</v>
       </c>
       <c r="F36" t="s">
-        <v>390</v>
+        <v>225</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>391</v>
+        <v>395</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="B37" t="s">
-        <v>278</v>
+        <v>397</v>
       </c>
       <c r="C37" t="s">
-        <v>252</v>
+        <v>270</v>
       </c>
       <c r="D37" t="s">
         <v>212</v>
       </c>
       <c r="E37" t="s">
-        <v>393</v>
+        <v>398</v>
       </c>
       <c r="F37" t="s">
-        <v>280</v>
+        <v>225</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>394</v>
+        <v>399</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>395</v>
+        <v>400</v>
       </c>
       <c r="B38" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="C38" t="s">
-        <v>284</v>
+        <v>402</v>
       </c>
       <c r="D38" t="s">
-        <v>321</v>
+        <v>212</v>
       </c>
       <c r="E38" t="s">
-        <v>397</v>
+        <v>403</v>
       </c>
       <c r="F38" t="s">
-        <v>398</v>
+        <v>404</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>399</v>
+        <v>405</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>400</v>
+        <v>406</v>
       </c>
       <c r="B39" t="s">
-        <v>401</v>
+        <v>407</v>
       </c>
       <c r="C39" t="s">
-        <v>402</v>
+        <v>338</v>
       </c>
       <c r="D39" t="s">
-        <v>212</v>
+        <v>249</v>
       </c>
       <c r="E39" t="s">
-        <v>403</v>
+        <v>408</v>
       </c>
       <c r="F39" t="s">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>405</v>
+        <v>410</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
@@ -4397,42 +4799,42 @@
         <v>406</v>
       </c>
       <c r="B40" t="s">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="C40" t="s">
-        <v>408</v>
+        <v>218</v>
       </c>
       <c r="D40" t="s">
-        <v>212</v>
+        <v>256</v>
       </c>
       <c r="E40" t="s">
-        <v>409</v>
+        <v>250</v>
       </c>
       <c r="F40" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="B41" t="s">
-        <v>413</v>
+        <v>296</v>
       </c>
       <c r="C41" t="s">
-        <v>261</v>
+        <v>270</v>
       </c>
       <c r="D41" t="s">
         <v>212</v>
       </c>
       <c r="E41" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="F41" t="s">
-        <v>415</v>
+        <v>298</v>
       </c>
       <c r="H41" s="2" t="s">
         <v>416</v>
@@ -4446,39 +4848,39 @@
         <v>418</v>
       </c>
       <c r="C42" t="s">
+        <v>302</v>
+      </c>
+      <c r="D42" t="s">
+        <v>249</v>
+      </c>
+      <c r="E42" t="s">
         <v>419</v>
       </c>
-      <c r="D42" t="s">
-        <v>212</v>
-      </c>
-      <c r="E42" t="s">
+      <c r="F42" t="s">
         <v>420</v>
       </c>
-      <c r="F42" t="s">
+      <c r="H42" s="2" t="s">
         <v>421</v>
-      </c>
-      <c r="H42" s="2" t="s">
-        <v>422</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
+        <v>422</v>
+      </c>
+      <c r="B43" t="s">
         <v>423</v>
       </c>
-      <c r="B43" t="s">
-        <v>313</v>
-      </c>
       <c r="C43" t="s">
-        <v>314</v>
+        <v>424</v>
       </c>
       <c r="D43" t="s">
         <v>212</v>
       </c>
       <c r="E43" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="F43" t="s">
-        <v>425</v>
+        <v>220</v>
       </c>
       <c r="H43" s="2" t="s">
         <v>426</v>
@@ -4492,134 +4894,134 @@
         <v>428</v>
       </c>
       <c r="C44" t="s">
-        <v>218</v>
+        <v>429</v>
       </c>
       <c r="D44" t="s">
         <v>212</v>
       </c>
       <c r="E44" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="F44" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>427</v>
+        <v>433</v>
       </c>
       <c r="B45" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="C45" t="s">
-        <v>433</v>
+        <v>279</v>
       </c>
       <c r="D45" t="s">
         <v>212</v>
       </c>
       <c r="E45" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="F45" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="H45" s="2" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>427</v>
+        <v>438</v>
       </c>
       <c r="B46" t="s">
-        <v>260</v>
+        <v>439</v>
       </c>
       <c r="C46" t="s">
-        <v>246</v>
+        <v>440</v>
       </c>
       <c r="D46" t="s">
         <v>212</v>
       </c>
       <c r="E46" t="s">
-        <v>437</v>
+        <v>441</v>
       </c>
       <c r="F46" t="s">
-        <v>264</v>
+        <v>442</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>438</v>
+        <v>443</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>439</v>
+        <v>444</v>
       </c>
       <c r="B47" t="s">
-        <v>440</v>
+        <v>445</v>
       </c>
       <c r="C47" t="s">
-        <v>441</v>
+        <v>446</v>
       </c>
       <c r="D47" t="s">
         <v>212</v>
       </c>
       <c r="E47" t="s">
-        <v>442</v>
+        <v>447</v>
       </c>
       <c r="F47" t="s">
-        <v>280</v>
+        <v>251</v>
       </c>
       <c r="H47" s="2" t="s">
-        <v>443</v>
+        <v>448</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>444</v>
+        <v>449</v>
       </c>
       <c r="B48" t="s">
-        <v>445</v>
+        <v>337</v>
       </c>
       <c r="C48" t="s">
-        <v>446</v>
+        <v>338</v>
       </c>
       <c r="D48" t="s">
         <v>212</v>
       </c>
       <c r="E48" t="s">
-        <v>219</v>
+        <v>450</v>
       </c>
       <c r="F48" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="H48" s="2" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="B49" t="s">
-        <v>450</v>
+        <v>454</v>
       </c>
       <c r="C49" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="D49" t="s">
         <v>212</v>
       </c>
       <c r="E49" t="s">
-        <v>451</v>
+        <v>455</v>
       </c>
       <c r="F49" t="s">
-        <v>219</v>
+        <v>456</v>
       </c>
       <c r="H49" s="2" t="s">
-        <v>452</v>
+        <v>457</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
@@ -4627,111 +5029,111 @@
         <v>453</v>
       </c>
       <c r="B50" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="C50" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="D50" t="s">
         <v>212</v>
       </c>
       <c r="E50" t="s">
-        <v>456</v>
+        <v>460</v>
       </c>
       <c r="F50" t="s">
-        <v>457</v>
+        <v>461</v>
       </c>
       <c r="H50" s="2" t="s">
-        <v>458</v>
+        <v>462</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>459</v>
+        <v>453</v>
       </c>
       <c r="B51" t="s">
-        <v>338</v>
+        <v>278</v>
       </c>
       <c r="C51" t="s">
-        <v>246</v>
+        <v>218</v>
       </c>
       <c r="D51" t="s">
         <v>212</v>
       </c>
       <c r="E51" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="F51" t="s">
-        <v>340</v>
+        <v>282</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="B52" t="s">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="C52" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="D52" t="s">
         <v>212</v>
       </c>
       <c r="E52" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="F52" t="s">
-        <v>466</v>
+        <v>298</v>
       </c>
       <c r="H52" s="2" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="B53" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="C53" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="D53" t="s">
         <v>212</v>
       </c>
       <c r="E53" t="s">
-        <v>471</v>
+        <v>225</v>
       </c>
       <c r="F53" t="s">
-        <v>219</v>
+        <v>473</v>
       </c>
       <c r="H53" s="2" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="B54" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="C54" t="s">
-        <v>475</v>
+        <v>224</v>
       </c>
       <c r="D54" t="s">
         <v>212</v>
       </c>
       <c r="E54" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="F54" t="s">
-        <v>477</v>
+        <v>225</v>
       </c>
       <c r="H54" s="2" t="s">
         <v>478</v>
@@ -4751,33 +5153,33 @@
         <v>212</v>
       </c>
       <c r="E55" t="s">
-        <v>309</v>
+        <v>482</v>
       </c>
       <c r="F55" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="H55" s="2" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>52</v>
+        <v>485</v>
       </c>
       <c r="B56" t="s">
-        <v>484</v>
+        <v>361</v>
       </c>
       <c r="C56" t="s">
-        <v>246</v>
+        <v>218</v>
       </c>
       <c r="D56" t="s">
         <v>212</v>
       </c>
       <c r="E56" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="F56" t="s">
-        <v>486</v>
+        <v>363</v>
       </c>
       <c r="H56" s="2" t="s">
         <v>487</v>
@@ -4785,13 +5187,13 @@
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>52</v>
+        <v>488</v>
       </c>
       <c r="B57" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="C57" t="s">
-        <v>489</v>
+        <v>218</v>
       </c>
       <c r="D57" t="s">
         <v>212</v>
@@ -4817,372 +5219,372 @@
         <v>495</v>
       </c>
       <c r="D58" t="s">
-        <v>321</v>
+        <v>212</v>
       </c>
       <c r="E58" t="s">
         <v>496</v>
       </c>
       <c r="F58" t="s">
-        <v>386</v>
+        <v>497</v>
       </c>
       <c r="H58" s="2" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="B59" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="C59" t="s">
-        <v>252</v>
+        <v>501</v>
       </c>
       <c r="D59" t="s">
         <v>212</v>
       </c>
       <c r="E59" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="F59" t="s">
-        <v>501</v>
+        <v>225</v>
       </c>
       <c r="H59" s="2" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="B60" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="C60" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="D60" t="s">
-        <v>321</v>
+        <v>212</v>
       </c>
       <c r="E60" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="F60" t="s">
-        <v>404</v>
+        <v>508</v>
       </c>
       <c r="H60" s="2" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="B61" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="C61" t="s">
-        <v>464</v>
+        <v>211</v>
       </c>
       <c r="D61" t="s">
         <v>212</v>
       </c>
       <c r="E61" t="s">
-        <v>485</v>
+        <v>512</v>
       </c>
       <c r="F61" t="s">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="H61" s="2" t="s">
-        <v>511</v>
+        <v>514</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>512</v>
+        <v>515</v>
       </c>
       <c r="B62" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="C62" t="s">
-        <v>252</v>
+        <v>517</v>
       </c>
       <c r="D62" t="s">
         <v>212</v>
       </c>
       <c r="E62" t="s">
-        <v>514</v>
+        <v>518</v>
       </c>
       <c r="F62" t="s">
-        <v>515</v>
+        <v>519</v>
       </c>
       <c r="H62" s="2" t="s">
-        <v>516</v>
+        <v>520</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>517</v>
+        <v>521</v>
       </c>
       <c r="B63" t="s">
-        <v>518</v>
+        <v>511</v>
       </c>
       <c r="C63" t="s">
-        <v>252</v>
+        <v>211</v>
       </c>
       <c r="D63" t="s">
         <v>212</v>
       </c>
       <c r="E63" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="F63" t="s">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="H63" s="2" t="s">
-        <v>521</v>
+        <v>524</v>
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="B64" t="s">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="C64" t="s">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="D64" t="s">
         <v>212</v>
       </c>
       <c r="E64" t="s">
-        <v>525</v>
+        <v>333</v>
       </c>
       <c r="F64" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="H64" s="2" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>528</v>
+        <v>52</v>
       </c>
       <c r="B65" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="C65" t="s">
-        <v>530</v>
+        <v>218</v>
       </c>
       <c r="D65" t="s">
-        <v>285</v>
+        <v>212</v>
       </c>
       <c r="E65" t="s">
-        <v>356</v>
+        <v>531</v>
       </c>
       <c r="F65" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="H65" s="2" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>533</v>
+        <v>52</v>
       </c>
       <c r="B66" t="s">
-        <v>374</v>
+        <v>534</v>
       </c>
       <c r="C66" t="s">
-        <v>252</v>
+        <v>535</v>
       </c>
       <c r="D66" t="s">
         <v>212</v>
       </c>
       <c r="E66" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="F66" t="s">
-        <v>219</v>
+        <v>537</v>
       </c>
       <c r="H66" s="2" t="s">
-        <v>535</v>
+        <v>538</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="B67" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
       <c r="C67" t="s">
-        <v>538</v>
+        <v>541</v>
       </c>
       <c r="D67" t="s">
-        <v>212</v>
+        <v>249</v>
       </c>
       <c r="E67" t="s">
-        <v>539</v>
+        <v>542</v>
       </c>
       <c r="F67" t="s">
-        <v>540</v>
+        <v>409</v>
       </c>
       <c r="H67" s="2" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="B68" t="s">
-        <v>326</v>
+        <v>545</v>
       </c>
       <c r="C68" t="s">
-        <v>327</v>
+        <v>546</v>
       </c>
       <c r="D68" t="s">
         <v>212</v>
       </c>
       <c r="E68" t="s">
-        <v>543</v>
+        <v>547</v>
       </c>
       <c r="F68" t="s">
-        <v>329</v>
+        <v>548</v>
       </c>
       <c r="H68" s="2" t="s">
-        <v>544</v>
+        <v>549</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>545</v>
+        <v>550</v>
       </c>
       <c r="B69" t="s">
-        <v>546</v>
+        <v>551</v>
       </c>
       <c r="C69" t="s">
-        <v>547</v>
+        <v>270</v>
       </c>
       <c r="D69" t="s">
         <v>212</v>
       </c>
       <c r="E69" t="s">
-        <v>548</v>
+        <v>552</v>
       </c>
       <c r="F69" t="s">
-        <v>482</v>
+        <v>553</v>
       </c>
       <c r="H69" s="2" t="s">
-        <v>549</v>
+        <v>554</v>
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>550</v>
+        <v>555</v>
       </c>
       <c r="B70" t="s">
-        <v>551</v>
+        <v>556</v>
       </c>
       <c r="C70" t="s">
-        <v>552</v>
+        <v>557</v>
       </c>
       <c r="D70" t="s">
-        <v>212</v>
+        <v>249</v>
       </c>
       <c r="E70" t="s">
-        <v>553</v>
+        <v>558</v>
       </c>
       <c r="F70" t="s">
-        <v>554</v>
+        <v>220</v>
       </c>
       <c r="H70" s="2" t="s">
-        <v>555</v>
+        <v>559</v>
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="B71" t="s">
-        <v>557</v>
+        <v>561</v>
       </c>
       <c r="C71" t="s">
-        <v>246</v>
+        <v>495</v>
       </c>
       <c r="D71" t="s">
         <v>212</v>
       </c>
       <c r="E71" t="s">
-        <v>558</v>
+        <v>531</v>
       </c>
       <c r="F71" t="s">
-        <v>559</v>
+        <v>562</v>
       </c>
       <c r="H71" s="2" t="s">
-        <v>560</v>
+        <v>563</v>
       </c>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>561</v>
+        <v>564</v>
       </c>
       <c r="B72" t="s">
-        <v>562</v>
+        <v>565</v>
       </c>
       <c r="C72" t="s">
-        <v>563</v>
+        <v>270</v>
       </c>
       <c r="D72" t="s">
         <v>212</v>
       </c>
       <c r="E72" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="F72" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="H72" s="2" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="B73" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="C73" t="s">
-        <v>481</v>
+        <v>270</v>
       </c>
       <c r="D73" t="s">
         <v>212</v>
       </c>
       <c r="E73" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="F73" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="H73" s="2" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>572</v>
+        <v>569</v>
       </c>
       <c r="B74" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="C74" t="s">
-        <v>574</v>
+        <v>472</v>
       </c>
       <c r="D74" t="s">
         <v>212</v>
@@ -5202,111 +5604,111 @@
         <v>578</v>
       </c>
       <c r="B75" t="s">
-        <v>307</v>
+        <v>579</v>
       </c>
       <c r="C75" t="s">
-        <v>579</v>
+        <v>495</v>
       </c>
       <c r="D75" t="s">
         <v>212</v>
       </c>
       <c r="E75" t="s">
+        <v>281</v>
+      </c>
+      <c r="F75" t="s">
         <v>580</v>
       </c>
-      <c r="F75" t="s">
+      <c r="H75" s="2" t="s">
         <v>581</v>
-      </c>
-      <c r="H75" s="2" t="s">
-        <v>582</v>
       </c>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
+        <v>582</v>
+      </c>
+      <c r="B76" t="s">
         <v>583</v>
       </c>
-      <c r="B76" t="s">
+      <c r="C76" t="s">
         <v>584</v>
       </c>
-      <c r="C76" t="s">
-        <v>481</v>
-      </c>
       <c r="D76" t="s">
         <v>212</v>
       </c>
       <c r="E76" t="s">
-        <v>219</v>
+        <v>585</v>
       </c>
       <c r="F76" t="s">
-        <v>219</v>
+        <v>586</v>
       </c>
       <c r="H76" s="2" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="B77" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="C77" t="s">
-        <v>588</v>
+        <v>58</v>
       </c>
       <c r="D77" t="s">
         <v>212</v>
       </c>
       <c r="E77" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="F77" t="s">
-        <v>501</v>
+        <v>591</v>
       </c>
       <c r="H77" s="2" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="B78" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="C78" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="D78" t="s">
-        <v>212</v>
+        <v>303</v>
       </c>
       <c r="E78" t="s">
-        <v>594</v>
+        <v>379</v>
       </c>
       <c r="F78" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="H78" s="2" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="B79" t="s">
-        <v>598</v>
+        <v>397</v>
       </c>
       <c r="C79" t="s">
-        <v>246</v>
+        <v>270</v>
       </c>
       <c r="D79" t="s">
-        <v>285</v>
+        <v>212</v>
       </c>
       <c r="E79" t="s">
-        <v>219</v>
+        <v>599</v>
       </c>
       <c r="F79" t="s">
-        <v>599</v>
+        <v>225</v>
       </c>
       <c r="H79" s="2" t="s">
         <v>600</v>
@@ -5320,502 +5722,1146 @@
         <v>602</v>
       </c>
       <c r="C80" t="s">
-        <v>464</v>
+        <v>603</v>
       </c>
       <c r="D80" t="s">
         <v>212</v>
       </c>
       <c r="E80" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="F80" t="s">
-        <v>482</v>
+        <v>605</v>
       </c>
       <c r="H80" s="2" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="B81" t="s">
-        <v>360</v>
+        <v>349</v>
       </c>
       <c r="C81" t="s">
-        <v>252</v>
+        <v>350</v>
       </c>
       <c r="D81" t="s">
         <v>212</v>
       </c>
       <c r="E81" t="s">
-        <v>606</v>
+        <v>231</v>
       </c>
       <c r="F81" t="s">
-        <v>361</v>
+        <v>352</v>
       </c>
       <c r="H81" s="2" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="B82" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="C82" t="s">
-        <v>218</v>
+        <v>611</v>
       </c>
       <c r="D82" t="s">
-        <v>237</v>
+        <v>212</v>
       </c>
       <c r="E82" t="s">
-        <v>610</v>
+        <v>575</v>
       </c>
       <c r="F82" t="s">
-        <v>299</v>
+        <v>528</v>
       </c>
       <c r="H82" s="2" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="B83" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="C83" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="D83" t="s">
-        <v>262</v>
+        <v>212</v>
       </c>
       <c r="E83" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="F83" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="H83" s="2" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="B84" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="C84" t="s">
-        <v>252</v>
+        <v>270</v>
       </c>
       <c r="D84" t="s">
         <v>212</v>
       </c>
       <c r="E84" t="s">
-        <v>375</v>
+        <v>621</v>
       </c>
       <c r="F84" t="s">
-        <v>421</v>
+        <v>622</v>
       </c>
       <c r="H84" s="2" t="s">
-        <v>620</v>
+        <v>623</v>
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>621</v>
+        <v>624</v>
       </c>
       <c r="B85" t="s">
-        <v>622</v>
+        <v>625</v>
       </c>
       <c r="C85" t="s">
-        <v>464</v>
+        <v>218</v>
       </c>
       <c r="D85" t="s">
-        <v>262</v>
+        <v>212</v>
       </c>
       <c r="E85" t="s">
-        <v>623</v>
+        <v>626</v>
       </c>
       <c r="F85" t="s">
-        <v>624</v>
+        <v>627</v>
       </c>
       <c r="H85" s="2" t="s">
-        <v>625</v>
+        <v>628</v>
       </c>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>626</v>
+        <v>629</v>
       </c>
       <c r="B86" t="s">
-        <v>454</v>
+        <v>630</v>
       </c>
       <c r="C86" t="s">
-        <v>455</v>
+        <v>631</v>
       </c>
       <c r="D86" t="s">
         <v>212</v>
       </c>
       <c r="E86" t="s">
-        <v>627</v>
+        <v>632</v>
       </c>
       <c r="F86" t="s">
-        <v>457</v>
+        <v>633</v>
       </c>
       <c r="H86" s="2" t="s">
-        <v>628</v>
+        <v>634</v>
       </c>
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>629</v>
+        <v>635</v>
       </c>
       <c r="B87" t="s">
-        <v>630</v>
+        <v>636</v>
       </c>
       <c r="C87" t="s">
-        <v>631</v>
+        <v>527</v>
       </c>
       <c r="D87" t="s">
         <v>212</v>
       </c>
       <c r="E87" t="s">
-        <v>632</v>
+        <v>637</v>
       </c>
       <c r="F87" t="s">
-        <v>633</v>
+        <v>638</v>
       </c>
       <c r="H87" s="2" t="s">
-        <v>634</v>
+        <v>639</v>
       </c>
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>635</v>
+        <v>640</v>
       </c>
       <c r="B88" t="s">
-        <v>636</v>
+        <v>641</v>
       </c>
       <c r="C88" t="s">
-        <v>637</v>
+        <v>642</v>
       </c>
       <c r="D88" t="s">
         <v>212</v>
       </c>
       <c r="E88" t="s">
-        <v>638</v>
+        <v>643</v>
       </c>
       <c r="F88" t="s">
-        <v>639</v>
+        <v>644</v>
       </c>
       <c r="H88" s="2" t="s">
-        <v>640</v>
+        <v>645</v>
       </c>
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>641</v>
+        <v>646</v>
       </c>
       <c r="B89" t="s">
-        <v>642</v>
+        <v>331</v>
       </c>
       <c r="C89" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="D89" t="s">
         <v>212</v>
       </c>
       <c r="E89" t="s">
-        <v>644</v>
+        <v>648</v>
       </c>
       <c r="F89" t="s">
-        <v>645</v>
+        <v>649</v>
       </c>
       <c r="H89" s="2" t="s">
-        <v>646</v>
+        <v>650</v>
       </c>
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>647</v>
+        <v>651</v>
       </c>
       <c r="B90" t="s">
-        <v>648</v>
+        <v>652</v>
       </c>
       <c r="C90" t="s">
-        <v>464</v>
+        <v>527</v>
       </c>
       <c r="D90" t="s">
         <v>212</v>
       </c>
       <c r="E90" t="s">
-        <v>649</v>
+        <v>225</v>
       </c>
       <c r="F90" t="s">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="H90" s="2" t="s">
-        <v>650</v>
+        <v>653</v>
       </c>
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>651</v>
+        <v>654</v>
       </c>
       <c r="B91" t="s">
-        <v>562</v>
+        <v>655</v>
       </c>
       <c r="C91" t="s">
-        <v>563</v>
+        <v>656</v>
       </c>
       <c r="D91" t="s">
         <v>212</v>
       </c>
       <c r="E91" t="s">
-        <v>652</v>
+        <v>657</v>
       </c>
       <c r="F91" t="s">
-        <v>565</v>
+        <v>553</v>
       </c>
       <c r="H91" s="2" t="s">
-        <v>653</v>
+        <v>658</v>
       </c>
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>654</v>
+        <v>659</v>
       </c>
       <c r="B92" t="s">
-        <v>655</v>
+        <v>660</v>
       </c>
       <c r="C92" t="s">
-        <v>481</v>
+        <v>661</v>
       </c>
       <c r="D92" t="s">
         <v>212</v>
       </c>
       <c r="E92" t="s">
-        <v>375</v>
+        <v>662</v>
       </c>
       <c r="F92" t="s">
-        <v>656</v>
+        <v>663</v>
       </c>
       <c r="H92" s="2" t="s">
-        <v>657</v>
+        <v>664</v>
       </c>
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>658</v>
+        <v>665</v>
       </c>
       <c r="B93" t="s">
-        <v>659</v>
+        <v>666</v>
       </c>
       <c r="C93" t="s">
-        <v>252</v>
+        <v>218</v>
       </c>
       <c r="D93" t="s">
-        <v>212</v>
+        <v>303</v>
       </c>
       <c r="E93" t="s">
-        <v>660</v>
+        <v>225</v>
       </c>
       <c r="F93" t="s">
-        <v>238</v>
+        <v>667</v>
       </c>
       <c r="H93" s="2" t="s">
-        <v>661</v>
+        <v>668</v>
       </c>
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>662</v>
+        <v>669</v>
       </c>
       <c r="B94" t="s">
-        <v>663</v>
+        <v>670</v>
       </c>
       <c r="C94" t="s">
-        <v>464</v>
+        <v>671</v>
       </c>
       <c r="D94" t="s">
         <v>212</v>
       </c>
       <c r="E94" t="s">
-        <v>519</v>
+        <v>672</v>
       </c>
       <c r="F94" t="s">
-        <v>664</v>
+        <v>673</v>
       </c>
       <c r="H94" s="2" t="s">
-        <v>665</v>
+        <v>674</v>
       </c>
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>666</v>
+        <v>675</v>
       </c>
       <c r="B95" t="s">
-        <v>667</v>
+        <v>676</v>
       </c>
       <c r="C95" t="s">
-        <v>668</v>
+        <v>495</v>
       </c>
       <c r="D95" t="s">
         <v>212</v>
       </c>
       <c r="E95" t="s">
-        <v>627</v>
+        <v>677</v>
       </c>
       <c r="F95" t="s">
-        <v>219</v>
+        <v>528</v>
       </c>
       <c r="H95" s="2" t="s">
-        <v>669</v>
+        <v>678</v>
       </c>
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>670</v>
+        <v>679</v>
       </c>
       <c r="B96" t="s">
-        <v>619</v>
+        <v>383</v>
       </c>
       <c r="C96" t="s">
-        <v>252</v>
+        <v>270</v>
       </c>
       <c r="D96" t="s">
         <v>212</v>
       </c>
       <c r="E96" t="s">
-        <v>519</v>
+        <v>680</v>
       </c>
       <c r="F96" t="s">
-        <v>421</v>
+        <v>384</v>
       </c>
       <c r="H96" s="2" t="s">
-        <v>671</v>
+        <v>681</v>
       </c>
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>672</v>
+        <v>682</v>
       </c>
       <c r="B97" t="s">
-        <v>673</v>
+        <v>683</v>
       </c>
       <c r="C97" t="s">
-        <v>246</v>
+        <v>224</v>
       </c>
       <c r="D97" t="s">
-        <v>212</v>
+        <v>256</v>
       </c>
       <c r="E97" t="s">
-        <v>674</v>
+        <v>684</v>
       </c>
       <c r="F97" t="s">
-        <v>675</v>
+        <v>323</v>
       </c>
       <c r="H97" s="2" t="s">
-        <v>676</v>
+        <v>685</v>
       </c>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>677</v>
+        <v>686</v>
       </c>
       <c r="B98" t="s">
-        <v>678</v>
+        <v>687</v>
       </c>
       <c r="C98" t="s">
-        <v>379</v>
+        <v>688</v>
       </c>
       <c r="D98" t="s">
-        <v>212</v>
+        <v>280</v>
       </c>
       <c r="E98" t="s">
-        <v>679</v>
+        <v>689</v>
       </c>
       <c r="F98" t="s">
-        <v>680</v>
+        <v>690</v>
       </c>
       <c r="H98" s="2" t="s">
-        <v>681</v>
+        <v>691</v>
       </c>
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>682</v>
+        <v>692</v>
       </c>
       <c r="B99" t="s">
-        <v>683</v>
+        <v>693</v>
       </c>
       <c r="C99" t="s">
-        <v>684</v>
+        <v>270</v>
       </c>
       <c r="D99" t="s">
         <v>212</v>
       </c>
       <c r="E99" t="s">
-        <v>685</v>
+        <v>694</v>
       </c>
       <c r="F99" t="s">
-        <v>686</v>
+        <v>695</v>
       </c>
       <c r="H99" s="2" t="s">
-        <v>687</v>
+        <v>696</v>
       </c>
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>688</v>
+        <v>697</v>
       </c>
       <c r="B100" t="s">
-        <v>689</v>
+        <v>698</v>
       </c>
       <c r="C100" t="s">
-        <v>690</v>
+        <v>270</v>
       </c>
       <c r="D100" t="s">
         <v>212</v>
       </c>
       <c r="E100" t="s">
-        <v>219</v>
+        <v>398</v>
       </c>
       <c r="F100" t="s">
-        <v>565</v>
+        <v>251</v>
       </c>
       <c r="H100" s="2" t="s">
-        <v>691</v>
+        <v>699</v>
       </c>
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>692</v>
+        <v>697</v>
       </c>
       <c r="B101" t="s">
-        <v>693</v>
+        <v>700</v>
       </c>
       <c r="C101" t="s">
-        <v>694</v>
+        <v>701</v>
       </c>
       <c r="D101" t="s">
-        <v>212</v>
+        <v>249</v>
       </c>
       <c r="E101" t="s">
-        <v>695</v>
+        <v>702</v>
       </c>
       <c r="F101" t="s">
-        <v>696</v>
+        <v>703</v>
       </c>
       <c r="H101" s="2" t="s">
-        <v>697</v>
+        <v>704</v>
+      </c>
+    </row>
+    <row r="102" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>705</v>
+      </c>
+      <c r="B102" t="s">
+        <v>706</v>
+      </c>
+      <c r="C102" t="s">
+        <v>495</v>
+      </c>
+      <c r="D102" t="s">
+        <v>280</v>
+      </c>
+      <c r="E102" t="s">
+        <v>707</v>
+      </c>
+      <c r="F102" t="s">
+        <v>708</v>
+      </c>
+      <c r="H102" s="2" t="s">
+        <v>709</v>
+      </c>
+    </row>
+    <row r="103" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>710</v>
+      </c>
+      <c r="B103" t="s">
+        <v>480</v>
+      </c>
+      <c r="C103" t="s">
+        <v>481</v>
+      </c>
+      <c r="D103" t="s">
+        <v>212</v>
+      </c>
+      <c r="E103" t="s">
+        <v>621</v>
+      </c>
+      <c r="F103" t="s">
+        <v>483</v>
+      </c>
+      <c r="H103" s="2" t="s">
+        <v>711</v>
+      </c>
+    </row>
+    <row r="104" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>712</v>
+      </c>
+      <c r="B104" t="s">
+        <v>713</v>
+      </c>
+      <c r="C104" t="s">
+        <v>506</v>
+      </c>
+      <c r="D104" t="s">
+        <v>212</v>
+      </c>
+      <c r="E104" t="s">
+        <v>714</v>
+      </c>
+      <c r="F104" t="s">
+        <v>715</v>
+      </c>
+      <c r="H104" s="2" t="s">
+        <v>716</v>
+      </c>
+    </row>
+    <row r="105" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>717</v>
+      </c>
+      <c r="B105" t="s">
+        <v>700</v>
+      </c>
+      <c r="C105" t="s">
+        <v>701</v>
+      </c>
+      <c r="D105" t="s">
+        <v>249</v>
+      </c>
+      <c r="E105" t="s">
+        <v>718</v>
+      </c>
+      <c r="F105" t="s">
+        <v>719</v>
+      </c>
+      <c r="H105" s="2" t="s">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="106" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>721</v>
+      </c>
+      <c r="B106" t="s">
+        <v>722</v>
+      </c>
+      <c r="C106" t="s">
+        <v>723</v>
+      </c>
+      <c r="D106" t="s">
+        <v>212</v>
+      </c>
+      <c r="E106" t="s">
+        <v>724</v>
+      </c>
+      <c r="F106" t="s">
+        <v>725</v>
+      </c>
+      <c r="H106" s="2" t="s">
+        <v>726</v>
+      </c>
+    </row>
+    <row r="107" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>727</v>
+      </c>
+      <c r="B107" t="s">
+        <v>728</v>
+      </c>
+      <c r="C107" t="s">
+        <v>218</v>
+      </c>
+      <c r="D107" t="s">
+        <v>212</v>
+      </c>
+      <c r="E107" t="s">
+        <v>729</v>
+      </c>
+      <c r="F107" t="s">
+        <v>730</v>
+      </c>
+      <c r="H107" s="2" t="s">
+        <v>731</v>
+      </c>
+    </row>
+    <row r="108" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>732</v>
+      </c>
+      <c r="B108" t="s">
+        <v>733</v>
+      </c>
+      <c r="C108" t="s">
+        <v>734</v>
+      </c>
+      <c r="D108" t="s">
+        <v>212</v>
+      </c>
+      <c r="E108" t="s">
+        <v>735</v>
+      </c>
+      <c r="F108" t="s">
+        <v>736</v>
+      </c>
+      <c r="H108" s="2" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="109" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>738</v>
+      </c>
+      <c r="B109" t="s">
+        <v>739</v>
+      </c>
+      <c r="C109" t="s">
+        <v>270</v>
+      </c>
+      <c r="D109" t="s">
+        <v>212</v>
+      </c>
+      <c r="E109" t="s">
+        <v>740</v>
+      </c>
+      <c r="F109" t="s">
+        <v>225</v>
+      </c>
+      <c r="H109" s="2" t="s">
+        <v>741</v>
+      </c>
+    </row>
+    <row r="110" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>742</v>
+      </c>
+      <c r="B110" t="s">
+        <v>743</v>
+      </c>
+      <c r="C110" t="s">
+        <v>495</v>
+      </c>
+      <c r="D110" t="s">
+        <v>212</v>
+      </c>
+      <c r="E110" t="s">
+        <v>744</v>
+      </c>
+      <c r="F110" t="s">
+        <v>225</v>
+      </c>
+      <c r="H110" s="2" t="s">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="111" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>746</v>
+      </c>
+      <c r="B111" t="s">
+        <v>630</v>
+      </c>
+      <c r="C111" t="s">
+        <v>631</v>
+      </c>
+      <c r="D111" t="s">
+        <v>212</v>
+      </c>
+      <c r="E111" t="s">
+        <v>747</v>
+      </c>
+      <c r="F111" t="s">
+        <v>633</v>
+      </c>
+      <c r="H111" s="2" t="s">
+        <v>748</v>
+      </c>
+    </row>
+    <row r="112" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>749</v>
+      </c>
+      <c r="B112" t="s">
+        <v>489</v>
+      </c>
+      <c r="C112" t="s">
+        <v>218</v>
+      </c>
+      <c r="D112" t="s">
+        <v>212</v>
+      </c>
+      <c r="E112" t="s">
+        <v>740</v>
+      </c>
+      <c r="F112" t="s">
+        <v>750</v>
+      </c>
+      <c r="H112" s="2" t="s">
+        <v>751</v>
+      </c>
+    </row>
+    <row r="113" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>752</v>
+      </c>
+      <c r="B113" t="s">
+        <v>753</v>
+      </c>
+      <c r="C113" t="s">
+        <v>211</v>
+      </c>
+      <c r="D113" t="s">
+        <v>212</v>
+      </c>
+      <c r="E113" t="s">
+        <v>754</v>
+      </c>
+      <c r="F113" t="s">
+        <v>755</v>
+      </c>
+      <c r="H113" s="2" t="s">
+        <v>756</v>
+      </c>
+    </row>
+    <row r="114" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
+        <v>757</v>
+      </c>
+      <c r="B114" t="s">
+        <v>758</v>
+      </c>
+      <c r="C114" t="s">
+        <v>527</v>
+      </c>
+      <c r="D114" t="s">
+        <v>212</v>
+      </c>
+      <c r="E114" t="s">
+        <v>398</v>
+      </c>
+      <c r="F114" t="s">
+        <v>759</v>
+      </c>
+      <c r="H114" s="2" t="s">
+        <v>760</v>
+      </c>
+    </row>
+    <row r="115" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
+        <v>761</v>
+      </c>
+      <c r="B115" t="s">
+        <v>762</v>
+      </c>
+      <c r="C115" t="s">
+        <v>218</v>
+      </c>
+      <c r="D115" t="s">
+        <v>212</v>
+      </c>
+      <c r="E115" t="s">
+        <v>763</v>
+      </c>
+      <c r="F115" t="s">
+        <v>764</v>
+      </c>
+      <c r="H115" s="2" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="116" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
+        <v>766</v>
+      </c>
+      <c r="B116" t="s">
+        <v>767</v>
+      </c>
+      <c r="C116" t="s">
+        <v>270</v>
+      </c>
+      <c r="D116" t="s">
+        <v>212</v>
+      </c>
+      <c r="E116" t="s">
+        <v>768</v>
+      </c>
+      <c r="F116" t="s">
+        <v>257</v>
+      </c>
+      <c r="H116" s="2" t="s">
+        <v>769</v>
+      </c>
+    </row>
+    <row r="117" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A117" t="s">
+        <v>770</v>
+      </c>
+      <c r="B117" t="s">
+        <v>771</v>
+      </c>
+      <c r="C117" t="s">
+        <v>772</v>
+      </c>
+      <c r="D117" t="s">
+        <v>212</v>
+      </c>
+      <c r="E117" t="s">
+        <v>773</v>
+      </c>
+      <c r="F117" t="s">
+        <v>725</v>
+      </c>
+      <c r="H117" s="2" t="s">
+        <v>774</v>
+      </c>
+    </row>
+    <row r="118" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A118" t="s">
+        <v>775</v>
+      </c>
+      <c r="B118" t="s">
+        <v>776</v>
+      </c>
+      <c r="C118" t="s">
+        <v>495</v>
+      </c>
+      <c r="D118" t="s">
+        <v>212</v>
+      </c>
+      <c r="E118" t="s">
+        <v>571</v>
+      </c>
+      <c r="F118" t="s">
+        <v>777</v>
+      </c>
+      <c r="H118" s="2" t="s">
+        <v>778</v>
+      </c>
+    </row>
+    <row r="119" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A119" t="s">
+        <v>779</v>
+      </c>
+      <c r="B119" t="s">
+        <v>780</v>
+      </c>
+      <c r="C119" t="s">
+        <v>781</v>
+      </c>
+      <c r="D119" t="s">
+        <v>212</v>
+      </c>
+      <c r="E119" t="s">
+        <v>621</v>
+      </c>
+      <c r="F119" t="s">
+        <v>225</v>
+      </c>
+      <c r="H119" s="2" t="s">
+        <v>782</v>
+      </c>
+    </row>
+    <row r="120" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A120" t="s">
+        <v>783</v>
+      </c>
+      <c r="B120" t="s">
+        <v>698</v>
+      </c>
+      <c r="C120" t="s">
+        <v>270</v>
+      </c>
+      <c r="D120" t="s">
+        <v>212</v>
+      </c>
+      <c r="E120" t="s">
+        <v>571</v>
+      </c>
+      <c r="F120" t="s">
+        <v>251</v>
+      </c>
+      <c r="H120" s="2" t="s">
+        <v>784</v>
+      </c>
+    </row>
+    <row r="121" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A121" t="s">
+        <v>785</v>
+      </c>
+      <c r="B121" t="s">
+        <v>786</v>
+      </c>
+      <c r="C121" t="s">
+        <v>218</v>
+      </c>
+      <c r="D121" t="s">
+        <v>212</v>
+      </c>
+      <c r="E121" t="s">
+        <v>787</v>
+      </c>
+      <c r="F121" t="s">
+        <v>788</v>
+      </c>
+      <c r="H121" s="2" t="s">
+        <v>789</v>
+      </c>
+    </row>
+    <row r="122" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A122" t="s">
+        <v>790</v>
+      </c>
+      <c r="B122" t="s">
+        <v>791</v>
+      </c>
+      <c r="C122" t="s">
+        <v>350</v>
+      </c>
+      <c r="D122" t="s">
+        <v>212</v>
+      </c>
+      <c r="E122" t="s">
+        <v>792</v>
+      </c>
+      <c r="F122" t="s">
+        <v>793</v>
+      </c>
+      <c r="H122" s="2" t="s">
+        <v>794</v>
+      </c>
+    </row>
+    <row r="123" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A123" t="s">
+        <v>795</v>
+      </c>
+      <c r="B123" t="s">
+        <v>796</v>
+      </c>
+      <c r="C123" t="s">
+        <v>402</v>
+      </c>
+      <c r="D123" t="s">
+        <v>212</v>
+      </c>
+      <c r="E123" t="s">
+        <v>797</v>
+      </c>
+      <c r="F123" t="s">
+        <v>798</v>
+      </c>
+      <c r="H123" s="2" t="s">
+        <v>799</v>
+      </c>
+    </row>
+    <row r="124" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A124" t="s">
+        <v>800</v>
+      </c>
+      <c r="B124" t="s">
+        <v>801</v>
+      </c>
+      <c r="C124" t="s">
+        <v>802</v>
+      </c>
+      <c r="D124" t="s">
+        <v>212</v>
+      </c>
+      <c r="E124" t="s">
+        <v>803</v>
+      </c>
+      <c r="F124" t="s">
+        <v>804</v>
+      </c>
+      <c r="H124" s="2" t="s">
+        <v>805</v>
+      </c>
+    </row>
+    <row r="125" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A125" t="s">
+        <v>806</v>
+      </c>
+      <c r="B125" t="s">
+        <v>807</v>
+      </c>
+      <c r="C125" t="s">
+        <v>808</v>
+      </c>
+      <c r="D125" t="s">
+        <v>256</v>
+      </c>
+      <c r="E125" t="s">
+        <v>809</v>
+      </c>
+      <c r="F125" t="s">
+        <v>810</v>
+      </c>
+      <c r="H125" s="2" t="s">
+        <v>811</v>
+      </c>
+    </row>
+    <row r="126" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A126" t="s">
+        <v>812</v>
+      </c>
+      <c r="B126" t="s">
+        <v>813</v>
+      </c>
+      <c r="C126" t="s">
+        <v>814</v>
+      </c>
+      <c r="D126" t="s">
+        <v>212</v>
+      </c>
+      <c r="E126" t="s">
+        <v>815</v>
+      </c>
+      <c r="F126" t="s">
+        <v>816</v>
+      </c>
+      <c r="H126" s="2" t="s">
+        <v>817</v>
+      </c>
+    </row>
+    <row r="127" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A127" t="s">
+        <v>818</v>
+      </c>
+      <c r="B127" t="s">
+        <v>819</v>
+      </c>
+      <c r="C127" t="s">
+        <v>820</v>
+      </c>
+      <c r="D127" t="s">
+        <v>212</v>
+      </c>
+      <c r="E127" t="s">
+        <v>225</v>
+      </c>
+      <c r="F127" t="s">
+        <v>633</v>
+      </c>
+      <c r="H127" s="2" t="s">
+        <v>821</v>
+      </c>
+    </row>
+    <row r="128" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A128" t="s">
+        <v>822</v>
+      </c>
+      <c r="B128" t="s">
+        <v>823</v>
+      </c>
+      <c r="C128" t="s">
+        <v>824</v>
+      </c>
+      <c r="D128" t="s">
+        <v>212</v>
+      </c>
+      <c r="E128" t="s">
+        <v>825</v>
+      </c>
+      <c r="F128" t="s">
+        <v>257</v>
+      </c>
+      <c r="H128" s="2" t="s">
+        <v>826</v>
+      </c>
+    </row>
+    <row r="129" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A129" t="s">
+        <v>827</v>
+      </c>
+      <c r="B129" t="s">
+        <v>828</v>
+      </c>
+      <c r="C129" t="s">
+        <v>829</v>
+      </c>
+      <c r="D129" t="s">
+        <v>212</v>
+      </c>
+      <c r="E129" t="s">
+        <v>830</v>
+      </c>
+      <c r="F129" t="s">
+        <v>548</v>
+      </c>
+      <c r="H129" s="2" t="s">
+        <v>831</v>
       </c>
     </row>
   </sheetData>
@@ -5921,6 +6967,34 @@
     <hyperlink ref="H99" r:id="rId98"/>
     <hyperlink ref="H100" r:id="rId99"/>
     <hyperlink ref="H101" r:id="rId100"/>
+    <hyperlink ref="H102" r:id="rId101"/>
+    <hyperlink ref="H103" r:id="rId102"/>
+    <hyperlink ref="H104" r:id="rId103"/>
+    <hyperlink ref="H105" r:id="rId104"/>
+    <hyperlink ref="H106" r:id="rId105"/>
+    <hyperlink ref="H107" r:id="rId106"/>
+    <hyperlink ref="H108" r:id="rId107"/>
+    <hyperlink ref="H109" r:id="rId108"/>
+    <hyperlink ref="H110" r:id="rId109"/>
+    <hyperlink ref="H111" r:id="rId110"/>
+    <hyperlink ref="H112" r:id="rId111"/>
+    <hyperlink ref="H113" r:id="rId112"/>
+    <hyperlink ref="H114" r:id="rId113"/>
+    <hyperlink ref="H115" r:id="rId114"/>
+    <hyperlink ref="H116" r:id="rId115"/>
+    <hyperlink ref="H117" r:id="rId116"/>
+    <hyperlink ref="H118" r:id="rId117"/>
+    <hyperlink ref="H119" r:id="rId118"/>
+    <hyperlink ref="H120" r:id="rId119"/>
+    <hyperlink ref="H121" r:id="rId120"/>
+    <hyperlink ref="H122" r:id="rId121"/>
+    <hyperlink ref="H123" r:id="rId122"/>
+    <hyperlink ref="H124" r:id="rId123"/>
+    <hyperlink ref="H125" r:id="rId124"/>
+    <hyperlink ref="H126" r:id="rId125"/>
+    <hyperlink ref="H127" r:id="rId126"/>
+    <hyperlink ref="H128" r:id="rId127"/>
+    <hyperlink ref="H129" r:id="rId128"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>

--- a/docs/xlsx/jobs-2026-09-28.xlsx
+++ b/docs/xlsx/jobs-2026-09-28.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1187" uniqueCount="832">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1194" uniqueCount="834">
   <si>
     <t>Title</t>
   </si>
@@ -1871,6 +1871,12 @@
   </si>
   <si>
     <t>https://www.idealist.org/en/nonprofit-job/5678c0766c9547669d8f90e7bd9c0e64-manager-of-violence-prevention-programs-worcester-youth-center-inc-worcester</t>
+  </si>
+  <si>
+    <t>Manager of Violence Prevention Programs &amp; Youth Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/5678c0766c9547669d8f90e7bd9c0e64-manager-of-violence-prevention-programs-youth-development-worcester-youth-center-inc-worcester</t>
   </si>
   <si>
     <t>Manager Of Youth Programs</t>
@@ -3881,7 +3887,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H129"/>
+  <dimension ref="A1:H130"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -5811,375 +5817,375 @@
         <v>619</v>
       </c>
       <c r="B84" t="s">
+        <v>614</v>
+      </c>
+      <c r="C84" t="s">
+        <v>615</v>
+      </c>
+      <c r="D84" t="s">
+        <v>212</v>
+      </c>
+      <c r="E84" t="s">
+        <v>616</v>
+      </c>
+      <c r="F84" t="s">
+        <v>617</v>
+      </c>
+      <c r="H84" s="2" t="s">
         <v>620</v>
-      </c>
-      <c r="C84" t="s">
-        <v>270</v>
-      </c>
-      <c r="D84" t="s">
-        <v>212</v>
-      </c>
-      <c r="E84" t="s">
-        <v>621</v>
-      </c>
-      <c r="F84" t="s">
-        <v>622</v>
-      </c>
-      <c r="H84" s="2" t="s">
-        <v>623</v>
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
+        <v>621</v>
+      </c>
+      <c r="B85" t="s">
+        <v>622</v>
+      </c>
+      <c r="C85" t="s">
+        <v>270</v>
+      </c>
+      <c r="D85" t="s">
+        <v>212</v>
+      </c>
+      <c r="E85" t="s">
+        <v>623</v>
+      </c>
+      <c r="F85" t="s">
         <v>624</v>
       </c>
-      <c r="B85" t="s">
+      <c r="H85" s="2" t="s">
         <v>625</v>
-      </c>
-      <c r="C85" t="s">
-        <v>218</v>
-      </c>
-      <c r="D85" t="s">
-        <v>212</v>
-      </c>
-      <c r="E85" t="s">
-        <v>626</v>
-      </c>
-      <c r="F85" t="s">
-        <v>627</v>
-      </c>
-      <c r="H85" s="2" t="s">
-        <v>628</v>
       </c>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
+        <v>626</v>
+      </c>
+      <c r="B86" t="s">
+        <v>627</v>
+      </c>
+      <c r="C86" t="s">
+        <v>218</v>
+      </c>
+      <c r="D86" t="s">
+        <v>212</v>
+      </c>
+      <c r="E86" t="s">
+        <v>628</v>
+      </c>
+      <c r="F86" t="s">
         <v>629</v>
       </c>
-      <c r="B86" t="s">
+      <c r="H86" s="2" t="s">
         <v>630</v>
-      </c>
-      <c r="C86" t="s">
-        <v>631</v>
-      </c>
-      <c r="D86" t="s">
-        <v>212</v>
-      </c>
-      <c r="E86" t="s">
-        <v>632</v>
-      </c>
-      <c r="F86" t="s">
-        <v>633</v>
-      </c>
-      <c r="H86" s="2" t="s">
-        <v>634</v>
       </c>
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
+        <v>631</v>
+      </c>
+      <c r="B87" t="s">
+        <v>632</v>
+      </c>
+      <c r="C87" t="s">
+        <v>633</v>
+      </c>
+      <c r="D87" t="s">
+        <v>212</v>
+      </c>
+      <c r="E87" t="s">
+        <v>634</v>
+      </c>
+      <c r="F87" t="s">
         <v>635</v>
       </c>
-      <c r="B87" t="s">
+      <c r="H87" s="2" t="s">
         <v>636</v>
-      </c>
-      <c r="C87" t="s">
-        <v>527</v>
-      </c>
-      <c r="D87" t="s">
-        <v>212</v>
-      </c>
-      <c r="E87" t="s">
-        <v>637</v>
-      </c>
-      <c r="F87" t="s">
-        <v>638</v>
-      </c>
-      <c r="H87" s="2" t="s">
-        <v>639</v>
       </c>
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
+        <v>637</v>
+      </c>
+      <c r="B88" t="s">
+        <v>638</v>
+      </c>
+      <c r="C88" t="s">
+        <v>527</v>
+      </c>
+      <c r="D88" t="s">
+        <v>212</v>
+      </c>
+      <c r="E88" t="s">
+        <v>639</v>
+      </c>
+      <c r="F88" t="s">
         <v>640</v>
       </c>
-      <c r="B88" t="s">
+      <c r="H88" s="2" t="s">
         <v>641</v>
-      </c>
-      <c r="C88" t="s">
-        <v>642</v>
-      </c>
-      <c r="D88" t="s">
-        <v>212</v>
-      </c>
-      <c r="E88" t="s">
-        <v>643</v>
-      </c>
-      <c r="F88" t="s">
-        <v>644</v>
-      </c>
-      <c r="H88" s="2" t="s">
-        <v>645</v>
       </c>
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
+        <v>642</v>
+      </c>
+      <c r="B89" t="s">
+        <v>643</v>
+      </c>
+      <c r="C89" t="s">
+        <v>644</v>
+      </c>
+      <c r="D89" t="s">
+        <v>212</v>
+      </c>
+      <c r="E89" t="s">
+        <v>645</v>
+      </c>
+      <c r="F89" t="s">
         <v>646</v>
       </c>
-      <c r="B89" t="s">
-        <v>331</v>
-      </c>
-      <c r="C89" t="s">
+      <c r="H89" s="2" t="s">
         <v>647</v>
-      </c>
-      <c r="D89" t="s">
-        <v>212</v>
-      </c>
-      <c r="E89" t="s">
-        <v>648</v>
-      </c>
-      <c r="F89" t="s">
-        <v>649</v>
-      </c>
-      <c r="H89" s="2" t="s">
-        <v>650</v>
       </c>
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
+        <v>648</v>
+      </c>
+      <c r="B90" t="s">
+        <v>331</v>
+      </c>
+      <c r="C90" t="s">
+        <v>649</v>
+      </c>
+      <c r="D90" t="s">
+        <v>212</v>
+      </c>
+      <c r="E90" t="s">
+        <v>650</v>
+      </c>
+      <c r="F90" t="s">
         <v>651</v>
       </c>
-      <c r="B90" t="s">
+      <c r="H90" s="2" t="s">
         <v>652</v>
-      </c>
-      <c r="C90" t="s">
-        <v>527</v>
-      </c>
-      <c r="D90" t="s">
-        <v>212</v>
-      </c>
-      <c r="E90" t="s">
-        <v>225</v>
-      </c>
-      <c r="F90" t="s">
-        <v>225</v>
-      </c>
-      <c r="H90" s="2" t="s">
-        <v>653</v>
       </c>
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
+        <v>653</v>
+      </c>
+      <c r="B91" t="s">
         <v>654</v>
       </c>
-      <c r="B91" t="s">
+      <c r="C91" t="s">
+        <v>527</v>
+      </c>
+      <c r="D91" t="s">
+        <v>212</v>
+      </c>
+      <c r="E91" t="s">
+        <v>225</v>
+      </c>
+      <c r="F91" t="s">
+        <v>225</v>
+      </c>
+      <c r="H91" s="2" t="s">
         <v>655</v>
-      </c>
-      <c r="C91" t="s">
-        <v>656</v>
-      </c>
-      <c r="D91" t="s">
-        <v>212</v>
-      </c>
-      <c r="E91" t="s">
-        <v>657</v>
-      </c>
-      <c r="F91" t="s">
-        <v>553</v>
-      </c>
-      <c r="H91" s="2" t="s">
-        <v>658</v>
       </c>
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
+        <v>656</v>
+      </c>
+      <c r="B92" t="s">
+        <v>657</v>
+      </c>
+      <c r="C92" t="s">
+        <v>658</v>
+      </c>
+      <c r="D92" t="s">
+        <v>212</v>
+      </c>
+      <c r="E92" t="s">
         <v>659</v>
       </c>
-      <c r="B92" t="s">
+      <c r="F92" t="s">
+        <v>553</v>
+      </c>
+      <c r="H92" s="2" t="s">
         <v>660</v>
-      </c>
-      <c r="C92" t="s">
-        <v>661</v>
-      </c>
-      <c r="D92" t="s">
-        <v>212</v>
-      </c>
-      <c r="E92" t="s">
-        <v>662</v>
-      </c>
-      <c r="F92" t="s">
-        <v>663</v>
-      </c>
-      <c r="H92" s="2" t="s">
-        <v>664</v>
       </c>
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
+        <v>661</v>
+      </c>
+      <c r="B93" t="s">
+        <v>662</v>
+      </c>
+      <c r="C93" t="s">
+        <v>663</v>
+      </c>
+      <c r="D93" t="s">
+        <v>212</v>
+      </c>
+      <c r="E93" t="s">
+        <v>664</v>
+      </c>
+      <c r="F93" t="s">
         <v>665</v>
       </c>
-      <c r="B93" t="s">
+      <c r="H93" s="2" t="s">
         <v>666</v>
-      </c>
-      <c r="C93" t="s">
-        <v>218</v>
-      </c>
-      <c r="D93" t="s">
-        <v>303</v>
-      </c>
-      <c r="E93" t="s">
-        <v>225</v>
-      </c>
-      <c r="F93" t="s">
-        <v>667</v>
-      </c>
-      <c r="H93" s="2" t="s">
-        <v>668</v>
       </c>
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
+        <v>667</v>
+      </c>
+      <c r="B94" t="s">
+        <v>668</v>
+      </c>
+      <c r="C94" t="s">
+        <v>218</v>
+      </c>
+      <c r="D94" t="s">
+        <v>303</v>
+      </c>
+      <c r="E94" t="s">
+        <v>225</v>
+      </c>
+      <c r="F94" t="s">
         <v>669</v>
       </c>
-      <c r="B94" t="s">
+      <c r="H94" s="2" t="s">
         <v>670</v>
-      </c>
-      <c r="C94" t="s">
-        <v>671</v>
-      </c>
-      <c r="D94" t="s">
-        <v>212</v>
-      </c>
-      <c r="E94" t="s">
-        <v>672</v>
-      </c>
-      <c r="F94" t="s">
-        <v>673</v>
-      </c>
-      <c r="H94" s="2" t="s">
-        <v>674</v>
       </c>
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
+        <v>671</v>
+      </c>
+      <c r="B95" t="s">
+        <v>672</v>
+      </c>
+      <c r="C95" t="s">
+        <v>673</v>
+      </c>
+      <c r="D95" t="s">
+        <v>212</v>
+      </c>
+      <c r="E95" t="s">
+        <v>674</v>
+      </c>
+      <c r="F95" t="s">
         <v>675</v>
       </c>
-      <c r="B95" t="s">
+      <c r="H95" s="2" t="s">
         <v>676</v>
-      </c>
-      <c r="C95" t="s">
-        <v>495</v>
-      </c>
-      <c r="D95" t="s">
-        <v>212</v>
-      </c>
-      <c r="E95" t="s">
-        <v>677</v>
-      </c>
-      <c r="F95" t="s">
-        <v>528</v>
-      </c>
-      <c r="H95" s="2" t="s">
-        <v>678</v>
       </c>
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
+        <v>677</v>
+      </c>
+      <c r="B96" t="s">
+        <v>678</v>
+      </c>
+      <c r="C96" t="s">
+        <v>495</v>
+      </c>
+      <c r="D96" t="s">
+        <v>212</v>
+      </c>
+      <c r="E96" t="s">
         <v>679</v>
       </c>
-      <c r="B96" t="s">
-        <v>383</v>
-      </c>
-      <c r="C96" t="s">
-        <v>270</v>
-      </c>
-      <c r="D96" t="s">
-        <v>212</v>
-      </c>
-      <c r="E96" t="s">
+      <c r="F96" t="s">
+        <v>528</v>
+      </c>
+      <c r="H96" s="2" t="s">
         <v>680</v>
-      </c>
-      <c r="F96" t="s">
-        <v>384</v>
-      </c>
-      <c r="H96" s="2" t="s">
-        <v>681</v>
       </c>
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
+        <v>681</v>
+      </c>
+      <c r="B97" t="s">
+        <v>383</v>
+      </c>
+      <c r="C97" t="s">
+        <v>270</v>
+      </c>
+      <c r="D97" t="s">
+        <v>212</v>
+      </c>
+      <c r="E97" t="s">
         <v>682</v>
       </c>
-      <c r="B97" t="s">
+      <c r="F97" t="s">
+        <v>384</v>
+      </c>
+      <c r="H97" s="2" t="s">
         <v>683</v>
-      </c>
-      <c r="C97" t="s">
-        <v>224</v>
-      </c>
-      <c r="D97" t="s">
-        <v>256</v>
-      </c>
-      <c r="E97" t="s">
-        <v>684</v>
-      </c>
-      <c r="F97" t="s">
-        <v>323</v>
-      </c>
-      <c r="H97" s="2" t="s">
-        <v>685</v>
       </c>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
+        <v>684</v>
+      </c>
+      <c r="B98" t="s">
+        <v>685</v>
+      </c>
+      <c r="C98" t="s">
+        <v>224</v>
+      </c>
+      <c r="D98" t="s">
+        <v>256</v>
+      </c>
+      <c r="E98" t="s">
         <v>686</v>
       </c>
-      <c r="B98" t="s">
+      <c r="F98" t="s">
+        <v>323</v>
+      </c>
+      <c r="H98" s="2" t="s">
         <v>687</v>
-      </c>
-      <c r="C98" t="s">
-        <v>688</v>
-      </c>
-      <c r="D98" t="s">
-        <v>280</v>
-      </c>
-      <c r="E98" t="s">
-        <v>689</v>
-      </c>
-      <c r="F98" t="s">
-        <v>690</v>
-      </c>
-      <c r="H98" s="2" t="s">
-        <v>691</v>
       </c>
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
+        <v>688</v>
+      </c>
+      <c r="B99" t="s">
+        <v>689</v>
+      </c>
+      <c r="C99" t="s">
+        <v>690</v>
+      </c>
+      <c r="D99" t="s">
+        <v>280</v>
+      </c>
+      <c r="E99" t="s">
+        <v>691</v>
+      </c>
+      <c r="F99" t="s">
         <v>692</v>
       </c>
-      <c r="B99" t="s">
+      <c r="H99" s="2" t="s">
         <v>693</v>
-      </c>
-      <c r="C99" t="s">
-        <v>270</v>
-      </c>
-      <c r="D99" t="s">
-        <v>212</v>
-      </c>
-      <c r="E99" t="s">
-        <v>694</v>
-      </c>
-      <c r="F99" t="s">
-        <v>695</v>
-      </c>
-      <c r="H99" s="2" t="s">
-        <v>696</v>
       </c>
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>697</v>
+        <v>694</v>
       </c>
       <c r="B100" t="s">
-        <v>698</v>
+        <v>695</v>
       </c>
       <c r="C100" t="s">
         <v>270</v>
@@ -6188,79 +6194,79 @@
         <v>212</v>
       </c>
       <c r="E100" t="s">
-        <v>398</v>
+        <v>696</v>
       </c>
       <c r="F100" t="s">
-        <v>251</v>
+        <v>697</v>
       </c>
       <c r="H100" s="2" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>697</v>
+        <v>699</v>
       </c>
       <c r="B101" t="s">
         <v>700</v>
       </c>
       <c r="C101" t="s">
+        <v>270</v>
+      </c>
+      <c r="D101" t="s">
+        <v>212</v>
+      </c>
+      <c r="E101" t="s">
+        <v>398</v>
+      </c>
+      <c r="F101" t="s">
+        <v>251</v>
+      </c>
+      <c r="H101" s="2" t="s">
         <v>701</v>
-      </c>
-      <c r="D101" t="s">
-        <v>249</v>
-      </c>
-      <c r="E101" t="s">
-        <v>702</v>
-      </c>
-      <c r="F101" t="s">
-        <v>703</v>
-      </c>
-      <c r="H101" s="2" t="s">
-        <v>704</v>
       </c>
     </row>
     <row r="102" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
+        <v>699</v>
+      </c>
+      <c r="B102" t="s">
+        <v>702</v>
+      </c>
+      <c r="C102" t="s">
+        <v>703</v>
+      </c>
+      <c r="D102" t="s">
+        <v>249</v>
+      </c>
+      <c r="E102" t="s">
+        <v>704</v>
+      </c>
+      <c r="F102" t="s">
         <v>705</v>
       </c>
-      <c r="B102" t="s">
+      <c r="H102" s="2" t="s">
         <v>706</v>
-      </c>
-      <c r="C102" t="s">
-        <v>495</v>
-      </c>
-      <c r="D102" t="s">
-        <v>280</v>
-      </c>
-      <c r="E102" t="s">
-        <v>707</v>
-      </c>
-      <c r="F102" t="s">
-        <v>708</v>
-      </c>
-      <c r="H102" s="2" t="s">
-        <v>709</v>
       </c>
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
+        <v>707</v>
+      </c>
+      <c r="B103" t="s">
+        <v>708</v>
+      </c>
+      <c r="C103" t="s">
+        <v>495</v>
+      </c>
+      <c r="D103" t="s">
+        <v>280</v>
+      </c>
+      <c r="E103" t="s">
+        <v>709</v>
+      </c>
+      <c r="F103" t="s">
         <v>710</v>
-      </c>
-      <c r="B103" t="s">
-        <v>480</v>
-      </c>
-      <c r="C103" t="s">
-        <v>481</v>
-      </c>
-      <c r="D103" t="s">
-        <v>212</v>
-      </c>
-      <c r="E103" t="s">
-        <v>621</v>
-      </c>
-      <c r="F103" t="s">
-        <v>483</v>
       </c>
       <c r="H103" s="2" t="s">
         <v>711</v>
@@ -6271,387 +6277,387 @@
         <v>712</v>
       </c>
       <c r="B104" t="s">
+        <v>480</v>
+      </c>
+      <c r="C104" t="s">
+        <v>481</v>
+      </c>
+      <c r="D104" t="s">
+        <v>212</v>
+      </c>
+      <c r="E104" t="s">
+        <v>623</v>
+      </c>
+      <c r="F104" t="s">
+        <v>483</v>
+      </c>
+      <c r="H104" s="2" t="s">
         <v>713</v>
-      </c>
-      <c r="C104" t="s">
-        <v>506</v>
-      </c>
-      <c r="D104" t="s">
-        <v>212</v>
-      </c>
-      <c r="E104" t="s">
-        <v>714</v>
-      </c>
-      <c r="F104" t="s">
-        <v>715</v>
-      </c>
-      <c r="H104" s="2" t="s">
-        <v>716</v>
       </c>
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
+        <v>714</v>
+      </c>
+      <c r="B105" t="s">
+        <v>715</v>
+      </c>
+      <c r="C105" t="s">
+        <v>506</v>
+      </c>
+      <c r="D105" t="s">
+        <v>212</v>
+      </c>
+      <c r="E105" t="s">
+        <v>716</v>
+      </c>
+      <c r="F105" t="s">
         <v>717</v>
       </c>
-      <c r="B105" t="s">
-        <v>700</v>
-      </c>
-      <c r="C105" t="s">
-        <v>701</v>
-      </c>
-      <c r="D105" t="s">
-        <v>249</v>
-      </c>
-      <c r="E105" t="s">
+      <c r="H105" s="2" t="s">
         <v>718</v>
-      </c>
-      <c r="F105" t="s">
-        <v>719</v>
-      </c>
-      <c r="H105" s="2" t="s">
-        <v>720</v>
       </c>
     </row>
     <row r="106" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
+        <v>719</v>
+      </c>
+      <c r="B106" t="s">
+        <v>702</v>
+      </c>
+      <c r="C106" t="s">
+        <v>703</v>
+      </c>
+      <c r="D106" t="s">
+        <v>249</v>
+      </c>
+      <c r="E106" t="s">
+        <v>720</v>
+      </c>
+      <c r="F106" t="s">
         <v>721</v>
       </c>
-      <c r="B106" t="s">
+      <c r="H106" s="2" t="s">
         <v>722</v>
-      </c>
-      <c r="C106" t="s">
-        <v>723</v>
-      </c>
-      <c r="D106" t="s">
-        <v>212</v>
-      </c>
-      <c r="E106" t="s">
-        <v>724</v>
-      </c>
-      <c r="F106" t="s">
-        <v>725</v>
-      </c>
-      <c r="H106" s="2" t="s">
-        <v>726</v>
       </c>
     </row>
     <row r="107" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
+        <v>723</v>
+      </c>
+      <c r="B107" t="s">
+        <v>724</v>
+      </c>
+      <c r="C107" t="s">
+        <v>725</v>
+      </c>
+      <c r="D107" t="s">
+        <v>212</v>
+      </c>
+      <c r="E107" t="s">
+        <v>726</v>
+      </c>
+      <c r="F107" t="s">
         <v>727</v>
       </c>
-      <c r="B107" t="s">
+      <c r="H107" s="2" t="s">
         <v>728</v>
-      </c>
-      <c r="C107" t="s">
-        <v>218</v>
-      </c>
-      <c r="D107" t="s">
-        <v>212</v>
-      </c>
-      <c r="E107" t="s">
-        <v>729</v>
-      </c>
-      <c r="F107" t="s">
-        <v>730</v>
-      </c>
-      <c r="H107" s="2" t="s">
-        <v>731</v>
       </c>
     </row>
     <row r="108" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
+        <v>729</v>
+      </c>
+      <c r="B108" t="s">
+        <v>730</v>
+      </c>
+      <c r="C108" t="s">
+        <v>218</v>
+      </c>
+      <c r="D108" t="s">
+        <v>212</v>
+      </c>
+      <c r="E108" t="s">
+        <v>731</v>
+      </c>
+      <c r="F108" t="s">
         <v>732</v>
       </c>
-      <c r="B108" t="s">
+      <c r="H108" s="2" t="s">
         <v>733</v>
-      </c>
-      <c r="C108" t="s">
-        <v>734</v>
-      </c>
-      <c r="D108" t="s">
-        <v>212</v>
-      </c>
-      <c r="E108" t="s">
-        <v>735</v>
-      </c>
-      <c r="F108" t="s">
-        <v>736</v>
-      </c>
-      <c r="H108" s="2" t="s">
-        <v>737</v>
       </c>
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
+        <v>734</v>
+      </c>
+      <c r="B109" t="s">
+        <v>735</v>
+      </c>
+      <c r="C109" t="s">
+        <v>736</v>
+      </c>
+      <c r="D109" t="s">
+        <v>212</v>
+      </c>
+      <c r="E109" t="s">
+        <v>737</v>
+      </c>
+      <c r="F109" t="s">
         <v>738</v>
       </c>
-      <c r="B109" t="s">
+      <c r="H109" s="2" t="s">
         <v>739</v>
-      </c>
-      <c r="C109" t="s">
-        <v>270</v>
-      </c>
-      <c r="D109" t="s">
-        <v>212</v>
-      </c>
-      <c r="E109" t="s">
-        <v>740</v>
-      </c>
-      <c r="F109" t="s">
-        <v>225</v>
-      </c>
-      <c r="H109" s="2" t="s">
-        <v>741</v>
       </c>
     </row>
     <row r="110" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
+        <v>740</v>
+      </c>
+      <c r="B110" t="s">
+        <v>741</v>
+      </c>
+      <c r="C110" t="s">
+        <v>270</v>
+      </c>
+      <c r="D110" t="s">
+        <v>212</v>
+      </c>
+      <c r="E110" t="s">
         <v>742</v>
-      </c>
-      <c r="B110" t="s">
-        <v>743</v>
-      </c>
-      <c r="C110" t="s">
-        <v>495</v>
-      </c>
-      <c r="D110" t="s">
-        <v>212</v>
-      </c>
-      <c r="E110" t="s">
-        <v>744</v>
       </c>
       <c r="F110" t="s">
         <v>225</v>
       </c>
       <c r="H110" s="2" t="s">
-        <v>745</v>
+        <v>743</v>
       </c>
     </row>
     <row r="111" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
+        <v>744</v>
+      </c>
+      <c r="B111" t="s">
+        <v>745</v>
+      </c>
+      <c r="C111" t="s">
+        <v>495</v>
+      </c>
+      <c r="D111" t="s">
+        <v>212</v>
+      </c>
+      <c r="E111" t="s">
         <v>746</v>
       </c>
-      <c r="B111" t="s">
-        <v>630</v>
-      </c>
-      <c r="C111" t="s">
-        <v>631</v>
-      </c>
-      <c r="D111" t="s">
-        <v>212</v>
-      </c>
-      <c r="E111" t="s">
+      <c r="F111" t="s">
+        <v>225</v>
+      </c>
+      <c r="H111" s="2" t="s">
         <v>747</v>
-      </c>
-      <c r="F111" t="s">
-        <v>633</v>
-      </c>
-      <c r="H111" s="2" t="s">
-        <v>748</v>
       </c>
     </row>
     <row r="112" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
+        <v>748</v>
+      </c>
+      <c r="B112" t="s">
+        <v>632</v>
+      </c>
+      <c r="C112" t="s">
+        <v>633</v>
+      </c>
+      <c r="D112" t="s">
+        <v>212</v>
+      </c>
+      <c r="E112" t="s">
         <v>749</v>
       </c>
-      <c r="B112" t="s">
-        <v>489</v>
-      </c>
-      <c r="C112" t="s">
-        <v>218</v>
-      </c>
-      <c r="D112" t="s">
-        <v>212</v>
-      </c>
-      <c r="E112" t="s">
-        <v>740</v>
-      </c>
       <c r="F112" t="s">
+        <v>635</v>
+      </c>
+      <c r="H112" s="2" t="s">
         <v>750</v>
-      </c>
-      <c r="H112" s="2" t="s">
-        <v>751</v>
       </c>
     </row>
     <row r="113" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
+        <v>751</v>
+      </c>
+      <c r="B113" t="s">
+        <v>489</v>
+      </c>
+      <c r="C113" t="s">
+        <v>218</v>
+      </c>
+      <c r="D113" t="s">
+        <v>212</v>
+      </c>
+      <c r="E113" t="s">
+        <v>742</v>
+      </c>
+      <c r="F113" t="s">
         <v>752</v>
       </c>
-      <c r="B113" t="s">
+      <c r="H113" s="2" t="s">
         <v>753</v>
-      </c>
-      <c r="C113" t="s">
-        <v>211</v>
-      </c>
-      <c r="D113" t="s">
-        <v>212</v>
-      </c>
-      <c r="E113" t="s">
-        <v>754</v>
-      </c>
-      <c r="F113" t="s">
-        <v>755</v>
-      </c>
-      <c r="H113" s="2" t="s">
-        <v>756</v>
       </c>
     </row>
     <row r="114" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
+        <v>754</v>
+      </c>
+      <c r="B114" t="s">
+        <v>755</v>
+      </c>
+      <c r="C114" t="s">
+        <v>211</v>
+      </c>
+      <c r="D114" t="s">
+        <v>212</v>
+      </c>
+      <c r="E114" t="s">
+        <v>756</v>
+      </c>
+      <c r="F114" t="s">
         <v>757</v>
       </c>
-      <c r="B114" t="s">
+      <c r="H114" s="2" t="s">
         <v>758</v>
-      </c>
-      <c r="C114" t="s">
-        <v>527</v>
-      </c>
-      <c r="D114" t="s">
-        <v>212</v>
-      </c>
-      <c r="E114" t="s">
-        <v>398</v>
-      </c>
-      <c r="F114" t="s">
-        <v>759</v>
-      </c>
-      <c r="H114" s="2" t="s">
-        <v>760</v>
       </c>
     </row>
     <row r="115" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
+        <v>759</v>
+      </c>
+      <c r="B115" t="s">
+        <v>760</v>
+      </c>
+      <c r="C115" t="s">
+        <v>527</v>
+      </c>
+      <c r="D115" t="s">
+        <v>212</v>
+      </c>
+      <c r="E115" t="s">
+        <v>398</v>
+      </c>
+      <c r="F115" t="s">
         <v>761</v>
       </c>
-      <c r="B115" t="s">
+      <c r="H115" s="2" t="s">
         <v>762</v>
-      </c>
-      <c r="C115" t="s">
-        <v>218</v>
-      </c>
-      <c r="D115" t="s">
-        <v>212</v>
-      </c>
-      <c r="E115" t="s">
-        <v>763</v>
-      </c>
-      <c r="F115" t="s">
-        <v>764</v>
-      </c>
-      <c r="H115" s="2" t="s">
-        <v>765</v>
       </c>
     </row>
     <row r="116" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
+        <v>763</v>
+      </c>
+      <c r="B116" t="s">
+        <v>764</v>
+      </c>
+      <c r="C116" t="s">
+        <v>218</v>
+      </c>
+      <c r="D116" t="s">
+        <v>212</v>
+      </c>
+      <c r="E116" t="s">
+        <v>765</v>
+      </c>
+      <c r="F116" t="s">
         <v>766</v>
       </c>
-      <c r="B116" t="s">
+      <c r="H116" s="2" t="s">
         <v>767</v>
-      </c>
-      <c r="C116" t="s">
-        <v>270</v>
-      </c>
-      <c r="D116" t="s">
-        <v>212</v>
-      </c>
-      <c r="E116" t="s">
-        <v>768</v>
-      </c>
-      <c r="F116" t="s">
-        <v>257</v>
-      </c>
-      <c r="H116" s="2" t="s">
-        <v>769</v>
       </c>
     </row>
     <row r="117" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
+        <v>768</v>
+      </c>
+      <c r="B117" t="s">
+        <v>769</v>
+      </c>
+      <c r="C117" t="s">
+        <v>270</v>
+      </c>
+      <c r="D117" t="s">
+        <v>212</v>
+      </c>
+      <c r="E117" t="s">
         <v>770</v>
       </c>
-      <c r="B117" t="s">
+      <c r="F117" t="s">
+        <v>257</v>
+      </c>
+      <c r="H117" s="2" t="s">
         <v>771</v>
-      </c>
-      <c r="C117" t="s">
-        <v>772</v>
-      </c>
-      <c r="D117" t="s">
-        <v>212</v>
-      </c>
-      <c r="E117" t="s">
-        <v>773</v>
-      </c>
-      <c r="F117" t="s">
-        <v>725</v>
-      </c>
-      <c r="H117" s="2" t="s">
-        <v>774</v>
       </c>
     </row>
     <row r="118" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
+        <v>772</v>
+      </c>
+      <c r="B118" t="s">
+        <v>773</v>
+      </c>
+      <c r="C118" t="s">
+        <v>774</v>
+      </c>
+      <c r="D118" t="s">
+        <v>212</v>
+      </c>
+      <c r="E118" t="s">
         <v>775</v>
       </c>
-      <c r="B118" t="s">
+      <c r="F118" t="s">
+        <v>727</v>
+      </c>
+      <c r="H118" s="2" t="s">
         <v>776</v>
-      </c>
-      <c r="C118" t="s">
-        <v>495</v>
-      </c>
-      <c r="D118" t="s">
-        <v>212</v>
-      </c>
-      <c r="E118" t="s">
-        <v>571</v>
-      </c>
-      <c r="F118" t="s">
-        <v>777</v>
-      </c>
-      <c r="H118" s="2" t="s">
-        <v>778</v>
       </c>
     </row>
     <row r="119" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
+        <v>777</v>
+      </c>
+      <c r="B119" t="s">
+        <v>778</v>
+      </c>
+      <c r="C119" t="s">
+        <v>495</v>
+      </c>
+      <c r="D119" t="s">
+        <v>212</v>
+      </c>
+      <c r="E119" t="s">
+        <v>571</v>
+      </c>
+      <c r="F119" t="s">
         <v>779</v>
       </c>
-      <c r="B119" t="s">
+      <c r="H119" s="2" t="s">
         <v>780</v>
-      </c>
-      <c r="C119" t="s">
-        <v>781</v>
-      </c>
-      <c r="D119" t="s">
-        <v>212</v>
-      </c>
-      <c r="E119" t="s">
-        <v>621</v>
-      </c>
-      <c r="F119" t="s">
-        <v>225</v>
-      </c>
-      <c r="H119" s="2" t="s">
-        <v>782</v>
       </c>
     </row>
     <row r="120" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
+        <v>781</v>
+      </c>
+      <c r="B120" t="s">
+        <v>782</v>
+      </c>
+      <c r="C120" t="s">
         <v>783</v>
       </c>
-      <c r="B120" t="s">
-        <v>698</v>
-      </c>
-      <c r="C120" t="s">
-        <v>270</v>
-      </c>
       <c r="D120" t="s">
         <v>212</v>
       </c>
       <c r="E120" t="s">
-        <v>571</v>
+        <v>623</v>
       </c>
       <c r="F120" t="s">
-        <v>251</v>
+        <v>225</v>
       </c>
       <c r="H120" s="2" t="s">
         <v>784</v>
@@ -6662,206 +6668,229 @@
         <v>785</v>
       </c>
       <c r="B121" t="s">
+        <v>700</v>
+      </c>
+      <c r="C121" t="s">
+        <v>270</v>
+      </c>
+      <c r="D121" t="s">
+        <v>212</v>
+      </c>
+      <c r="E121" t="s">
+        <v>571</v>
+      </c>
+      <c r="F121" t="s">
+        <v>251</v>
+      </c>
+      <c r="H121" s="2" t="s">
         <v>786</v>
-      </c>
-      <c r="C121" t="s">
-        <v>218</v>
-      </c>
-      <c r="D121" t="s">
-        <v>212</v>
-      </c>
-      <c r="E121" t="s">
-        <v>787</v>
-      </c>
-      <c r="F121" t="s">
-        <v>788</v>
-      </c>
-      <c r="H121" s="2" t="s">
-        <v>789</v>
       </c>
     </row>
     <row r="122" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
+        <v>787</v>
+      </c>
+      <c r="B122" t="s">
+        <v>788</v>
+      </c>
+      <c r="C122" t="s">
+        <v>218</v>
+      </c>
+      <c r="D122" t="s">
+        <v>212</v>
+      </c>
+      <c r="E122" t="s">
+        <v>789</v>
+      </c>
+      <c r="F122" t="s">
         <v>790</v>
       </c>
-      <c r="B122" t="s">
+      <c r="H122" s="2" t="s">
         <v>791</v>
-      </c>
-      <c r="C122" t="s">
-        <v>350</v>
-      </c>
-      <c r="D122" t="s">
-        <v>212</v>
-      </c>
-      <c r="E122" t="s">
-        <v>792</v>
-      </c>
-      <c r="F122" t="s">
-        <v>793</v>
-      </c>
-      <c r="H122" s="2" t="s">
-        <v>794</v>
       </c>
     </row>
     <row r="123" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
+        <v>792</v>
+      </c>
+      <c r="B123" t="s">
+        <v>793</v>
+      </c>
+      <c r="C123" t="s">
+        <v>350</v>
+      </c>
+      <c r="D123" t="s">
+        <v>212</v>
+      </c>
+      <c r="E123" t="s">
+        <v>794</v>
+      </c>
+      <c r="F123" t="s">
         <v>795</v>
       </c>
-      <c r="B123" t="s">
+      <c r="H123" s="2" t="s">
         <v>796</v>
-      </c>
-      <c r="C123" t="s">
-        <v>402</v>
-      </c>
-      <c r="D123" t="s">
-        <v>212</v>
-      </c>
-      <c r="E123" t="s">
-        <v>797</v>
-      </c>
-      <c r="F123" t="s">
-        <v>798</v>
-      </c>
-      <c r="H123" s="2" t="s">
-        <v>799</v>
       </c>
     </row>
     <row r="124" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
+        <v>797</v>
+      </c>
+      <c r="B124" t="s">
+        <v>798</v>
+      </c>
+      <c r="C124" t="s">
+        <v>402</v>
+      </c>
+      <c r="D124" t="s">
+        <v>212</v>
+      </c>
+      <c r="E124" t="s">
+        <v>799</v>
+      </c>
+      <c r="F124" t="s">
         <v>800</v>
       </c>
-      <c r="B124" t="s">
+      <c r="H124" s="2" t="s">
         <v>801</v>
-      </c>
-      <c r="C124" t="s">
-        <v>802</v>
-      </c>
-      <c r="D124" t="s">
-        <v>212</v>
-      </c>
-      <c r="E124" t="s">
-        <v>803</v>
-      </c>
-      <c r="F124" t="s">
-        <v>804</v>
-      </c>
-      <c r="H124" s="2" t="s">
-        <v>805</v>
       </c>
     </row>
     <row r="125" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
+        <v>802</v>
+      </c>
+      <c r="B125" t="s">
+        <v>803</v>
+      </c>
+      <c r="C125" t="s">
+        <v>804</v>
+      </c>
+      <c r="D125" t="s">
+        <v>212</v>
+      </c>
+      <c r="E125" t="s">
+        <v>805</v>
+      </c>
+      <c r="F125" t="s">
         <v>806</v>
       </c>
-      <c r="B125" t="s">
+      <c r="H125" s="2" t="s">
         <v>807</v>
-      </c>
-      <c r="C125" t="s">
-        <v>808</v>
-      </c>
-      <c r="D125" t="s">
-        <v>256</v>
-      </c>
-      <c r="E125" t="s">
-        <v>809</v>
-      </c>
-      <c r="F125" t="s">
-        <v>810</v>
-      </c>
-      <c r="H125" s="2" t="s">
-        <v>811</v>
       </c>
     </row>
     <row r="126" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
+        <v>808</v>
+      </c>
+      <c r="B126" t="s">
+        <v>809</v>
+      </c>
+      <c r="C126" t="s">
+        <v>810</v>
+      </c>
+      <c r="D126" t="s">
+        <v>256</v>
+      </c>
+      <c r="E126" t="s">
+        <v>811</v>
+      </c>
+      <c r="F126" t="s">
         <v>812</v>
       </c>
-      <c r="B126" t="s">
+      <c r="H126" s="2" t="s">
         <v>813</v>
-      </c>
-      <c r="C126" t="s">
-        <v>814</v>
-      </c>
-      <c r="D126" t="s">
-        <v>212</v>
-      </c>
-      <c r="E126" t="s">
-        <v>815</v>
-      </c>
-      <c r="F126" t="s">
-        <v>816</v>
-      </c>
-      <c r="H126" s="2" t="s">
-        <v>817</v>
       </c>
     </row>
     <row r="127" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
+        <v>814</v>
+      </c>
+      <c r="B127" t="s">
+        <v>815</v>
+      </c>
+      <c r="C127" t="s">
+        <v>816</v>
+      </c>
+      <c r="D127" t="s">
+        <v>212</v>
+      </c>
+      <c r="E127" t="s">
+        <v>817</v>
+      </c>
+      <c r="F127" t="s">
         <v>818</v>
       </c>
-      <c r="B127" t="s">
+      <c r="H127" s="2" t="s">
         <v>819</v>
-      </c>
-      <c r="C127" t="s">
-        <v>820</v>
-      </c>
-      <c r="D127" t="s">
-        <v>212</v>
-      </c>
-      <c r="E127" t="s">
-        <v>225</v>
-      </c>
-      <c r="F127" t="s">
-        <v>633</v>
-      </c>
-      <c r="H127" s="2" t="s">
-        <v>821</v>
       </c>
     </row>
     <row r="128" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
+        <v>820</v>
+      </c>
+      <c r="B128" t="s">
+        <v>821</v>
+      </c>
+      <c r="C128" t="s">
         <v>822</v>
       </c>
-      <c r="B128" t="s">
+      <c r="D128" t="s">
+        <v>212</v>
+      </c>
+      <c r="E128" t="s">
+        <v>225</v>
+      </c>
+      <c r="F128" t="s">
+        <v>635</v>
+      </c>
+      <c r="H128" s="2" t="s">
         <v>823</v>
-      </c>
-      <c r="C128" t="s">
-        <v>824</v>
-      </c>
-      <c r="D128" t="s">
-        <v>212</v>
-      </c>
-      <c r="E128" t="s">
-        <v>825</v>
-      </c>
-      <c r="F128" t="s">
-        <v>257</v>
-      </c>
-      <c r="H128" s="2" t="s">
-        <v>826</v>
       </c>
     </row>
     <row r="129" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
+        <v>824</v>
+      </c>
+      <c r="B129" t="s">
+        <v>825</v>
+      </c>
+      <c r="C129" t="s">
+        <v>826</v>
+      </c>
+      <c r="D129" t="s">
+        <v>212</v>
+      </c>
+      <c r="E129" t="s">
         <v>827</v>
       </c>
-      <c r="B129" t="s">
+      <c r="F129" t="s">
+        <v>257</v>
+      </c>
+      <c r="H129" s="2" t="s">
         <v>828</v>
       </c>
-      <c r="C129" t="s">
+    </row>
+    <row r="130" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A130" t="s">
         <v>829</v>
       </c>
-      <c r="D129" t="s">
-        <v>212</v>
-      </c>
-      <c r="E129" t="s">
+      <c r="B130" t="s">
         <v>830</v>
       </c>
-      <c r="F129" t="s">
+      <c r="C130" t="s">
+        <v>831</v>
+      </c>
+      <c r="D130" t="s">
+        <v>212</v>
+      </c>
+      <c r="E130" t="s">
+        <v>832</v>
+      </c>
+      <c r="F130" t="s">
         <v>548</v>
       </c>
-      <c r="H129" s="2" t="s">
-        <v>831</v>
+      <c r="H130" s="2" t="s">
+        <v>833</v>
       </c>
     </row>
   </sheetData>
@@ -6995,6 +7024,7 @@
     <hyperlink ref="H127" r:id="rId126"/>
     <hyperlink ref="H128" r:id="rId127"/>
     <hyperlink ref="H129" r:id="rId128"/>
+    <hyperlink ref="H130" r:id="rId129"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
